--- a/data/processed/export/APOLLO_Screening_Results.xlsx
+++ b/data/processed/export/APOLLO_Screening_Results.xlsx
@@ -34,13 +34,13 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="00333333"/>
+      <b val="1"/>
+      <color rgb="00C65911"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
+      <color rgb="00333333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -140,16 +140,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -937,11 +937,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -974,11 +970,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -1011,11 +1003,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -1048,11 +1036,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1130,11 +1114,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
@@ -1167,11 +1147,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
@@ -1204,11 +1180,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1286,11 +1258,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
@@ -1368,11 +1336,7 @@
           <t>EC1</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
@@ -1405,11 +1369,7 @@
           <t>EC2; EC5</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
@@ -1442,11 +1402,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
@@ -1479,11 +1435,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -1516,11 +1468,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -1598,11 +1546,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
@@ -1635,11 +1579,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -1672,11 +1612,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -1709,11 +1645,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
@@ -1746,11 +1678,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -1828,11 +1756,7 @@
           <t>EC4</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
@@ -1865,11 +1789,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
@@ -1902,11 +1822,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
@@ -1939,11 +1855,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
@@ -1976,11 +1888,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
@@ -2013,11 +1921,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
@@ -2050,11 +1954,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
@@ -2087,11 +1987,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
@@ -2214,11 +2110,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
@@ -2251,11 +2143,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
@@ -2288,11 +2176,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
@@ -2325,11 +2209,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -2362,11 +2242,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -2489,11 +2365,7 @@
           <t>EC2; EC4</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
@@ -2526,11 +2398,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
@@ -2608,11 +2476,7 @@
           <t>EC2</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
@@ -2690,11 +2554,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
@@ -3050,11 +2910,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
@@ -3095,11 +2951,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
@@ -3140,11 +2992,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
@@ -3185,11 +3033,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
@@ -3226,11 +3070,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
@@ -3271,11 +3111,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
@@ -3316,11 +3152,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
@@ -3357,9 +3189,9 @@
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J67" s="2" t="n"/>
@@ -3402,11 +3234,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
@@ -3447,11 +3275,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
@@ -3492,11 +3316,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
@@ -3582,11 +3402,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
@@ -3627,11 +3443,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
@@ -3672,11 +3484,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
@@ -3713,11 +3521,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
@@ -3758,11 +3562,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
@@ -3803,11 +3603,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="n"/>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
@@ -3893,9 +3689,9 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J79" s="2" t="n"/>
@@ -3983,11 +3779,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="n"/>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
@@ -4099,9 +3891,7 @@
           <t>Software Engineering Job Market: Salaries, Trends &amp; Insights</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>

--- a/data/processed/export/APOLLO_Screening_Results.xlsx
+++ b/data/processed/export/APOLLO_Screening_Results.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,23 +34,11 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
       <color rgb="00333333"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -61,18 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,22 +111,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -696,12 +666,12 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -709,30 +679,26 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Big Code Search: A Bibliography</t>
+          <t>Goal-oriented assessment of product-line domains</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Code search is an essential task in software development. Developers often search the internet and other code databases for necessary source code snippets to ease the development efforts. Code search techniques also help learn programming as novice programmers or students can quickly retrieve (hopefully good) examples already used in actual software projects. Given the recurrence of the code search activity in software development, there is an increasing interest in the research community. To improve the code search experience, the research community suggests many code search tools and techniques. These tools and techniques leverage several different ideas and claim a better code search performance. However, it is still challenging to illustrate a comprehensive view of the field considering that existing studies generally explore narrow and limited subsets of used components. This study aims to devise a grounded approach to understanding the procedure for code search and build an operational taxonomy capturing the critical facets of code search techniques. Additionally, we investigate evaluation methods, benchmarks, and datasets used in the field of code search.</t>
+          <t>Software product-line engineering is a method for improving the efficiency and effectiveness of software development. Introducing such a method into an industrial software development environment is potentially of great benefit, but one cannot afford to stop product development while doing so. Rather, in Avaya we apply an incremental adoption strategy and therefore must identify which part(s) of the product line we will create first. Since we consider a product line to consist of a number of domains, the problem is to identify the right domains to start with. We identified two driving factors for selecting product-line domains: corporate impact and likelihood of success. Our assessment of candidate domains is driven by these two goals, which we decompose further into a set of domain selection criteria and corresponding questions. The data, i.e., the answers to the questions, are gathered during interview sessions with our domain experts and evaluated according to our goal decomposition formulas. We illustrate the approach by an example application for which we assessed 20 different domains for one of Avaya's major product lines. © 2003 IEEE.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Code search; code recommendation; code retrieval; find code; code snippet; code search procedure</t>
+          <t>Application programs; Computer architecture; Computer programming; Computer software; Mathematical programming; Product development; Computer industry; Different domains; Domain experts; Driving factors; Goal-oriented; Industrial software development; Selection criteria; Software product line engineerings; Software design</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -746,7 +712,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -754,30 +720,26 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>How Much Effort Do You Need to Expend on a Technical Interview? A Study of LeetCode Problem Solving Statistics</t>
+          <t>An Exploration of the Perceived Value of Information Technology Certification between Information Technology and Human Resources Professionals</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A technical interview is the culmination of the recruiting process for hiring software engineers in the tech industry. Many well-known companies, including Amazon, Meta (formerly Facebook), Alphabet (Google), and Microsoft, use it to filter candidates. However, the drawbacks of technical interviews are well-documented, including their lack of real-world relevance, bias towards newer developers, demanding time commitment, and potential to induce unnecessary anxiety and frustration. De-spite these criticisms, there is no clear indication that the industry will alter the format of technical interviews in the near future. To assist student developers in preparing for these challenges, we conducted a quantitative analysis using over 300,000 user profiles from LeetCode, arguably the most popular online platform for preparing software development candidates for interviews. Our analysis aims to provide developers with insights into the effort required to prepare for technical interviews, especially in terms of solving programming questions, to secure a position at a renowned company. © 2024 IEEE.</t>
+          <t>During the decade of the 1990s, many firms engaged in widespread internal dissemination of information technology (IT) in an effort to leverage the capabilities of IT into greater organizational efficiencies. Information technologies such as electronic mail, office automation applications, and enterprise resource planning systems, are a few of the most popular examples of organizational IT initiatives from the past decade. Today, the use of information technology is an integral part of the ordinary course of business and provides technologically progressive firms with heretofore-unseen opportunities. For example, Dell Computers developed and maintains a competitive advantage in the retail technology sector based partly upon the use if information technology that did not exist 10 years ago. Although business applications of information technology present firms with vast opportunity, there is a myriad of complexities associated with organizational IT usage. Generally, this paper examines one critical area: the human resource aspect of organizational IT usage. Specifically, the research presented herein answers the question “Do human resource and information technology professionals perceive information technology certification differently?” The question is of practical relevance when examined, as in this study, within the context of the candidate selection process for a firm evaluating potential hires for an information technology-related position. Initially, the current paper presents a comprehensive overview of the theoretical foundations of certification. From theory, we construct a testing methodology that utilizes, as subjects, practicing human resource and information technology professionals. An analysis of the collected data revealed a marked difference in the perception of information technology certification among the subject groups. Based on the results of structured interviews with the study participants, we present concluding explanations regarding the statistically significant differences among groups. © 2009 by IGI Global. All rights reserved.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Career; Coding challenge; Facebook; Google+; Hiring practices; Leetcode; MicroSoft; Problem-solving; Real-world; Technical interview; Software design</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC4</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>Enterprise resource planning; Information dissemination; Information use; Personnel selection; Automation applications; Enterprise resource planning systems; Information technology certification; Information technology professionals; Information technology usages; Organizational efficiency; Organizational information; Perceived value; Resource professionals; Value of information; Competition</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -791,7 +753,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -799,26 +761,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>“This Gig Is Not for Women”: Gender Stereotyping in Online Hiring</t>
+          <t>Demand and Status of a Scientific Degree in the Non-Academic Labour Market: Regional Case; [Востребованность и статус учёной степени на неакадемическом рынке труда: региональный кейс]</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This study examines gender segregation in the context of the so-called gig economy. In particular, it explores the role that stereotypes about male and female occupations play in sorting men and women into different jobs in an online freelance marketplace. The findings suggest that gender stereotypes are particularly salient in online hiring because employers typically contract for short-term, relatively low-value jobs based on limited information about job applicants. These conditions trigger the use of cognitive shortcuts about intrinsic gender characteristics linked to different skills and occupations. The results corroborate that female candidates are less likely to be hired for male-typed jobs (e.g., software development) but more likely to be hired for female-typed jobs (e.g., writing and translation) than equally qualified male candidates. Further, the study investigates three mechanisms predicted to attenuate the female penalty in male-typed jobs. The penalty is found to be self-reinforcing, as it perpetuates gender imbalances in worker activity across job categories that strengthen the sex typing of occupations. © The Author(s) 2019.</t>
+          <t>Technological leadership and innovation-driven growth have actualized the request for highly qualified personnel, which have recently been associated with holders of a scientific degree. In the academic field, a scientific degree is a testimony to the occupational status and an integral feature of professional growth and advancement. The reasonableness and significance of a scientific degree in the non-academic market are ambiguous. The purpose of this article is to investigate the opinion and assessments of the non-academic sphere representatives about the demand for the employees with a scientific degree and the status of a scientific degree outside the academic labour market. The research was conducted using the method of semi-structured interview with employers and representatives of seven enterprises in the south of Russia in the machine engineering, metalworking, ferrous metallurgy and IT sectors (n = 13). As a result of the study it was established that: in employment a scientific degree does not give competitive advantages to the applicant; a scientific degree has no value in the non-academic labour market, does not contribute to the advancement and occupation of a higher position in the enterprise; a scientific degree and the presence of employees with a scientific degree in the staff are considered as image-building, status marker and reputation capital of the enterprise; employers have stereotypes regarding scientific employees, which are associated both with the individual organization of labour processes and the compatibility of the scientific, creative and production process; the non-academic sector lacks a human resources strategy for dealing with such employees and a system of their incentives. The authors conclude that the demand for a scientific degree in the non-academic labour market is caused largely by a political request related with the belief that technological and innovative breakthroughs can provide highly qualified personnel with a scientific degree. The authors focus on the probable risks associated with the massification of degree holders, that can lead to a blurring of academic culture and loss of identity of the scientific community. © 2025 Moscow Polytechnic University. All rights reserved.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
@@ -832,7 +790,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -840,30 +798,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Using the DELPHI Method for Model for Role Assignment in the Software Industry</t>
+          <t>Evaluating the effectiveness of E-recruitment in IT companies: Overcoming technological constraints and regulatory compliance</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Over the past two decades, there has been a growing interest in modeling the elements that need to be considered when assigning people to roles in software projects, as evidenced by the number of available publications related to the topic. However, for the most part, these studies, have taken only a partial approach to the issue. Some have focused on the target role's competency profile, while others have tried to understand the preferences of software developers for activities linked to certain roles and the relationship between these preferences and the candidate's personal traits, to mention only two examples. Our research aims to find elements that can be integrated into an allocation model that complements current approaches by including competencies, personal traits, and project team building theories. To do so we performed an expert's consultation exercise using the DELPHI method; which allowed us to validate a set of patterns related to different candidate's personal traits, and the link between the team's motivational motors and their roles within the software development. © 2021 IEEE.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Decision making; Personnel selection; Assigning role in software project; DELPHI method and software engineering; Empirical studies; Personality trait in software project staffing; Personality traits; Software engineering empirical study; Software project; Software project staffing; Software design</t>
-        </is>
-      </c>
+          <t>As the Information Technology industry evolves, e-recruitment emerges as a pivotal tool for sourcing talent. However, challenges like technological constraints and regulatory compliance hinder its effectiveness. This cross-sectional study delves into the discerned effectiveness of e-recruitment methods and the associated barriers encountered by Information Technology companies in the adoption of these practices. A robust dataset comprising responses from 537 participants actively involved in recruitment activities across various sectors of the Information Technology industry was collected through a structured questionnaire. The analysis employed descriptive statistics to summarize sample demographics, inferential statistics including correlation and regression analyses to test hypotheses, and Harman's single-factor test to determine common method variance. The study identified several key findings aligned with its research objectives. Firstly, it confirmed a constructive association between the discerned effectiveness of e-recruitment methods and their adoption by Information Technology companies. However, it also revealed that technological constraints negatively impact the perceived effectiveness of e-recruitment, highlighting a critical barrier in the adoption process. Additionally, the study uncovered a significant association between the availability of skilled Information Technology professionals and the effectiveness of e-recruitment methods utilized by Information Technology firms. Moreover, it found that the integration of e-recruitment platforms with existing human resources systems positively influences their perceived effectiveness in the Information Technology sector, while regulatory compliance requirements pose significant barriers to their effective implementation. Furthermore, the study revealed that the user experience design in e-recruitment platforms affects their perceived effectiveness among Information Technology job seekers and human resources professionals. This study contributes novel insights by providing empirical evidence on the efficacy of e-recruitment methods in Information Technology organizations and the barriers hindering their adoption. Its findings offer insights for Information Technology companies and human resources professionals to enhance their recruitment strategies and address potential challenges, thereby unlocking the potential of e-recruitment in the Information Technology field. © The Author(s) 2025.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IC1; IC2</t>
+          <t>IC1; IC2; IC3; IC4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
@@ -877,7 +827,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -885,26 +835,26 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Leveraging Analytics for Talent Acquisition: Case of IT Sector in India</t>
+          <t>Assessing technical candidates on the social web</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>One of the challenges faced by Talent Acquisition teams today pertains to the acquisition of human resources by matching job descriptions and skillsets desired. It is more so in the case of competitive sectors like the Indian IT sector. There can be various channels for Talent Acquisition and accordingly, the cost and benefits might vary. However, the consequences of a mismatch have an impact on the quality of deliverables, high recruitment expenses and loss of revenue for the organization. With increased and diverse sources of data that are available to organizations today, there is ample opportunity to apply analytics for informed decision making in this field. This paper reveals useful insights that help streamline the Talent Acquisition process in the Indian IT Industry. The paper adopts a data-centric approach to examine the critical determinants for efficient and effective Talent Acquisition process in IT organizations. Selected supervised machine learning algorithms are applied for the analysis of the dataset. The study is likely to help organizations in reassessing their talent acquisition strategy with respect to key parameters like expected cost to company (CTC), candidate sourcing channels and optimal joining period. © 2020, Asia Pacific Journal of Information Systems. All rights reserved</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>The Social Web provides comprehensive and publicly available information about software developers, identifying them as contributors to open source projects, experts at maintaining ties on social network sites, or active participants on knowledge-sharing sites. These signals, when aggregated and summarized, could be used to define potential candidates' individual profiles: potential employers could qualitatively evaluate job seekers, even those lacking a formal degree or changing their career path, by assessing candidates' online contributions. At the same time, developers are aware of the Web's public nature and the possible uses of published information when they determine what to share with the world. Some might even try to manipulate public signals of technical qualifications, soft skills, and reputation in their favor. Assessing candidates on the Web for technical positions presents challenges to recruiters, the most serious being the interpretation of the provided signals. An in-depth discussion proposes guidelines for software engineers and recruiters to help recruiters interpret the value and trouble with the signals and metrics they use to assess a candidate's characteristics and skills. © 1984-2012 IEEE.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Computer supported cooperative work; Human computer interaction; Knowledge management; Knowledge representation; Social networking (online); Social sciences computing; Career paths; Group and organization interfaces; Information interfaces; Job seekers; Knowledge retrieval; Knowledge-sharing; Open source projects; Social Networks; Soft skills; Software developer; Software engineers; Technical qualification; Employment</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -913,12 +863,12 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -926,17 +876,21 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gender Discrimination in Hiring Decisions: Evidence from a Field Experiment</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+          <t>“This Gig Is Not for Women”: Gender Stereotyping in Online Hiring</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>This study examines gender segregation in the context of the so-called gig economy. In particular, it explores the role that stereotypes about male and female occupations play in sorting men and women into different jobs in an online freelance marketplace. The findings suggest that gender stereotypes are particularly salient in online hiring because employers typically contract for short-term, relatively low-value jobs based on limited information about job applicants. These conditions trigger the use of cognitive shortcuts about intrinsic gender characteristics linked to different skills and occupations. The results corroborate that female candidates are less likely to be hired for male-typed jobs (e.g., software development) but more likely to be hired for female-typed jobs (e.g., writing and translation) than equally qualified male candidates. Further, the study investigates three mechanisms predicted to attenuate the female penalty in male-typed jobs. The penalty is found to be self-reinforcing, as it perpetuates gender imbalances in worker activity across job categories that strengthen the sex typing of occupations. © The Author(s) 2019.</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
@@ -946,12 +900,12 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -959,15 +913,23 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Unlocking the Value of Artificial Intelligence in Human Resource Management Through Effective Implementation and Usage</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>A model for navigating interview processes in requirements elicitation</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Experts in requirements elicitation have interviews to stakeholders using various levels of knowledge to grasp and elicit user's requirements. This paper analyzes interview processes of these experts and explores a computation model for simulating them. This model can be used to navigate novice analysts' interview processes. It is a mixture consisting of a blackboard model and a state transition model in order to narrow the candidates for the questions that an expert analyst will ask the stakeholders next in the interview process. The candidates are selected based on the information that has been elicited from the stakeholders until now, and the blackboard model is for holding this information in the form of IEEE 830, a standard form of requirements specification documents. We have analyzed the experts' interview processes and constructed the instance of the computation model in sales management domain. And we recorded novices' processes, simulated it on the novices' ones, and showed that we could improve them by means of the model.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Computer simulation; Mathematical models; Software engineering; Specifications; Requirements elicitation; Software requirements specification; Requirements engineering</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -979,12 +941,12 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -992,15 +954,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Uncovering the skillsets required in computer science jobs using social network analysis</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>Education as a signal of trainability: Results from a vignette study with Italian employers</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Drawing on queuing theory, this study explores the relationship between education and labour market entry from the perspective of employers. On the basis of vignette study, we simulated a hiring process with a sample of recruiters and human resource managers. We analysed the role of education in the screening of applicants' resumes for job openings in the Information, Communication, and Technology sector in the Italian labour market. Findings reveal that employers attach importance to fine-grained indicators of school performance, such as grades and study duration to formulate their hiring decisions, in line with queuing theory. However, internships are disregarded as signals. Results are explained in light of the institutional arrangements that characterize the Italian school-to-work transition system: a standardized education system, poorly specific vocational tracks, weakly developed linkages between schools and firms, a remarkably high dropout rate before study completion. © 2014 © The Author 2014. Published by Oxford University Press. All rights reserved.</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1012,12 +978,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1025,17 +991,25 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Responsible artificial intelligence in human resources management: a review of the empirical literature</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+          <t>Hiring and Intra-occupational Gender Segregation in Software Engineering</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Women tend to be segregated into different subspecialties than men within male-dominated occupations, but the mechanisms contributing to such intra-occupational gender segregation remain obscure. In this study, I use data from an online recruiting platform and a survey to examine the hiring mechanisms leading to gender segregation within software engineering and development. I find that women are much more prevalent among workers hired in software quality assurance than in other software subspecialties. Importantly, jobs in software quality assurance are lower-paying and perceived as lower status than jobs in other software subspecialties. In examining the origins of this pattern, I find that it stems largely from women being more likely than men to apply for jobs in software quality assurance. Further, such gender differences in job applications are attenuated among candidates with stronger educational credentials, consistent with the idea that relevant accomplishments help mitigate gender differences in self-assessments of competence and belonging in these fields. Demand-side selection processes further contribute to gender segregation, as employers penalize candidates with quality assurance backgrounds, a subspecialty where women are overrepresented, when they apply for jobs in other, higher-status software subspecialties. © American Sociological Association 2020.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>engineering; gender disparity; gender identity; gender relations; labor market; occupation; software; womens employment; womens status; workplace</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
@@ -1045,12 +1019,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1058,30 +1032,26 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cross-national usability study of a housing accessibility app: findings from the European innovage project</t>
+          <t>Automated Question Generation for Technical Interviews Using Deep Learning Models</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>The present usability study concerns an evaluation of an Android based mobile application (app) targeting housing accessibility issues, in a prototype stage for a touch tablet. The objective was to identify and compare elicited usability issues involving senior citizens in two different national contexts: Sweden and Latvia. Applying a problem discovery approach, the study included individual sessions in home environments and follow-up user forums; researchers and user panel participants collaborated to formatively evaluate the app. To support decision-making, the task for the participants was to process information about their present or projected future functional capacity and environmental barriers in their current dwelling. The task was also to make use of a database of professionally assessed available apartments that could be considered for relocation. Data generated in the two countries were analyzed and compared.The results generated new knowledge on relevant usability issues in the two countries and were used to provide design recommendations for the app. The identified usability issues point to a need for a more thorough exploration of design solutions that are tailored for the targeted group of people aging with functional limitations. The results also highlight how national and cultural contexts may influence perceived usability and acceptance and thereby indicate the need to consider these contexts early on and throughout the development process.Tips for usability practitioners: Be aware of possible cross-national differences and handle those challenges in a structured and predefined way, and use real data and real sites to reach close and first-hand experiences.</t>
+          <t>The process of hiring technical talent often demands a thorough and effective evaluation method, though creating interview questions by hand can be slow and lead to uneven results. This paper introduces a tool that automatically generates targeted interview questions from job descriptions, using a specially adjusted BART model. The software, it depends on a selected dataset covering Software Engineering, Cloud Engineering, and Data Science, produces distinct, relevant, and varied questions that are suitable for specific task requirement. Also, it makes use of candidate and recruiter feedback via Reinforcement Learning from Human feedback (RLHF) in order to constantly improve its output, boosting the questions' fit and quality. The experiments using ROUGE metrics show this method not only improves the hiring process but also allows an adaptable way to boost the level of consistency of technical evaluations. © 2025 IEEE.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ICT products; aging; culture; functional capacity; housing provision; mobile applications; social innovation; software development; user interface; user involvement</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Deep learning; Employment; Feedback; Job analysis; Software engineering; Automated question generation; BART; Interview question generation; Language processing; Natural language processing; Natural languages; Recruitment automation; Reinforcement learning from human feedback; Reinforcement learnings; Technical interview; Automation</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
@@ -1090,12 +1060,12 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1103,15 +1073,23 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>A Field Study on the Use of Gen AI to Support Computing Education</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+          <t>Comparative analysis study of open source GIS in Malaysia</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Open source origin might appear like a major prospective change which is qualified to deliver in various industries and also competing means in developing countries. The leading purpose of this research study is to basically discover the degree of adopting Open Source Software (OSS) that is connected with Geographic Information System (GIS) application within Malaysia. It was derived based on inadequate awareness with regards to the origin ideas or even on account of techie deficiencies in the open origin instruments. This particular research has been carried out based on two significant stages; the first stage involved a survey questionnaire: to evaluate the awareness and acceptance level based on the comparison feedback regarding OSS and commercial GIS. This particular survey was conducted among three groups of candidates: government servant, university students and lecturers, as well as individual. The approaches of measuring awareness in this research were based on a comprehending signal plus a notion signal for each survey questions. These kinds of signs had been designed throughout the analysis in order to supply a measurable and also a descriptive signal to produce the final result. The second stage involved an interview session with a major organization that carries out available origin internet GIS; the Federal Department of Town and Country Planning Peninsular Malaysia (JPBD). The impact of this preliminary study was to understand the particular viewpoint of different groups of people on the available origin, and also their insufficient awareness with regards to origin ideas as well as likelihood may be significant root of adopting level connected with available origin options. © Published under licence by IOP Publishing Ltd.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Malaysia; Developing countries; Open source software; Remote sensing; Software engineering; Surveys; Comparative analysis; Federal Department; Internet GIS; Malaysia; Open sources; Open-source GIS; Research studies; University students; comparative study; developing world; GIS; instrumentation; questionnaire survey; software; urban planning; Geographic information systems</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1123,12 +1101,12 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1136,17 +1114,25 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Start-ups create career opportunities for scientists</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>EC2</t>
-        </is>
-      </c>
+          <t>Searching, examining, and exploiting in-demand technical (SEE IT) skills using web data mining</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>There has always been a mismatch between academic education and industry demands in various industry fields. Especially, in the computer related jobs such as software developers or engineers, employers and job seekers are experiencing a large curriculum or skill gap compared to other industry fields due to its fast-changing nature. In order to minimize the gap, identifying the current job skill trends and offering/learning relevant skills are critically important for both educators and students in the fast-paced job market. However, due to the lack of relative information about the trends of in demand technical skills in certain regions or around the nation, it is difficult for educators to keep up with these changes and determine what needs to be conveyed to students so they can be ready for the job on day one. In this paper, in order to address these challenges, we focused on the analysis of in demand technical skills and their trends in software developer and engineer jobs around the nation. We collected and analyzed over 120,000 software developer or engineer job postings and summarized demanding and required skills from different regions throughout the nation. © 2020 Knowledge Systems Institute Graduate School. All rights reserved.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Curricula; Engineers; Software engineering; Students; Academic education; Job postings; Job seekers; Job skills; Relative information; Software developer; Technical skills; Web data mining; Data mining</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>IC1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
@@ -1161,7 +1147,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1169,7 +1155,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Comparing Advantages in India’s Computer Hardware and Software Sectors</t>
+          <t>Gender Discrimination in Hiring Decisions: Evidence from a Field Experiment</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
@@ -1189,12 +1175,12 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1202,30 +1188,18 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>How Are We Detecting Inconsistent Method Names? An Empirical Study from Code Review Perspective</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Proper naming of methods can make program code easier to understand, and thus enhance software maintainability. Yet, developers may use inconsistent names due to poor communication or a lack of familiarity with conventions within the software development lifecycle. To address this issue, much research effort has been invested into building automatic tools that can check for method name inconsistency and recommend consistent names. However, existing datasets generally do not provide precise details about why a method name was deemed improper and required to be changed. Such information can give useful hints on how to improve the recommendation of adequate method names. Accordingly, we construct a sample method-naming benchmark, ReName4J, by matching name changes with code reviews. We then present an empirical study on how state-of-the-art techniques perform in detecting or recommending consistent and inconsistent method names based on ReName4J. The main purpose of the study is to reveal a different perspective based on reviewed names rather than proposing a complete benchmark. We find that the existing techniques underperform on our review-driven benchmark, both in inconsistent checking and the recommendation. We further identify potential biases in the evaluation of existing techniques, which future research should consider thoroughly.</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Method Name Recommendation; Consistency Checking; Code Review; Empirical Study</t>
-        </is>
-      </c>
+          <t>Uncovering the skillsets required in computer science jobs using social network analysis</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
@@ -1239,7 +1213,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1247,7 +1221,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Success of cloud computing adoption over an era in human resource management systems: a comprehensive meta-analytic literature review</t>
+          <t>AI ethics and governance in business management: challenges, opportunities, and a comparative analysis</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -1255,7 +1229,7 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1272,7 +1246,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1280,17 +1254,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ROSE: An IDE-Based Interactive Repair Framework for Debugging</t>
+          <t>Synthesising Privacy by Design Knowledge Toward Explainable Internet of Things Application Designing in Healthcare</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Debugging is costly. Automated program repair (APR) holds the promise of reducing its cost by automatically fixing errors. However, current techniques are not easily applicable in a realistic debugging scenario because they assume a high-quality test suite and frequent program re-execution, have low repair efficiency, and only handle a limited set of errors. To improve the practicality of APR for debugging, we propose ROSE, an interactive repair framework that is able to suggest quick and effective repairs of semantic errors while debugging in an Integrated Development Environment (IDE). ROSE allows an easy integration of existing APR patch generators and can do program repair without assuming the existence of a test suite and without requiring program re-execution. It works in conjunction with an IDE debugger and assumes a debugger stopping point where a problem symptom is observed. ROSE asks the developer to quickly describe the symptom. Then it uses the stopping point, the identified symptom, and the current environment to identify potentially faulty lines, uses a variety of APR techniques to suggest repairs at those lines, and validates those repairs without re-executing the program. Finally, it presents the results so the developer can examine, select, and make the appropriate repair. ROSE uses novel approaches to achieve effective fault localization and patch validation without a test suite or program re-execution. For fault localization, ROSE builds on a fast abstract interpretation-based flow analysis to compute a static backward slice approximating the real dynamic slice while taking into account the symptom and the current execution. For patch validation without re-running the program, ROSE generates simulated traces based on a live-programming system for both the original and repaired executions and compares the traces with respect to the problem symptoms to infer patch correctness. We implemented a prototype of ROSE that works in an Eclipse-based IDE and evaluated its potency and utility with an effectiveness study and a user study. We found that ROSE’s fault localization and validation are highly effective and a ROSE-based tool using existing APR patch generators generated correct repair suggestions for many errors in only seconds. Moreover, the user study demonstrated that ROSE was helpful for debugging and developers liked to use it.</t>
+          <t>Privacy by Design (PbD) is the most common approach followed by software developers who aim to reduce risks within their application designs, yet it remains commonplace for developers to retain little conceptual understanding of what is meant by privacy. A vision is to develop an intelligent privacy assistant to whom developers can easily ask questions to learn how to incorporate different privacy-preserving ideas into their IoT application designs. This article lays the foundations toward developing such a privacy assistant by synthesising existing PbD knowledge to elicit requirements. It is believed that such a privacy assistant should not just prescribe a list of privacy-preserving ideas that developers should incorporate into their design. Instead, it should explain how each prescribed idea helps to protect privacy in a given application design context—this approach is defined as “Explainable Privacy.” A total of 74 privacy patterns were analysed and reviewed using ten different PbD schemes to understand how each privacy pattern is built and how each helps to ensure privacy. Due to page limitations, we have presented a detailed analysis in Reference [3]. In addition, different real-world Internet of Things (IoT) use-cases, including a healthcare application, were used to demonstrate how each privacy pattern could be applied to a given application design. By doing so, several knowledge engineering requirements were identified that need to be considered when developing a privacy assistant. It was also found that, when compared to other IoT application domains, privacy patterns can significantly benefit healthcare applications. In conclusion, this article identifies the research challenges that must be addressed if one wishes to construct an intelligent privacy assistant that can truly augment software developers’ capabilities at the design phase.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Debugging; Interactive Repair Framework; Automated Program Repair; Integrated Development Environment</t>
+          <t>Internet of Things; privacy; privacy by design; privacy assistant; knowledge engineering; healthcare; explainable privacy</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1299,11 +1273,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
@@ -1312,12 +1282,12 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1325,15 +1295,23 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Possible Solutions of Wage Problems in Russian IT Market</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
+          <t>A Review of Peer Code Review in Higher Education</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Peer review is the standard process within academia for maintaining publication quality, but it is also widely employed in other settings, such as education and industry, for improving work quality and for generating actionable feedback to content authors. For example, in the software industry peer review of program source code—or peer code review—is a key technique for detecting bugs and maintaining coding standards. In a programming education context, although peer code review offers potential benefits to both code reviewers and code authors, individuals are typically less experienced, which presents a number of challenges. Some of these challenges are similar to those reported in the educational literature on peer review in other academic disciplines, but reviewing code presents unique difficulties. Better understanding these challenges and the conditions under which code review can be taught and implemented successfully in computer science courses is of value to the computing education community. In this work, we conduct a systematic review of the literature on peer code review in higher education to examine instructor motivations for conducting peer code review activities, how such activities have been implemented in practice, and the primary benefits and difficulties that have been reported. We initially identified 187 potential studies and analyzed 51 empirical studies pertinent to our goals. We report the most commonly cited benefits (e.g., the development of programming-related skills) and barriers (e.g., low student engagement), and we identify a wide variety of tools that have been used to facilitate the peer code review process. While we argue that more empirical work is needed to validate currently reported results related to learning outcomes, there is also a clear need to address the challenges around student motivation, which we believe could be an important avenue for future research.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Peer review; code review; higher education; peer code review; programming course; systematic literature review; systematic review</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1345,12 +1323,12 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1358,15 +1336,23 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Competences for Digital Transformation in Companies – An Analysis of Job Advertisements in Germany</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
+          <t>XCoS: Explainable Code Search Based on Query Scoping and Knowledge Graph</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>When searching code, developers may express additional constraints (e.g., functional constraints and nonfunctional constraints) on the implementations of desired functionalities in the queries. Existing code search tools treat the queries as a whole and ignore the different implications of different parts of the queries. Moreover, these tools usually return a ranked list of candidate code snippets without any explanations. Therefore, the developers often find it hard to choose the desired results and build confidence on them. In this article, we conduct a developer survey to better understand and address these issues and induct some insights from the survey results. Based on the insights, we propose XCoS, an explainable code search approach based on query scoping and knowledge graph. XCoS extracts a background knowledge graph from general knowledge bases like Wikidata and Wikipedia. Given a code search query, XCoS identifies different parts (i.e., functionalities, functional constraints, nonfunctional constraints) from it and use the expressions of functionalities and functional constraints to search the codebase. It then links both the query and the candidate code snippets to the concepts in the background knowledge graph and generates explanations based on the association paths between these two parts of concepts together with relevant descriptions. XCoS uses an interactive user interface that allows the user to better understand the associations between candidate code snippets and the query from different aspects and choose the desired results. Our evaluation shows that the quality of the extracted background knowledge and the concept linkings in codebase is generally high. Furthermore, the generated explanations are considered complete, concise, and readable, and the approach can help developers find the desired code snippets more accurately and confidently.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Code search; explainability; knowledge; concept</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC5</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1383,7 +1369,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1391,7 +1377,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Challenges and practices of deep learning model reengineering: A case study on computer vision</t>
+          <t>Usage of&amp;#xa0;Generative Artificial Intelligence for&amp;#xa0;the&amp;#xa0;Design of&amp;#xa0;Graphic User Interfaces: Initial Approaches</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1399,7 +1385,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1416,7 +1402,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1424,7 +1410,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Age-related bias and artificial intelligence: a scoping review</t>
+          <t>Achieving a Data-Driven Risk Assessment Methodology for Ethical AI</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
@@ -1432,7 +1418,7 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1444,12 +1430,12 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1457,17 +1443,25 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>The Hidden Price of&amp;#xa0;Poor Cooperation – Exploring Industry Perspectives on&amp;#xa0;Social Debt</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+          <t>Impacts of an Industrial Partnership with a Historically Black University on the Computing Career Decisions of Black Undergraduate Students</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>In order to rectify the historical marginalization of Black workers in computing fields, many academic and industrial initiatives have been established to increase the diversity and inclusion in the tech industry. In this study, we explored how one particular post-secondary education program at one historically black institution known as the Google in Residence (GIR) program impacted students’ interests and their pursuit of computing-related careers. Data on employment outcomes at this institution showed that the GIR participants who obtained internships and full-time employment at Google were predominantly international students, not African American students who make up the majority of the undergraduate student and about half of the GIR participants. To understand this phenomenon better, we interviewed 27 students who spanned all 4 years of study and included African American and international students. The interviews were structured to elicit a wide range of factors influencing career decisions. Our analysis describes the impact of a particular GIR introductory-level programming course and other GIR program impacts beyond the introductory-level course. We found that the GIR introductory course was engaging, inspired students to change their degree in a more computing-oriented direction and supported internship applications. The informational workshops, networking events, mock-interviews, and advising of the computer science club, which were supported by the GIR program, built students’ confidence in interviewing and obtaining full-time employment within the tech industry. While the GIR course and program had a positive influence on students of all backgrounds, the reputation of Google was especially motivating for international students. However, the African American students in this study generally had career aspirations and goals that were less tied to specific companies or industries. Based on our findings, potential improvements could include broadening awareness and access of the GIR course to non-computer science majors, offering summer programs to increase students’ computational confidence, and increasing the diversity of GIR and computer science instructors.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>inclusion; internships; industrial partnerships</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
@@ -1477,12 +1471,12 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1490,30 +1484,18 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ClarifyGPT: A Framework for Enhancing LLM-Based Code Generation via Requirements Clarification</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Large Language Models (LLMs), such as ChatGPT, have demonstrated impressive capabilities in automatically generating code from provided natural language requirements. However, in real-world practice, it is inevitable that the requirements written by users might be ambiguous or insufficient. Current LLMs will directly generate programs according to those unclear requirements, regardless of interactive clarification, which will likely deviate from the original user intents. To bridge that gap, we introduce a novel framework named ClarifyGPT, which aims to enhance code generation by empowering LLMs with the ability to identify ambiguous requirements and ask targeted clarifying questions. Specifically, ClarifyGPT first detects whether a given requirement is ambiguous by performing a code consistency check. If it is ambiguous, ClarifyGPT prompts an LLM to generate targeted clarifying questions. After receiving question responses, ClarifyGPT refines the ambiguous requirement and inputs it into the same LLM to generate a final code solution. To evaluate our ClarifyGPT, we invite ten participants to use ClarifyGPT for code generation on two benchmarks: MBPP-sanitized and MBPP-ET. The results show that ClarifyGPT elevates the performance (Pass@1) of GPT-4 from 70.96% to 80.80% on MBPP-sanitized. Furthermore, to conduct large-scale automated evaluations of ClarifyGPT across different LLMs and benchmarks without requiring user participation, we introduce a high-fidelity simulation method to simulate user responses. The results demonstrate that ClarifyGPT can significantly enhance code generation performance compared to the baselines. In particular, ClarifyGPT improves the average performance of GPT-4 and ChatGPT across five benchmarks from 62.43% to 69.60% and from 54.32% to 62.37%, respectively. A human evaluation also confirms the effectiveness of ClarifyGPT in detecting ambiguous requirements and generating high-quality clarifying questions. We believe that ClarifyGPT can effectively facilitate the practical application of LLMs in real-world development environments.</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Code Generation; Large Language Model; Prompt Engineering</t>
-        </is>
-      </c>
+          <t>Workplace Experiences of Muslim Women in STEM in Canada: An Intersectional Qualitative Analysis</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2; EC4</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -1527,7 +1509,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1535,7 +1517,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Jesuit-Informed Casuistry and the Role of Principles for Organizational Ethics</t>
+          <t>Revolutionizing software developmental processes by utilizing continuous software approaches</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -1543,7 +1525,7 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1560,7 +1542,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1568,7 +1550,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Maximizing Business Potential by Utilizing FinTech Innovative Technologies and Strategies</t>
+          <t>On Using Large Language Models Pre-trained on&amp;#xa0;Digital Twins as&amp;#xa0;Oracles to&amp;#xa0;Foster the&amp;#xa0;Use of&amp;#xa0;Formal Methods in&amp;#xa0;Practice</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
@@ -1576,7 +1558,7 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1593,7 +1575,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1601,7 +1583,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>The Fractional CIO in SMEs: conceptualization and research agenda</t>
+          <t>From Requirements to Prototyping: Proposal and Evaluation of an Artifact to Support Interface Design in the Context of Autism</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -1609,7 +1591,7 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1626,7 +1608,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1634,7 +1616,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Much more than a prediction: Expert-based software effort estimation as a behavioral act</t>
+          <t>Enhancing continuous integration predictions: a hybrid LSTM-GRU deep learning framework with evolved DBSO algorithm</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
@@ -1659,7 +1641,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1667,7 +1649,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>The large language model diagnoses tuberculous pleural effusion in pleural effusion patients through clinical feature landscapes</t>
+          <t>Technology, multidisciplinarianism, and the university</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
@@ -1675,7 +1657,7 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1687,12 +1669,12 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1700,30 +1682,18 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Dependency Update Strategies and Package Characteristics</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Managing project dependencies is a key maintenance issue in software development. Developers need to choose an update strategy that allows them to receive important updates and fixes while protecting them from breaking changes. Semantic Versioning was proposed to address this dilemma, but many have opted for more restrictive or permissive alternatives. This empirical study explores the association between package characteristics and the dependency update strategy selected by its dependents to understand how developers select and change their update strategies. We study over 112,000 Node Package Manager (npm) packages and use 19 characteristics to build a prediction model that identifies the common dependency update strategy for each package. Our model achieves a minimum improvement of 72% over the baselines and is much better aligned with community decisions than the npm default strategy. We investigate how different package characteristics can influence the predicted update strategy and find that dependent count, age, and release status to be the highest influencing features. We complement the work with qualitative analyses of 160 packages to investigate the evolution of update strategies. While the common update strategy remains consistent for many packages, certain events such as the release of the 1.0.0 version or breaking changes influence the selected update strategy over time.</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Dependency update strategy; dependency management; software ecosystems; npm</t>
-        </is>
-      </c>
+          <t>An Automated Approach to&amp;#xa0;Identify Source Code Files Affected by&amp;#xa0;Architectural Technical Debt</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
@@ -1737,7 +1707,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1745,7 +1715,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Runtime monitoring of operational design domain to safeguard machine learning components</t>
+          <t>Documenting research software in engineering science</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
@@ -1753,7 +1723,7 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1770,7 +1740,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1778,7 +1748,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Multimodal Agent AI: A Survey of Recent Advances and Future Directions</t>
+          <t>What is an app store? The software engineering perspective</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -1803,7 +1773,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1811,7 +1781,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Trustworthy AI and Corporate Governance: The EU’s Ethics Guidelines for Trustworthy Artificial Intelligence from a Company Law Perspective</t>
+          <t>Prioritizing unit tests using object-oriented metrics, centrality measures, and machine learning algorithms</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
@@ -1819,7 +1789,7 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1836,7 +1806,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1844,7 +1814,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>An Integrated Operations and Maintenance Admissions Management System Using Artificial Intelligence Assistance</t>
+          <t>A comprehensive analysis of challenges and strategies for software release notes on GitHub</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
@@ -1852,7 +1822,7 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1869,7 +1839,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Potential to use metaverse for future teaching and learning</t>
+          <t>A data-driven API recommendation approach for service mashup composition</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
@@ -1885,7 +1855,7 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC4</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1902,7 +1872,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1910,7 +1880,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Research, Learning, and Innovation Through Industry-Academia Synergy with the Industry Interaction Cell Model</t>
+          <t>Enhancing Productivity with&amp;#xa0;AI During the&amp;#xa0;Development of&amp;#xa0;an&amp;#xa0;ISMS: Case Kempower</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
@@ -1918,7 +1888,7 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -1935,7 +1905,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1943,7 +1913,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Applying Data Mining Techniques in People Analytics for Balancing Employees’ Interests</t>
+          <t>Potential Candidate Selection Using Information Extraction and Skyline Queries</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
@@ -1968,7 +1938,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1976,7 +1946,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Managing the&amp;#xa0;Root Causes of&amp;#xa0;“Internal API Hell”: An Experience Report</t>
+          <t>Creating of a General Purpose Language for the Construction of Dynamic Reports</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr"/>
@@ -1984,7 +1954,7 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -1996,12 +1966,12 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2009,30 +1979,18 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Leveraging Rust Types for Program Synthesis</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>The Rust type system guarantees memory safety and data-race freedom. However, to satisfy Rust's type rules, many familiar implementation patterns must be adapted substantially. These necessary adaptations complicate programming and might hinder language adoption. In this paper, we demonstrate that, in contrast to manual programming, automatic synthesis is not complicated by Rust's type system, but rather benefits in two major ways. First, a Rust synthesizer can get away with significantly simpler specifications. While in more traditional imperative languages, synthesizers often require lengthy annotations in a complex logic to describe the shape of data structures, aliasing, and potential side effects, in Rust, all this information can be inferred from the types, letting the user focus on specifying functional properties using a slight extension of Rust expressions. Second, the Rust type system reduces the search space for synthesis, which improves performance. In this work, we present the first approach to automatically synthesizing correct-by-construction programs in safe Rust. The key ingredient of our synthesis procedure is Synthetic Ownership Logic, a new program logic for deriving programs that are guaranteed to satisfy both a user-provided functional specification and, importantly, Rust's intricate type system. We implement this logic in a new tool called RusSOL. Our evaluation shows the effectiveness of RusSOL, both in terms of annotation burden and performance, in synthesizing provably correct solutions to common problems faced by new Rust developers.</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Rust; program logic; program synthesis; type systems</t>
-        </is>
-      </c>
+          <t>Method for Eliciting Requirements in the Area of Digital Sovereignty (MERDigS)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2; EC3</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
@@ -2041,12 +1999,12 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2054,30 +2012,18 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Open Collaborative Writing: Investigation of the Fork-and-Pull Model</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Work of all kinds increasingly takes place via networked digital environments that support diverse modes of collaboration. Previous work has investigated how collaborative writing takes place in shared and open workspaces. This study investigates how the "fork-and-pull'' model of distributed version management, now widely utilized in software development, supports coordination and public contribution in collaborative writing. We employ a case study approach to understand coordination around written artifacts in an open pull-based environment. Through interviews and archival analysis of two open text projects: a mathematics textbook on homotopy type theory (HoTT) and open source policies by 18F, a branch of federal agency, we reconstruct how text artifacts were created. We find that in both cases an intensive multi-channel communication among a small core preceded an explicit release action in the form of public communication to solicit broader contribution. Our analysis reveals a dichotomy between two modes of collaboration: a perfecting mode of crafting a public written document versus an evolution mode. In perfecting, authors used the fork-and-pull model to manage contributions refining the text to a more correct version. In evolution, authors used the fork-and-pull model to use a written artifact as a template and starting point, customizing it to their relevant scope. Based on our results, we consider how we might design systems and policies to support pull-based coordination around written artifacts and the forms it takes.</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>case study; coordination; fork-and-pull model; mixed-methods; open collaborative writing; open source model</t>
-        </is>
-      </c>
+          <t>Gender disparity in U.S. patenting</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
@@ -2091,7 +2037,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2099,7 +2045,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Bridging Business Analysts Competence Gaps: Labor Market Needs Versus Education Standards</t>
+          <t>AI Driving Game Changing Trends in Project Delivery and Enterprise Performance</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr"/>
@@ -2107,7 +2053,7 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2124,7 +2070,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2132,7 +2078,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Data-driven prototyping via natural-language-based GUI retrieval</t>
+          <t>Runtime monitoring of operational design domain to safeguard machine learning components</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr"/>
@@ -2140,7 +2086,7 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC4</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2157,7 +2103,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -2165,7 +2111,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Mining domain-specific edit operations from model repositories with applications to semantic lifting of model differences and change profiling</t>
+          <t>&lt;span&gt;prompt4vis&lt;/span&gt;: prompting large language models with example mining for tabular data visualization</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
@@ -2173,7 +2119,7 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2190,7 +2136,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -2198,7 +2144,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Applying a&amp;#xa0;Prompt Pattern Sequence for&amp;#xa0;Decision-Making in&amp;#xa0;Microservices Architectures</t>
+          <t>Operationalising AI governance through ethics-based auditing: an industry case study</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
@@ -2223,7 +2169,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -2231,7 +2177,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Intermittent control and retinal optic flow when maintaining a curvilinear path</t>
+          <t>Enhancing Research, Learning, and Innovation Through Industry-Academia Synergy with the Industry Interaction Cell Model</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
@@ -2251,12 +2197,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -2264,30 +2210,18 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Inductive Synthesis of Structurally Recursive Functional Programs from Non-recursive Expressions</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>We present a novel approach to synthesizing recursive functional programs from input-output examples. Synthesizing a recursive function is challenging because recursive subexpressions should be constructed while the target function has not been fully defined yet. We address this challenge by using a new technique we call block-based pruning. A block refers to a recursion- and conditional-free expression (i.e., straight-line code) that yields an output from a particular input. We first synthesize as many blocks as possible for each input-output example, and then we explore the space of recursive programs, pruning candidates that are inconsistent with the blocks. Our method is based on an efficient version space learning, thereby effectively dealing with a possibly enormous number of blocks. In addition, we present a method that uses sampled input-output behaviors of library functions to enable a goal-directed search for a recursive program using the library. We have implemented our approach in a system called Trio and evaluated it on synthesis tasks from prior work and on new tasks. Our experiments show that Trio outperforms prior work by synthesizing a solution to 98% of the benchmarks in our benchmark suite.</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Programming by Example; Recursive Functional Programs; Synthesis</t>
-        </is>
-      </c>
+          <t>Data-access performance anti-patterns in data-intensive systems</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
@@ -2296,12 +2230,12 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -2309,30 +2243,18 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>"They Can Only Ever Guide": How an Open Source Software Community Uses Roadmaps to Coordinate Effort</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Unlike in commercial software development, open source software (OSS) projects do not generally have managers with direct control over how developers spend their time, yet for projects with large, diverse sets of contributors, the need exists to focus and steer development in a particular direction in a coordinated way. This is especially important for "infrastructure" projects, such as critical libraries and programming languages that many other people depend on. Some projects have taken the approach of borrowing planning tools that originated in commercial development, despite the fact that these techniques were designed for very different contexts, e.g. strong top-down control and profit motives. Little research has been done to understand how these practices are adapted to a new context. In this paper, we examine the Rust project's use of roadmaps: how has an important OSS infrastructure project adapted an inherently top-down tool to the freewheeling world of OSS? We find that because Rust's roadmaps are built in part by summarizing what motivated developers most prefer to work on, they are in some ways more a description of the motivated labor available than they are a directive that the community move in a particular direction. They allow the community to avoid wasting time on unpopular proposals by revealing that there will be little help in building them, and encouraging work on popular features by making visible the amount of consensus in those features. Roadmaps generate a collective focus without limiting the full scope of what developers work on: roadmap issues consume proportionally more effort than other issues, but constitute a minority of the work done (i.e issues and pull requests made) by both central and peripheral participants. They also create transparency among and beyond the community into what central contributors' plans are, and allow more rational decision-making by providing a way for evidence about community needs to be linked to decision-making.</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>collaboration; common pool resources; open source; rust language</t>
-        </is>
-      </c>
+          <t>Configuring Participatory Design of ICT for Aging Well as Matters of Care</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2; EC4</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
@@ -2346,7 +2268,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -2354,7 +2276,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Establishing Effective PhD Supervision for Cross-Disciplinary Research in Advanced Production</t>
+          <t>Revolutionizing User Testing: AI-Powered Feedback with Personalized Personas</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
@@ -2362,7 +2284,7 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2379,7 +2301,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -2387,7 +2309,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>The ethical wisdom of AI developers</t>
+          <t>Competing for Technology Talent: Listed Companies Versus Funded Startups in India</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr"/>
@@ -2407,12 +2329,12 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -2420,30 +2342,18 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Explainable Program Synthesis by Localizing Specifications</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>The traditional formulation of the program synthesis problem is to find a program that meets a logical correctness specification. When synthesis is successful, there is a guarantee that the implementation satisfies the specification. Unfortunately, synthesis engines are typically monolithic algorithms, and obscure the correspondence between the specification, implementation and user intent. In contrast, humans often include comments in their code to guide future developers towards the purpose and design of different parts of the codebase. In this paper, we introduce subspecifications as a mechanism to augment the synthesized implementation with explanatory notes of this form. In this model, the user may ask for explanations of different parts of the implementation; the subspecification generated in response is a logical formula that describes the constraints induced on that subexpression by the global specification and surrounding implementation. We develop algorithms to construct and verify subspecifications and investigate their theoretical properties. We perform an experimental evaluation of the subspecification generation procedure, and measure its effectiveness and running time. Finally, we conduct a user study to determine whether subspecifications are useful: we find that subspecifications greatly aid in understanding the global specification, in identifying alternative implementations, and in debugging faulty implementations.</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Program synthesis; explainability; program comprehension</t>
-        </is>
-      </c>
+          <t>A meta-analysis on social exchange relationships and employee innovation in teams</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
@@ -2457,7 +2367,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -2465,7 +2375,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Towards ensemble-based use case point prediction</t>
+          <t>Modelling the quantification of requirements technical debt</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
@@ -2473,7 +2383,7 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
+          <t>EC5</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2490,7 +2400,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -2498,17 +2408,17 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Automatic Rule Checking for Microservices: Supporting Security Analysis with Explainability</t>
+          <t>Inductive Synthesis of Structurally Recursive Functional Programs from Non-recursive Expressions</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Software security analysis is often done manually, raising performance and correctness issues. Introducing automation is challenging because human verification of the outcomes is often required, especially for security assessment and certification. The distributed nature of microservice applications further increases these concerns.We present an approach for automatically checking architectural security rules on models of microservice applications. It provides explainability for verdicts of rules that are expressed as model queries in our rule specification language. This comprehensible, step-by-step evidence leverages traceability information from the input models to link to artifacts in code. Hence, the complete analysis process from source code via model to rule verdict can be traced and verified. Custom rules can be formulated in addition to a library of 25 best-practice architectural security rules.We evaluated the approach’s correctness by checking the 25 rules on 16 dataflow diagrams of microservice applications with a prototype (called MicroCertiSec) and observed promising results (precision=0.98; recall=1). Additionally, we performed an evaluation with industry experts and academics to gain initial insights into the approach’s usefulness for real-world security analysis. The nine participants gave highly positive feedback on usefulness and usability and stated they would use such an approach in their daily work.</t>
+          <t>We present a novel approach to synthesizing recursive functional programs from input-output examples. Synthesizing a recursive function is challenging because recursive subexpressions should be constructed while the target function has not been fully defined yet. We address this challenge by using a new technique we call block-based pruning. A block refers to a recursion- and conditional-free expression (i.e., straight-line code) that yields an output from a particular input. We first synthesize as many blocks as possible for each input-output example, and then we explore the space of recursive programs, pruning candidates that are inconsistent with the blocks. Our method is based on an efficient version space learning, thereby effectively dealing with a possibly enormous number of blocks. In addition, we present a method that uses sampled input-output behaviors of library functions to enable a goal-directed search for a recursive program using the library. We have implemented our approach in a system called Trio and evaluated it on synthesis tasks from prior work and on new tasks. Our experiments show that Trio outperforms prior work by synthesizing a solution to 98% of the benchmarks in our benchmark suite.</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Security; microservices; software architecture; model-driven engineering; application analysis; dataflow diagrams</t>
+          <t>Programming by Example; Recursive Functional Programs; Synthesis</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2517,11 +2427,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
@@ -2535,7 +2441,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -2543,7 +2449,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Towards fair graph-based machine learning software: unveiling and mitigating graph model bias</t>
+          <t>Dynamic Retrieval Augmented Generation of Ontologies using Artificial Intelligence (DRAGON-AI)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
@@ -2551,7 +2457,7 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
+          <t>EC2</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2563,12 +2469,12 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -2576,30 +2482,18 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Understanding the OSS Communities of Deep Learning Frameworks: A Comparative Case Study of PyTorch and TensorFlow</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Over the past two decades, deep learning has received tremendous success in developing software systems across various domains. Deep learning frameworks have been proposed to facilitate the development of such software systems, among which, PyTorch and TensorFlow stand out as notable examples. Considerable attention focuses on exploring software engineering practices and addressing diverse technical aspects in developing and deploying deep learning frameworks and software systems. Despite these efforts, little is known about the open source software communities involved in the development of deep learning frameworks.In this article, we perform a comparative investigation into the open source software communities of the two representative deep learning frameworks, PyTorch and TensorFlow. To facilitate the investigation, we compile a dataset of 2,792 and 3,288 code commit authors, along with 9,826 and 19,750 participants engaged in issue events on GitHub, from the two communities, respectively. With the dataset, we first characterize the structures of the two communities by employing four operationalizations to classify contributors into various roles and inspect the contributions made by common contributors across the two communities. We then conduct a longitudinal analysis to characterize the evolution of the two communities across various releases, in terms of the numbers of contributors with various roles and role transitions among contributors. Finally, we explore the causal effects between community characteristics and the popularity of the two frameworks.We find that the TensorFlow community harbors a larger base of contributors, encompassing a higher proportion of core developers and a more extensive cohort of active users compared to the PyTorch community. In terms of the technical background of the developers, 64.4% and 56.1% developers in the PyTorch and TensorFlow communities are employed by the leading companies of the corresponding open source software projects, Meta and Google, respectively; 25.9% and 21.9% core developers in the PyTorch and TensorFlow communities possess Ph.D. degrees, while 77.2% and 77.7% contribute to other machine learning or deep learning open source projects, respectively. Developers contributing to both communities demonstrate spatial and temporal similarities to some extent in their pull requests across the respective projects. The evolution of contributors with various roles exhibits a consistent upward trend over time in the PyTorch community. Conversely, a noticeable turning point in the growth of contributors characterizes the evolution of the TensorFlow community. Both communities show a statistically significant decreasing trend in the inflow rates of core developers. Furthermore, we observe statistically significant causal effects between the expansion of communities and retention of core developers and the popularity of deep learning frameworks. Based on our findings, we discuss implications, provide recommendations for sustaining open source software communities of deep learning frameworks, and outline directions for future research.</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Deep learning; community evolution; GitHub; developer classification</t>
-        </is>
-      </c>
+          <t>Iran Obesity and Metabolic Surgery (IOMS) Cohort Study: Rationale and Design</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
@@ -2608,12 +2502,12 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Web of Science</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -2621,30 +2515,18 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Open Source Resume (OSR): A Visualization Tool for Presenting OSS Biographies of Developers</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>In order to recruit appropriate developers for software projects, it is important to have a clarified understanding on the practical experience and expertise of each candidate. However, traditional resume only shows experiences claimed by developers, and very few evidence or information regarding their actual development activities can be obtained. In this paper, we propose an approach to extract developers' practical activities from their participated open source software (OSS) projects, and generate the biographies that reflect their OSS contributions. We applied the approach on the largest code hosting service, GitHub. By investigating the resumes generated from the extracted dataset, recruiters of software projects can be given a clearer view on whether the developers' experiences fulfill the qualifications. Moreover, based on the approach, we present a web-based visualization tool, named as Open Source Resume (OSR). We believe our tool is useful to help recruiters from software development organizations to search for suitable developers, and then construct development teams in software projects based on their OSS contributions.</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Open Source Software; Mining Software Repositories; Developer Expertise; Visualization Tool</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>IC1</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>Towards fair machine learning using combinatorial methods</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
@@ -2653,12 +2535,12 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Web of Science</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -2666,30 +2548,18 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Who is attracted and why? How agile project management influences employee's attraction and commitment</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Purpose In times of market volatility and uncertainty, finding effective strategies to attract and retain individuals continues to be a challenge for organizations. Based on the psychological empowerment process (Spreitzer, 1996), this paper strives to examine if the application of agile project management could serve as such a strategy. Design/methodology/approach In two independent studies, the authors used an experiment with students as potential applicants (N = 121) and a field study with employees (N = 229) to test the predictive quality of agile project management for attracting individuals toward the organization. Findings Using structural equation modeling, the authors identified an indirect relationship between agile project management and attraction toward the organization via psychological empowerment. The authors found this relationship for potential applicants as well as employees. Furthermore, individuals high in sensation seeking are found to be more attracted toward organizations that apply agile project management than individuals low in sensation seeking. Research limitations/implications The findings contribute to the empowerment literature by establishing agile project management as a work structure that fosters feelings of psychological empowerment. Practical implications Taken together, these results suggest that agile project management can attract individuals who seek novel, complex and intense sensations. Where applicable, organizations may highlight their practice of agile project management methodologies as part of their employer brand to attract future specialists for agile projects. Originality/value This paper is the first to integrate the research streams on agile project management and attraction toward the organization using quantitative data.</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Agile project management; Psychological empowerment; Organizational attractiveness; Organizational commitment; Sensation seeking; Employer branding</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC4</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>The Personalized Learning Interaction Framework in Practice (PLIFs): Current Implementations According to Chief Learning Officers and Learning Leaders</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
@@ -2698,12 +2568,12 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -2711,30 +2581,18 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Managing the Transition to Online Freelance Platforms: Self-Directed Socialization</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Individuals increasingly turn to online freelance platforms to find flexible, remote, knowledge-based work. Yet we have only begun to understand the challenges new freelancers face with limited formal resources to orient themselves to this career. To inform design and policy to support new freelancers, we conducted a qualitative interview study on transitions to online freelance platforms with 27 freelancers working on the Upwork and Fiverr platforms. We found that new freelancers engage in self-directed socialization as they proactively seek support not directly provided by the platform or their clients. This support helps them resolve professional identity ambiguity, learn platform work self-management, build credibility, and overcome self-doubt in their new careers. Our findings suggest opportunities to support new forms of socialization and mentorship to address disparities in access to networks, resources, and knowledge needed to successfully begin an online freelance career.</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>career development; future of work; gig economy; mentorship; online freelance platforms; online freelancing; socialization</t>
-        </is>
-      </c>
+          <t>Gamification in software engineering: the mediating role of developer engagement and job satisfaction</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
@@ -2743,12 +2601,12 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -2756,30 +2614,18 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>CSM: A Code Style Model for Computing Educators</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Objectives Code style is an important aspect of text-based programming because programs written with good style are considered easier to understand and change and so improve the maintainability of the delivered software product. However teaching code style is complicated by the existence of many style guides and standards that contain inconsistent, low-level advice. The objective of the study is to support educators in helping students understand the nature of these inconsistencies by highlighting the rationale behind rules and their contextual nature.Participants Seventy members of local and national computing science education (CSE) groups contributed in the exploratory phase. Fifty-two members of the ACM SIGCSE members mailing list and the Australasian Chapter contributed in the evaluation and refinement phases. These mailing lists represent a large, global population of CSE educators.Study Methods We created, evaluated and refined an abstract code style model (CSM) comprising a Definition and eight Principles for code style. For CSM creation, we took an exploratory approach based on an examination of the existing literature on code quality and style. To evaluate the level of community endorsement for the model, we analysed quantitative and qualitative data from an international survey questionnaire. We refined the CSM based on an analysis of the qualitative survey data.Findings Analysis of the data from the survey indicated a strong level of support for the CSM. Quantitative data revealed a general agreement with the Principles, with responses for five Principles achieving a minimum of 84 percent agreement and all Principles achieving a minimum of 66 percent agreement. Qualitative data contained very few comments that voiced dissatisfaction with a basic aspect of the model. We found that barriers to developing a community-wide CSM were the strongly-held beliefs about style held by some and the abstract nature of the CSM.Conclusions The creation of an abstract set of Principles for code style is generally perceived by the community to be worthwhile and important and our approach has high levels of endorsement. A validated version of the CSM has been created.</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>computing education; text-based programming; software quality; code style; online survey</t>
-        </is>
-      </c>
+          <t>Distribution-free Bayesian analyses with the DFBA statistical package</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
@@ -2788,12 +2634,12 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Web of Science</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -2801,30 +2647,26 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Automatically Identifying the Quality of Developer Chats for Post Hoc Use</t>
+          <t>The Evaluation of Founder Failure and Success by Hiring Firms: A Field Experiment</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Software engineers are crowdsourcing answers to their everyday challenges on Q&amp;amp;A forums (e.g., Stack Overflow) and more recently in public chat communities such as Slack, IRC, and Gitter. Many software-related chat conversations contain valuable expert knowledge that is useful for both mining to improve programming support tools and for readers who did not participate in the original chat conversations. However, most chat platforms and communities do not contain built-in quality indicators (e.g., accepted answers, vote counts). Therefore, it is difficult to identify conversations that contain useful information for mining or reading, i.e., conversations of post hoc quality. In this article, we investigate automatically detecting developer conversations of post hoc quality from public chat channels. We first describe an analysis of 400 developer conversations that indicate potential characteristics of post hoc quality, followed by a machine learning-based approach for automatically identifying conversations of post hoc quality. Our evaluation of 2,000 annotated Slack conversations in four programming communities (python, clojure, elm, and racket) indicates that our approach can achieve precision of 0.82, recall of 0.90, F-measure of 0.86, and MCC of 0.57. To our knowledge, this is the first automated technique for detecting developer conversations of post hoc quality.</t>
+          <t>Organizations tout the importance of innovation and entrepreneurship. Yet, when hiring it remains unclear how they evaluate entrepreneurial human capital-namely, job candidates with founder experience. How hiring firms evaluate this experience-and especially how this evaluation varies by entrepreneurial success and failure-reveals insights into the structures and processes within organizations. Organizations research points to two perspectives related to the evaluation of founder experience: Former founders may be advantaged, due to founder experience signaling high-quality capabilities and human capital, or disadvantaged, due to concerns related to fit and commitment. To identify the dominant class of mechanisms driving the evaluation of founder experience, it is important to consider how these evaluations differ, depending on whether the founder's venture failed or succeeded. To isolate demand-side mechanisms and hold supply-side factors constant, we conducted a field experiment. We sent applications varying the candidate's founder experience to 2,400 software engineering positions in the United States at random. We find that former founders received 43% fewer callbacks than nonfounders and that this difference is driven by older hiring firms. Further, this founder penalty is greatest for former successful founders, who received 33% fewer callbacks than former failed founders. Our results highlight that mechanisms related to concerns about fit and commitment, rather than information asymmetry about quality, are most influential when hiring firms evaluate former founders in our context.</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Online software developer chats; quality of social content</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>careers; entrepreneurship; evaluations; failure; experiment; founders; hiring; labor markets</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC3; IC4; IC5</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
@@ -2833,12 +2675,12 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Web of Science</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2846,30 +2688,26 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>"A Blocklist is a Boundary": Tensions between Community Protection and Mutual Aid on Federated Social Networks</t>
+          <t>ACHIEVING JOB PERFORMANCE FROM EMPOWERMENT THROUGH THE MEDIATION OF EMPLOYEE ENGAGEMENT: AN EMPIRICAL STUDY</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>The Fediverse (the network encompassing Mastodon, Pleroma, Lemmy, etc.) provides a decentralized alternative to traditional social media platforms, making it both an important refuge for marginalized users and a platform which is well-suited for conducting mutual aid. One emergent type of moderation action for maintaining mutual aid spaces on the Fediverse is the use of community boundary blocklists, which we define as shared lists of Fediverse servers intended to be imported as a common blocklist. However, the use of community boundary blocklists has incited conflict on the Fediverse, with many users left cut off from their communities and sources of support due to actions outside of their control. Using an approach rooted in constructivist grounded theory, we interviewed nine Fediverse users, including a mix of community boundary blocklist curators, server staff, and regular users, to determine key tensions between community moderation and mutual aid practices. From our interviews, we identify the novel perspective of community stewardship as an act of mutual aid. We extend existing collective action and mutual aid frameworks to understand why this perspective conflicts with more typical mutual aid activities. We also observe how federation as a protocol encodes a negative form of consent, allowing users to interact by default and individuals to consent for their entire instance, leading to consent violations. From these insights, we develop a series of community-sourced suggestions for Fediverse platform designers, blocklist curators, and community staff to help address these conflicts and protect marginalized users.</t>
+          <t>In present scenario, business organization understood the importance of sophisticated employee behavior for the development of overall job performance. It is important for an organization to perform effectively for that it enhances their employee's job performance. Many study supports that an empowered employee recognizes and attaches himself or herself with the wider extent of organizational objectives. An engaged employee has more ownership and able to contribute towards his/her own growth and overall productivity. Boston focuses on implementing feedback given by employees with immediate effect and has 43% employees who are highly engaged. Facebook has a culture of contribution and each employee is recognized for his contribution to the overall goal of the company "to make the world more open and connected ". This policy of contributing culture is communicated to all the candidates during recruitment process. That is why Facebook is not only known for being one of the most popular social networking platforms but for its highly engaging culture as well. Under this study, the focus is to understand the relationship between employee empowerment and job performance. The study also tries to explore empirically the mediating effect of employee engagement in this regard. It was conducted on IT sector in Delhi NCR region with a sample size of 182 employees. The finding of the study reflects that engagement has its mediation effect on job performance with respect to employee empowerment.</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>acm proceedings; blocklists; federated networks; fediverse; mastodon; mutual aid; online communities</t>
+          <t>Employee engagement; Employee empowerment; Job Performance; Mediation; Regression</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
@@ -2883,7 +2721,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -2891,17 +2729,17 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Decision Support Model for Selecting the Optimal Blockchain Oracle Platform: An Evaluation of Key Factors</t>
+          <t>Transformative and Troublesome? Students' and Professional Programmers' Perspectives on Difficult Concepts in Programming</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Smart contract-based applications are executed in a blockchain environment, and they cannot directly access data from external systems, which is required for the service provision of these applications. Instead, smart contracts use agents known as blockchain oracles to collect and provide data feeds to the contracts. The functionality and compatibility with smart contract applications need to be considered when selecting the best-fit oracle platform. As the number of oracle alternatives and their features increases, the decision-making process becomes increasingly complex. Selecting the wrong or sub-optimal oracle is costly and may lead to severe security risks. This article provides a decision support model for the oracle selection problem. The model supports smart contract decision-makers in selecting a secure, cost-effective, and feasible oracle platform for their applications. We interviewed oracle co-founders and smart contracts experts to refine and validate the decision model. Two real-world smart contract application case studies were used to evaluate the model. Our model prioritises and suggests more than one possible oracle platform based on the developer’s required criteria, security assessment and cost analysis. Moreover, this guided decision model serves to reveal issues that may go unnoticed if done haphazardly, reduce decision-making efforts and provide a cost-effective solution.</t>
+          <t>Programming skills are an increasingly desirable asset across disciplines; however, learning to program continues to be difficult for many students. To improve pedagogy, we need to better understand the concepts that students find difficult and which have the biggest impact on their learning. Threshold-concept theory provides a potential lens on student learning, focusing on concepts that are troublesome and transformative. However, there is still a lack of consensus as to what the most relevant threshold concepts in programming are. The challenges involved are related to concept granularity and to evidencing some of the properties expected of threshold concepts. In this article, we report on a qualitative study aiming to address some of these concerns. The study involved focus groups with undergraduate students of different-year groups as well as professional software developers so as to gain insights into how perspectives on concepts change over time. Four concepts emerged from the data, where the majority of participants agreed on their troublesome nature—including abstract classes and data structures. Some of these concepts are considered transformative, too, but the evidence base is weaker. However, even though these concepts may not be considered transformative in the “big” sense of threshold concept theory, we argue the “soft” transformative effect of such concepts means they can provide important guidance for pedagogy and the design of programming courses. Further analysis of the data identified additional concepts that may hinder rather than help the learning of these threshold concepts, which we have called “accidental complexities.” We conclude the article with a critique of the use of threshold concepts as a lens for studying students’ learning of programming.</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>blockchain oracle; smart contracts; technical debt; MCDM</t>
+          <t>Threshold concepts; accidental complexities; computer science curriculum; focus groups; learning programming</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2924,7 +2762,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2932,17 +2770,17 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>An Empirical Study on the Suitability of Test-based Patch Acceptance Criteria</t>
+          <t>Can GPT-4 Replicate Empirical Software Engineering Research?</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>In this article, we empirically study the suitability of tests as acceptance criteria for automated program fixes, by checking patches produced by automated repair tools using a bug-finding tool, as opposed to previous works that used tests or manual inspections. We develop a number of experiments in which faulty programs from IntroClass, a known benchmark for program repair techniques, are fed to the program repair tools GenProg, Angelix, AutoFix, and Nopol, using test suites of varying quality, including those accompanying the benchmark. We then check the produced patches against formal specifications using a bug-finding tool. Our results show that, in the studied scenarios, automated program repair tools are significantly more likely to accept a spurious program fix than producing an actual one. Using bounded-exhaustive suites larger than the originally given ones (with about 100 and 1,000 tests) we verify that overfitting is reduced but (a) few new correct repairs are generated and (b) some tools see their performance reduced by the larger suites and fewer correct repairs are produced. Finally, by comparing with previous work, we show that overfitting is underestimated in semantics-based tools and that patches not discarded using held-out tests may be discarded using a bug-finding tool.</t>
+          <t>Empirical software engineering research on production systems has brought forth a better understanding of the software engineering process for practitioners and researchers alike. However, only a small subset of production systems is studied, limiting the impact of this research. While software engineering practitioners could benefit from replicating research on their own data, this poses its own set of challenges, since performing replications requires a deep understanding of research methodologies and subtle nuances in software engineering data. Given that large language models (LLMs), such as GPT-4, show promise in tackling both software engineering- and science-related tasks, these models could help replicate and thus democratize empirical software engineering research.In this paper, we examine GPT-4’s abilities to perform replications of empirical software engineering research on new data. We specifically study their ability to surface assumptions made in empirical software engineering research methodologies, as well as their ability to plan and generate code for analysis pipelines on seven empirical software engineering papers. We perform a user study with 14 participants with software engineering research expertise, who evaluate GPT-4-generated assumptions and analysis plans (i.e., a list of module specifications) from the papers. We find that GPT-4 is able to surface correct assumptions, but struggles to generate ones that apply common knowledge about software engineering data. In a manual analysis of the generated code, we find that the GPT-4-generated code contains correct high-level logic, given a subset of the methodology. However, the code contains many small implementation-level errors, reflecting a lack of software engineering knowledge. Our findings have implications for leveraging LLMs for software engineering research as well as practitioner data scientists in software teams.</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>automatic program repair; formal specifications; testing; oracle</t>
+          <t>Large language models; study replication; empirical software engineering</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2965,7 +2803,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -2973,17 +2811,17 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Cat and Mouse Game: Patching Bureaucratic Work Relations by Patching Technologies</t>
+          <t>Towards Automated Accessibility Report Generation for Mobile Apps</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>This article uses findings from a field study of the world's largest guaranteed employment scheme (NREGA) in India to understand how digital technology mediates work relations and power dynamics within a bureaucracy. In this initiative, upper-level bureaucrats in the south Indian state of Andhra Pradesh built a digital network to remove local discretion at the "last mile" of an implementation of NREGA. I show how digital infrastructure affords actors at both the first and last mile opportunities to modify software to control as well as subvert certain practices. This article refers to this dialectic phenomenon as "governance by patching" and defines it as a socio-technical instantiation of a top-down process that focuses on small changes, iterative, and political process for positive change. Governance by patching is, therefore, neither a purely technical process nor an exclusively administrative one. Rather, it refers to the ability to fix unanticipated problems that arise in the implementation of governance programs by altering the socio-technical systems. The struggle for power continues, but on the new digital terrain.</t>
+          <t>Many apps have basic accessibility issues, like missing labels or low contrast. To supplement manual testing, automated tools can help developers and QA testers find basic accessibility issues, but they can be laborious to use or require writing dedicated tests. To motivate our work, we interviewed eight accessibility QA professionals at a large technology company. From these interviews, we synthesized three design goals for accessibility report generation systems. Motivated by these goals, we developed a system to generate whole app accessibility reports by combining varied data collection methods (e.g., app crawling, manual recording) with an existing accessibility scanner. Many such scanners are based on single-screen scanning, and a key problem in whole app accessibility reporting is to effectively de-duplicate and summarize issues collected across an app. To this end, we developed a screen grouping model with 96.9% accuracy (88.8% F1-score) and UI element matching heuristics with 97% accuracy (98.2% F1-score). We combine these technologies in a system to report and summarize unique issues across an app, and enable a unique pixel-based ignore feature to help engineers and testers better manage reported issues across their app’s lifetime. We conducted a user study where 19 accessibility engineers and testers used multiple tools to create lists of prioritized issues in the context of an accessibility audit. Our system helped them create lists they were more satisfied with while addressing key limitations of current accessibility scanning tools.</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>bureaucracy; governance; ictd; infrastructures; last-mile; nrega; patching</t>
+          <t>UI understanding; app crawling; accessibility</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -3006,7 +2844,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>293</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -3014,17 +2852,17 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>DesignManager: An Agent-Powered Copilot for Designers to Integrate AI Design Tools into Creative Workflows</t>
+          <t>"Innovative Technologies or Invasive Technologies?": Exploring Design Challenges of Privacy Protection With Smart Home in Jordan</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Creative design is an inherently complex and iterative process characterized by continuous exploration, evaluation, and refinement. While recent advances in generative AI have demonstrated remarkable potential in supporting specific design tasks, there remains a critical gap in understanding how these technologies can enhance the holistic design process rather than just isolated stages. This paper introduces DesignManager, a novel AI-powered design support system that aims to transform how designers collaborate with AI throughout their creative workflow. Through a formative study examining designers' current practices with generative AI, we identified key challenges and opportunities in integrating AI into the creative design process. Based on these insights, we developed DesignManager as an interactive copilot system that provides node-based visualization of design evolution, enabling designers to track, modify, and branch their design processes while maintaining meaningful dialogue-based collaboration. The system offers two collaboration modes: DesignManager-guiding and Designer-guiding. Designers can engage in conversational interactions with the DesignManager to obtain design inspiration and tool recommendations, and proactively advance the design progress. The system employs an agent framework to manage decoupled contextual information emerged during the design process, facilitating deep understanding of designers' needs and providing context-aware assistance. Our technical evaluation validated the effectiveness of context decoupling and the use of agent framework, while the open-ended user study with experts demonstrated that DesignManager successfully supports intuitive intention expression, flexible process control, and deeper creative articulation. This work contributes to the understanding of how AI can evolve from task-specific tools to collaborative partners in creative design processes.</t>
+          <t>The growing adoption of smart devices has fuelled privacy concerns, and prior research has highlighted the privacy of bystanders: individuals who are subjected to the smart device use of others. Most of this research has focused on households in Western contexts (i.e., Europe and North America), but few studies have explored the design challenges of protecting bystanders, and even fewer have explored these in Muslim Arab Middle Eastern settings, such as Jordan.We conduct 44 interviews with users (i.e., families, domestic workers), local and international business leaders, and smart device designers to explore design challenges for privacy protection in the Jordanian context. Our analysis highlights the importance of considering contextual influences and power dynamics, localization and design guidelines, innovative technologies, awareness to design, and regulation. This paper concludes with recommendations for technical, social, business, and legal interventions to improve data protection design of smart devices in Jordan.</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>design copilot; agent; designer-AI collaboration; creative design</t>
+          <t>bystander; design; jordan; privacy; protection; security; smart device; smart home</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -3047,7 +2885,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -3055,15 +2893,19 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>HLB: Toward Load-Aware Load Balancing</t>
+          <t>On the Role of Structural Holes in Requirements Identification: An Exploratory Study on Open-Source Software Development</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>The purpose of network load balancers is to optimize quality of service to the users of a set of servers– basically, to improve response times and to reducing computing resources– by properly distributing workloads. This paper proposes a distributed, application-agnostic, Hybrid Load Balancer (HLB) that– without explicit monitoring or signaling– infers server occupancies and processing speeds, which allows making optimised workload placement decisions. This approach is evaluated both through simulations and extensive experiments, including synthetic workloads and Wikipedia replays on a real-world testbed. Results show significant performance gains, in terms of both response time and system utilisation, when compared to existing load-balancing algorithms.</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr"/>
+          <t>Requirements identification is a human-centric activity that involves interaction among multiple stakeholders. Traditional requirements engineering (RE) techniques addressing stakeholders’ social interaction are mainly part of a centralized process intertwined with a specific phase of software development. However, in open-source software (OSS) development, stakeholders’ social interactions are often decentralized, iterative, and dynamic. Little is known about new requirements identification in OSS and the stakeholders’ organizational arrangements supporting such an activity. In this article, we investigate the theory of structural hole from the context of contributing new requirements in OSS projects. Structural hole theory suggests that stakeholders positioned in the structural holes in their social network are able to produce new ideas. In this study, we find that structural hole positions emerge in stakeholders’ social network and these positions are positively related to contributing a higher number of new requirements. We find that along with structural hole positions, stakeholders’ role is also an important part in identifying new requirements. We further observe that structural hole positions evolve over time, thereby identifying requirements to realize enriched features. Our work advances the fundamental understanding of the RE process in a decentralized environment and opens avenues for improved techniques supporting this process.</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Requirements identification; brokerage; open-source requirements engineering; social capital; social information foraging theory; stakeholders’ social network; structural hole</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3084,7 +2926,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -3092,17 +2934,17 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>A Scoping Review of Informed Consent Practices in Human–Computer Interaction Research</t>
+          <t>An Empirical Study of Self-Admitted Technical Debt in Machine Learning Software</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Obtaining informed consent is a fundamental ethical requirement in research involving human subjects, designed to ensure autonomy, respect, and the protection of participants. However, new technologies and research methodologies in Human–Computer Interaction (HCI) present unique challenges in maintaining ethical standards and require a deeper understanding of how consent practices are implemented. This scoping review provides a detailed examination of the frameworks, methodologies, and practices for obtaining informed consent in HCI. We present recognized universal principles while also discussing the ethical guidelines, and legal frameworks that underpin consent processes. Furthermore, we analyze the practices of disclosure, screening, consenting, and confirmation to assess how researchers ensure voluntary participation. The review addresses key criticisms and challenges identified in the literature, suggesting improvements and exploring alternative approaches. By offering comprehensive insights into the complexities of informed consent, we underscore the ongoing need for ethical awareness and continuous refinement of ethical conduct in HCI.</t>
+          <t>The emergence of open-source ML libraries such as TensorFlow and Google Auto ML has enabled developers to harness state-of-the-art ML algorithms with minimal overhead. However, during this accelerated ML development process, said developers may often make sub-optimal design and implementation decisions, leading to the introduction of technical debt that, if not addressed promptly, can significantly impact on the quality of ML-based software. Developers frequently acknowledge these sub-optimal design and development choices through code comments written during development. These comments, which often highlight areas requiring additional work or refinement in the future are known as self-admitted technical debt (SATD). While prior research has demonstrated that SATD can serve as a reliable indicator of technical debt and has extensively studied SATD in traditional (non-ML) software, little attention has been given to this issue in the context of ML. This paper aims to investigate the occurrence of SATD in ML code by analyzing 318 open-source ML projects across five domains, along with 318 non-ML projects. We detected SATD in source code comments in various snapshots of the studied projects, conducted a manual analysis of a sample of the identified SATD to comprehend the nature of technical debt in the ML code, and performed a survival analysis of the SATD to understand the evolution dynamics of such debts. Our analyses yielded the following observations: (i) Machine learning projects have a median percentage of SATD that is twice that of non-machine learning projects. (ii) ML pipeline stages for data preprocessing and model generation logic are more susceptible to debt than model validation and deployment stages. (iii) SATDs appear in ML projects earlier in the development process compared to non-ML projects. (iv) Long-lasting SATDs are typically introduced during extensive code changes that span multiple files, which exhibit low complexity.Our research contributes to the understanding of technical debt in an ML context and underscores the need for targeted debt management strategies. This contribution is particularly relevant for developers and stakeholders in ML projects by aiding them in identifying and addressing technical debt proactively and paving the way for future research in developing automated tools and methodologies for managing SATD in an ML environment.</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Ethical research; informed consent; consent process; consent forms; literature review</t>
+          <t>Self-Admitted Technical Debt; Machine Learning; Survival Analysis; Mining Software Repositories; ML Pipeline; Empirical Software Engineering</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -3125,7 +2967,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>413</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -3133,17 +2975,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>COSTELLO: Contrastive Testing for Embedding-Based Large Language Model as a Service Embeddings</t>
+          <t>A Survey of AIOps in the Era of Large Language Models</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Large language models have gained significant popularity and are often provided as a service (i.e., LLMaaS). Companies like OpenAI and Google provide online APIs of LLMs to allow downstream users to create innovative applications. Despite its popularity, LLM safety and quality assurance is a well-recognized concern in the real world, requiring extra efforts for testing these LLMs. Unfortunately, while end-to-end services like ChatGPT have garnered rising attention in terms of testing, the LLMaaS embeddings have comparatively received less scrutiny. We state the importance of testing and uncovering problematic individual embeddings without considering downstream applications. The abstraction and non-interpretability of embedded vectors, combined with the black-box inaccessibility of LLMaaS, make testing a challenging puzzle. This paper proposes Costello, a black-box approach to reveal potential defects in abstract embedding vectors from LLMaaS by contrastive testing. Our intuition is that high-quality LLMs can adequately capture the semantic relationships of the input texts and properly represent their relationships in the high-dimensional space. For the given interface of LLMaaS and seed inputs, Costello can automatically generate test suites and output words with potential problematic embeddings. The idea is to synthesize contrastive samples with guidance, including positive and negative samples, by mutating seed inputs. Our synthesis guide will leverage task-specific properties to control the mutation procedure and generate samples with known partial relationships in the high-dimensional space. Thus, we can compare the expected relationship (oracle) and embedding distance (output of LLMs) to locate potential buggy cases. We evaluate Costello on 42 open-source (encoder-based) language models and two real-world commercial LLMaaS. Experimental results show that Costello can effectively detect semantic violations, where more than 62% of violations on average result in erroneous behaviors (e.g., unfairness) of downstream applications.</t>
+          <t>As large language models (LLMs) grow increasingly sophisticated and pervasive, their application to various Artificial Intelligence for IT Operations (AIOps) tasks has garnered significant attention. However, a comprehensive understanding of the impact, potential, and limitations of LLMs in AIOps remains in its infancy. To address this gap, we conducted a detailed survey of LLM4AIOps, focusing on how LLMs can optimize processes and improve outcomes in this domain. We analyzed 183 research articles published between January 2020 and December 2024 to answer four key research questions (RQs). In RQ1, we examine the diverse failure data sources utilized, including advanced LLM-based processing techniques for legacy data and the incorporation of new data sources enabled by LLMs. RQ2 explores the evolution of AIOps tasks, highlighting the emergence of novel tasks and the publication trends across these tasks. RQ3 investigates the various LLM-based methods applied to address AIOps challenges. Finally, RQ4 reviews evaluation methodologies tailored to assess LLM-integrated AIOps approaches. Based on our findings, we discuss the state-of-the-art advancements and trends, identify gaps in existing research, and propose promising directions for future exploration.</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Software and its engineering → Software testing and debugging; Contrastive Testing; LLMaaS; Embeddings</t>
+          <t>Large language model; AIOps; metrics; logs; time series; incident report; failure perception; anomaly detection; root cause analysis; assisted remediation</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -3166,7 +3008,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>468</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -3174,26 +3016,26 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Social Sourcing: Incorporating Social Networks Into Crowdsourcing Contest Design</t>
+          <t>A Stack-Propagation Framework for Low-Resource Personalized Dialogue Generation</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>In a crowdsourcing contest, a principal holding a task posts it to a crowd. People in the crowd then compete with each other to win the rewards. Although in real life, a crowd is usually networked and people influence each other via social ties, existing crowdsourcing contest theories do not aim to answer how interpersonal relationships influence people’s incentives and behaviors and thereby affect the crowdsourcing performance. In this work, we novelly take people’s social ties as a key factor in the modeling and designing of agents’ incentives in crowdsourcing contests. We establish two contest mechanisms by which the principal can impel the agents to invite their neighbors to contribute to the task. The first mechanism has a symmetric Bayesian Nash equilibrium, and it is very simple for agents to play and easy for the principal to predict the contest performance. The second mechanism has an asymmetric Bayesian Nash equilibrium, and agents’ behaviors in equilibrium show a vast diversity which is strongly related to their social relations. The Bayesian Nash equilibrium analysis of these new mechanisms reveals that, besides agents’ intrinsic abilities, the social relations among them also play a central role in decision-making. Moreover, we design an effective algorithm to automatically compute the Bayesian Nash equilibrium of the invitation crowdsourcing contest and further adapt it to a large graph dataset. Both theoretical and empirical results show that the new invitation crowdsourcing contests can substantially enlarge the number of participants, whereby the principal can obtain significantly better solutions without a large advertisement expenditure.</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>IC2; IC4</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>With the resurgent interest in building open-domain dialogue systems, the dialogue generation task has attracted increasing attention over the past few years. This task is usually formulated as a conditional generation problem, which aims to generate a natural and meaningful response given dialogue contexts and specific constraints, such as persona. And maintaining a consistent persona is essential for the dialogue systems to gain trust from the users. Although tremendous advancements have been brought, traditional persona-based dialogue models are typically trained by leveraging a large number of persona-dense dialogue examples. Yet, such persona-dense training data are expensive to obtain, leading to a limited scale. This work presents a novel approach to learning from limited training examples by regarding consistency understanding as a regularization of response generation. To this end, we propose a novel stack-propagation framework for learning a generation and understanding pipeline. Specifically, the framework stacks a Transformer encoder and two Transformer decoders, where the first decoder models response generation and the second serves as a regularizer and jointly models response generation and consistency understanding. The proposed framework can benefit from the stacked encoder and decoders to learn from much smaller personalized dialogue data while maintaining competitive performance. Under different low-resource settings, subjective and objective evaluations prove that the stack-propagation framework outperforms strong baselines in response quality and persona consistency and largely overcomes the shortcomings of traditional models that rely heavily on the persona-dense dialogue data.</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Open-domain dialogue; personalized dialogue generation; stack-propagation; low-resource</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
@@ -3207,7 +3049,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>477</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -3215,17 +3057,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Fixing Faults in C and Java Source Code: Abbreviated vs. Full-Word Identifier Names</t>
+          <t>Psychometrics in Behavioral Software Engineering: A Methodological Introduction with Guidelines</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>We carried out a family of controlled experiments to investigate whether the use of abbreviated identifier names, with respect to full-word identifier names, affects fault fixing in C and Java source code. This family consists of an original (or baseline) controlled experiment and three replications. We involved 100 participants with different backgrounds and experiences in total. Overall results suggested that there is no difference in terms of effort, effectiveness, and efficiency to fix faults, when source code contains either only abbreviated or only full-word identifier names. We also conducted a qualitative study to understand the values, beliefs, and assumptions that inform and shape fault fixing when identifier names are either abbreviated or full-word. We involved in this qualitative study six professional developers with 1--3 years of work experience. A number of insights emerged from this qualitative study and can be considered a useful complement to the quantitative results from our family of experiments. One of the most interesting insights is that developers, when working on source code with abbreviated identifier names, adopt a more methodical approach to identify and fix faults by extending their focus point and only in a few cases do they expand abbreviated identifiers.</t>
+          <t>A meaningful and deep understanding of the human aspects of software engineering (SE) requires psychological constructs to be considered. Psychology theory can facilitate the systematic and sound development as well as the adoption of instruments (e.g., psychological tests, questionnaires) to assess these constructs. In particular, to ensure high quality, the psychometric properties of instruments need evaluation. In this article, we provide an introduction to psychometric theory for the evaluation of measurement instruments for SE researchers. We present guidelines that enable using existing instruments and developing new ones adequately. We conducted a comprehensive review of the psychology literature framed by the Standards for Educational and Psychological Testing. We detail activities used when operationalizing new psychological constructs, such as item pooling, item review, pilot testing, item analysis, factor analysis, statistical property of items, reliability, validity, and fairness in testing and test bias. We provide an openly available example of a psychometric evaluation based on our guideline. We hope to encourage a culture change in SE research towards the adoption of established methods from psychology. To improve the quality of behavioral research in SE, studies focusing on introducing, validating, and then using psychometric instruments need to be more common.</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>source code identifiers; software testing; replications; qualitative investigation; maintenance; family of experiments; ethnography study; Controlled experiments</t>
+          <t>Empirical software engineering; psychology; behavioral software engineering; methodology; questionnaire design</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -3248,7 +3090,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -3256,17 +3098,17 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>An In-Depth Analysis of Occasional and Recurring Collaborations in Online Music Co-creation</t>
+          <t>Market-aware Long-term Job Skill Recommendation with Explainable Deep Reinforcement Learning</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>The success of online creative communities depends on the will of participants to create and derive content in a collaborative environment. Despite their growing popularity, the factors that lead to remixing existing content in online creative communities are not entirely understood. In this article, we focus on overdubbing, a dyadic collaboration in which one author mixes one new track with an audio recording previously uploaded by another. We study musicians who collaborate regularly, frequently overdubbing each other's songs. Building on frequent pattern–mining techniques, we develop an approach to seek instances of such recurring collaborations in the Songtree community. We identify 43 instances involving two or three members with a similar reputation in the community. Our findings highlight common and different remix factors in occasional and recurring collaborations. Specifically, fresh and less mature songs are generally overdubbed more. Exchanging messages and invitations to collaborate are significant factors only for songs generated through recurring collaborations, whereas author reputation (ranking) and applying metadata tags to songs have a positive effect only in occasional collaborations.</t>
+          <t>Continuously learning new skills is essential for talents to gain a competitive advantage in the labor market. Despite extensive efforts on relevance- or preference-based skill recommendations, little attention has been given to the practical effects of job skills in the market. To bridge this gap, we propose an explainable personalized skill learning recommendation system that considers the long-term learning benefits and costs. Specifically, we model skill learning utilities based on salary and learning cost associated with job positions and propose a multi-objective deep reinforcement learning framework to model and maximize long-term utilities. Furthermore, we propose a Self-explaining Skill Recommendation Deep Q-network (SeSRDQN) that captures and prototypes prevalent skill sets in the market into representative exemplars for decision-making. SeSRDQN quantitatively decomposes the talent’s long-term learning utility into contributions from each exemplar, offering a comprehensive and multi-factorial explanation across various skill learning options. To tackle the combinatorial complexity of the skill space, we develop an MCTS-based optimization-decoding iterative training procedure for explanation fidelity and human understandability. In this way, talents will receive a tailored roadmap of essential skills, complemented by exemplar-based explanations, to effectively plan their careers. Extensive experiments on a real-world dataset validate the effectiveness and explainability of our approach.</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Remix factors; reuse antecedents; online communities; creative work; songwriting; Songtree</t>
+          <t>Skill Recommendation; Explainable Recommendation; Reinforcement Learning; Deep Q Network; Case-based Reasoning; Prototype Learning; Self-Interpretable Neural Network</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -3289,7 +3131,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>521</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -3297,17 +3139,17 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Back to the Roots: Assessing Mining Techniques for Java Vulnerability-Contributing Commits</t>
+          <t>A Method to Analyze Multiple Social Identities in Twitter Bios</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Context: Vulnerability-contributing commits (VCCs) are code changes that introduce vulnerabilities. Mining historical VCCs relies on SZZ-based algorithms that trace from known vulnerability-fixing commits. Objective: Although these techniques have been used, e.g., to train just-in-time vulnerability predictors, they lack systematic benchmarking to evaluate their precision, recall, and error sources. Method: We empirically assessed 12 VCC mining techniques in Java repositories using two benchmark datasets (one from the literature and one newly curated). We also explored combinations of techniques, through intersections, voting schemes, and machine learning, to improve performance. Results: Individual techniques achieved at most 0.60 precision but up to 0.89 recall. The precision rose to 0.75 when the outputs were combined with the logical AND, at the expense of recall. Machine learning ensembles reached 0.80 precision with a better precision–recall balance. Performance varied significantly by dataset. Analyzing “fixing commits” showed that certain fix types (e.g., filtering or sanitization) affect retrieval accuracy, and failure patterns highlighted weaknesses when fixes involve external data handling. Conclusion: Such results help software security researchers select the most suitable mining technique for their studies and understand new ways to design more accurate solutions.</t>
+          <t>Twitter users signal social identity in their profile descriptions, or bios, in a number of important but complex ways that are not well-captured by existing characterizations of how identity is expressed in language. Better ways of defining and measuring these expressions may therefore be useful both in understanding how social identity is expressed in text, and how the self is presented on Twitter. To this end, the present work makes three contributions. First, using qualitative methods, we identify and define the concept of a personal identifier, which is more representative of the ways in which identity is signaled in Twitter bios. Second, we propose a method to extract all personal identifiers expressed in a given bio. Finally, we present a series of validation analyses that explore the strengths and limitations of our proposed method. Our work opens up exciting new opportunities at the intersection between the social psychological study of social identity and the study of how we compose the self through markers of identity on Twitter and in social media more generally.</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Mining Software Repositories; Software Vulnerability; Software Analytics; Machine Learning</t>
+          <t>computational social science; self-presentation; social identity; twitter</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -3330,7 +3172,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>567</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -3338,17 +3180,17 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Arising of Informal Women's Learn-to-code Communities: Activity Systems as Incubators</t>
+          <t>Understanding is a Two-Way Street: User-Initiated Repair on Agent Responses and Hearing in Conversational Interfaces</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Female-focused, grassroots communities purporting to help women learn to code are popping up in a variety of settings, indicating the motivation on the part of the participants to evade male-dominated settings while learning. However, little is known about how these groups function as an activity system. With current technology enabling the forming of virtual communities and the meteoric rise in use of the Salesforce CRM (customer relationship management) platform, a group of women have formed a coaching and learning community designed to help women move from Salesforce administrators to software developers through learning to code. We used activity systems analysis (ASA) to investigate this real-world instance of the larger phenomenon using an ethnographic approach. We used ASA to organize and make sense of the data by first creating a table listing the points on the activity system triangle (subject, rules, object, etc.) and filling in the points of the triangle based on the design of the coaching and learning group as described by participants; this gave us a high-level view of the activity system. To understand the subjects’ point of view of the system, we then created a new column in the table to fill in themes that emerged from our qualitative data analysis organized by dimension of the activity system. This process enabled us to capture the activity and the voices of participants as well as tensions that had emerged in the system. Findings show a range of outcomes, from participants crediting the group as a kickstart to the journey to successfully landing a job as a developer to members stalling in their progress after involvement. Results also show that purposeful tensions of welcoming novice questions and offering unsolicited verbal encouragement built into the activity system create a welcoming, safe environment for women learning to code.</t>
+          <t>Although methods for repairing prior turns in natural conversation are critical for enabling mutual understanding, or successful communication, these methods are seldom built into conversational user interfaces systematically. Chatbots and voice assistants tend to ask users to paraphrase what they said if it was not understood, but users cannot do the same if they encounter trouble in understanding what the agent said. Understanding is a one-way street in most (intent-based) conversation-like interfaces. An exception to this is Moore and Arar (2019), who demonstrate nine types of user-initiated repair on agent responses that are common in natural conversation and who have shown that users will employ these repair features correctly in text-based interfaces if taught. In this small-scale study, we test these user-initiated repairs (in second position) in a voice-based interface. With understanding-oriented repairs, we found that participants employed them much the same way in text and voice. In addition, we examine some hearing- and speaking-oriented repairs that emerged from the use of our novel multi-modal interface. We found that participants used them to manage troubles specific to the voice modality. Analysis of user logs and transcripts suggests that user-initiated repair features are valuable components of conversational interfaces.</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Informal learning; activity system; software development; women; workplace</t>
+          <t>chatbots; conversational agents; conversational ai; conversational user interfaces; conversational ux; user-initiated repair</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -3357,11 +3199,7 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
@@ -3375,7 +3213,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -3383,17 +3221,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Designing Mid-Air Haptic Gesture Controlled User Interfaces for Cars</t>
+          <t>A Survey of Asynchronous Programming Using Coroutines in the Internet of Things and Embedded Systems</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>We present advancements in the design and development of in-vehicle infotainment systems that utilize gesture input and ultrasonic mid-air haptic feedback. Such systems employ state-of-the-art hand tracking technology and novel haptic feedback technology and promise to reduce driver distraction while performing a secondary task therefore cutting the risk of road accidents. In this paper, we document design process considerations during the development of a mid-air haptic gesture-enabled user interface for human-vehicle-interactions. This includes an online survey, business development insights, background research, and an agile framework component with three prototype iterations and user-testing on a simplified driving simulator. We report on the reasoning that led to the convergence of the chosen gesture-input and haptic-feedback sets used in the final prototype, discuss the lessons learned, and give hints and tips that act as design guidelines for future research and development of this technology in cars.</t>
+          <t>Many Internet of Things and embedded projects are event driven, and therefore require asynchronous and concurrent programming. Current proposals for C++20 suggest that coroutines will have native language support. It is timely to survey the current use of coroutines in embedded systems development. This article investigates existing research which uses or describes coroutines on resource-constrained platforms. The existing research is analysed with regard to: software platform, hardware platform, and capacity; use cases and intended benefits; and the application programming interface design used for coroutines. A systematic mapping study was performed, to select studies published between 2007 and 2018 which contained original research into the application of coroutines on resource-constrained platforms. An initial set of 566 candidate papers, collated from on-line databases, were reduced to only 35 after filters were applied, revealing the following taxonomy. The C 8 C++ programming languages were used by 22 studies out of 35. As regards hardware, 16 studies used 8- or 16-bit processors while 13 used 32-bit processors. The four most common use cases were concurrency (17 papers), network communication (15), sensor readings (9), and data flow (7). The leading intended benefits were code style and simplicity (12 papers), scheduling (9), and efficiency (8). A wide variety of techniques have been used to implement coroutines, including native macros, additional tool chain steps, new language features, and non-portable assembly language. We conclude that there is widespread demand for coroutines on resource-constrained devices. Our findings suggest that there is significant demand for a formalised, stable, well-supported implementation of coroutines in C++, designed with consideration of the special needs of resource-constrained devices, and further that such an implementation would bring benefits specific to such devices.</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>user experience design; ultrasound haptics; in-vehicle controls; human-machine interface; gesture interaction</t>
+          <t>scheduling; resource-constrained; direct style; asynchronous; Embedded</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -3416,7 +3254,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -3424,25 +3262,25 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Automatic API Usage Scenario Documentation from Technical Q&amp;amp;A Sites</t>
+          <t>Recruitment Promotion via Twitter: A Network-centric Approach of Analyzing Community Engagement Using Social Identity</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>The online technical Q&amp;amp;A site Stack Overflow (SO) is popular among developers to support their coding and diverse development needs. To address shortcomings in API official documentation resources, several research works have thus focused on augmenting official API documentation with insights (e.g., code examples) from SO. The techniques propose to add code examples/insights about APIs into its official documentation. Recently, surveys of software developers find that developers in SO consider the combination of code examples and reviews about APIs as a form of API documentation, and that they consider such a combination to be more useful than official API documentation when the official resources can be incomplete, ambiguous, incorrect, and outdated. Reviews are opinionated sentences with positive/negative sentiments. However, we are aware of no previous research that attempts to automatically produce API documentation from SO by considering both API code examples and reviews. In this article, we present two novel algorithms that can be used to automatically produce API documentation from SO by combining code examples and reviews towards those examples. The first algorithm is called statistical documentation, which shows the distribution of positivity and negativity around the code examples of an API using different metrics (e.g., star ratings). The second algorithm is called concept-based documentation, which clusters similar and conceptually relevant usage scenarios. An API usage scenario contains a code example, a textual description of the underlying task addressed by the code example, and the reviews (i.e., opinions with positive and negative sentiments) from other developers towards the code example. We deployed the algorithms in Opiner, a web-based platform to aggregate information about APIs from online forums. We evaluated the algorithms by mining all Java JSON-based posts in SO and by conducting three user studies based on produced documentation from the posts. The first study is a survey, where we asked the participants to compare our proposed algorithms against a Javadoc-syle documentation format (called as Type-based documentation in Opiner). The participants were asked to compare along four development scenarios (e.g., selection, documentation). The participants preferred our proposed two algorithms over type-based documentation. In our second user study, we asked the participants to complete four coding tasks using Opiner and the API official and informal documentation resources. The participants were more effective and accurate while using Opiner. In a subsequent survey, more than 80% of participants asked the Opiner documentation platform to be integrated into the formal API documentation to complement and improve the API official documentation.</t>
+          <t>With the proliferation of online technologies, social media recruitment has become an essential part of any company’s outreach campaign. A social media platform can provide marketing posts with access to a large pool of candidates and at a low cost. It also provides the opportunity to quickly customize and refine messages in response to the reception. With online marketing, the key question is: which communities are attracted by recruitment tweets on social media? In this work, we profile the Twitter accounts that interact with a set of recruitment tweets by the U.S. Army’s Recruitment Command through a network-centric perspective. By harnessing how users signal their affiliations through user information, we extract and analyze communities of social identities. From Social Identity Theory, these social identities can be critical drivers of behavior, like the decision to enlist in the military. With this framework, we evaluate the effectiveness of the U.S. Army’s recruitment campaign on Twitter, observing that these campaigns typically attract communities with military exposure like veterans or those that identify with professional careers and fitness (e.g., student, professionals, athletes). The campaign also attracts, but at a much lower level, interaction from those in the digital industries—data scientists, cybersecurity professionals, and so forth. When analyzing the accounts in terms of their degree of automation, we find a set of intent-unknown bot accounts interacting with the tweets, and that many of the recruitment accounts are perceived as automated accounts. These observations can aid in campaign refinement: targeting the digital community and getting a broader reach for online recruitment publicity campaigns.</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>usage scenario; documentation; crowd-sourced developer forum; API</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+          <t>Twitter; bot detection; network analysis; social signaling; social identity</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
@@ -3457,7 +3295,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -3465,17 +3303,17 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Functional programming for modular Bayesian inference</t>
+          <t>SnappView, a Software Development Kit for Supporting End-user Mobile Interface Review</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>We present an architectural design of a library for Bayesian modelling and inference in modern functional programming languages. The novel aspect of our approach are modular implementations of existing state-of-the-art inference algorithms. Our design relies on three inherently functional features: higher-order functions, inductive data-types, and support for either type-classes or an expressive module system. We provide a performant Haskell implementation of this architecture, demonstrating that high-level and modular probabilistic programming can be added as a library in sufficiently expressive languages. We review the core abstractions in this architecture: inference representations, inference transformations, and inference representation transformers. We then implement concrete instances of these abstractions, counterparts to particle filters and Metropolis-Hastings samplers, which form the basic building blocks of our library. By composing these building blocks we obtain state-of-the-art inference algorithms: Resample-Move Sequential Monte Carlo, Particle Marginal Metropolis-Hastings, and Sequential Monte Carlo Squared. We evaluate our implementation against existing probabilistic programming systems and find it is already competitively performant, although we conjecture that existing functional programming optimisation techniques could reduce the overhead associated with the abstractions we use. We show that our modular design enables deterministic testing of inherently stochastic Monte Carlo algorithms. Finally, we demonstrate using OCaml that an expressive module system can also implement our design.</t>
+          <t>This paper presents SnappView, an open-source software development kit that facilitates end-user review of graphical user interfaces for mobile applications and streamlines their input into a continuous design life cycle. SnappView structures this user interface review process into four cumulative stages: (1) a developer creates a mobile application project with user interface code instrumented by only a few instructions governing SnappView and deploys the resulting application on an application store; (2) any tester, such as an end-user, a designer, a reviewer, while interacting with the instrumented user interface, shakes the mobile device to freeze and capture its screen and to provide insightful multimodal feedback such as textual comments, critics, suggestions, drawings by stroke gestures, voice or video records, with a level of importance; (3) the screenshot is captured with the application, browser, and status data and sent with the feedback to SnappView server; and (4) a designer then reviews collected and aggregated feedback data and passes them to the developer to address raised usability problems. Another cycle then initiates an iterative design. This paper presents the motivations and process for performing mobile application review based on SnappView. Based on this process, we deployed on the AppStore "WeTwo", a real-world mobile application to find various personal activities over a one-month period with 420 active users. This application served for a user experience evaluation conducted with N1=14 developers to reveal the advantages and shortcomings of the toolkit from a development point of view. The same application was also used in a usability evaluation conducted with N2=22 participants to reveal the advantages and shortcomings from an end-user viewpoint.</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>type-classes; probabilistic programming; monads; monad transformers; module systems; machine learning; inductive types; higher-order functions; functional programming; WebPPL; Sequential Monte Carlo; Monte Carlo samplers; Markov Chain Monte Carlo; Bayesian inference; Anglican</t>
+          <t>GUI testing; application review; code instrumentation; heuristic evaluation; mobile computing; remote evaluation; software development kit; usability evaluation; usability problem; user interface evaluation</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -3498,7 +3336,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -3506,15 +3344,19 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Teaching embedded systems using the raspberry PI and sense hat</t>
+          <t>An Architectural Viewpoint for Benefit-Cost-Risk-Aware Decision-Making in Self-Adaptive Systems</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>This paper describes an upper division course in embedded systems development for Computer Science majors who have not had any Engineering courses. The course was developed to teach low-level programming, sensors, and some real-time concepts; using the Raspberry Pi™ and the Sense HAT™ sensor platform; with Python and C as programming languages.</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr"/>
+          <t>Self-adaptation equips a software system with a feedback loop that resolves uncertainties during operation and adapts the system to deal with them when necessary. Most self-adaptation approaches today use decision-making mechanisms that select for execution the adaptation option with the best-estimated benefit expressed as a set of adaptation goals. A few approaches also consider the estimated (one-off) cost of executing the candidate adaptation options. We argue that besides benefit and cost, decision-making in self-adaptive systems should also consider the estimated risk the system or its users would be exposed to if an adaptation option were selected for execution. Balancing all three concerns when evaluating the options for adaptation to mitigate uncertainty is essential for satisfying stakeholders’ concerns and ensuring the safety and public acceptance of self-adaptive systems. In this article, we present a reference model for decision-making in self-adaptation that considers the estimated benefit, cost, and risk as core concerns of each adaptation option. Leveraging this model, we then present an ISO/IEC/IEEE 42010 compatible architectural viewpoint that aims at supporting software architects responsible for designing robust decision-making mechanisms for self-adaptive systems. We demonstrate the applicability, usefulness, and understandability of the viewpoint through a case study where participants with experience in the engineering of self-adaptive systems performed a set of design tasks in DeltaIoT, an Internet-of-Things exemplar for research on self-adaptive systems.</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>self-adaptive; risk; cost; benefit; viewpoint; decision-making</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3535,7 +3377,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -3543,17 +3385,17 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>An empirical comparison of formalisms for modelling and analysis of dynamic reconfiguration of dependable systems</t>
+          <t>Adventures in monitorability: from branching to linear time and back again</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>This paper uses a case study to evaluate empirically three formalisms of different kinds for their suitability for the modelling and analysis of dynamic reconfiguration of dependable systems. The requirements on an ideal formalism for dynamic software reconfiguration are defined. The reconfiguration of an office workflow for order processing is described, and the requirements on the reconfiguration of the workflow are defined. The workflow is modelled using the Vienna Development Method (VDM), conditional partial order graphs (CPOGs), and the basic Calculus of Communicating Systems for dynamic process reconfiguration (basic CCSdp), and verification of the reconfiguration requirements is attempted using the models. The formalisms are evaluated according to their ability to model the reconfiguration of the workflow, to verify the requirements on the workflow’s reconfiguration, and to meet the requirements on an ideal formalism.</t>
+          <t>This paper establishes a comprehensive theory of runtime monitorability for Hennessy-Milner logic with recursion, a very expressive variant of the modal µ-calculus. It investigates the monitorability of that logic with a linear-time semantics and then compares the obtained results with ones that were previously presented in the literature for a branching-time setting. Our work establishes an expressiveness hierarchy of monitorable fragments of Hennessy-Milner logic with recursion in a linear-time setting and exactly identifies what kinds of guarantees can be given using runtime monitors for each fragment in the hierarchy. Each fragment is shown to be complete, in the sense that it can express all properties that can be monitored under the corresponding guarantees. The study is carried out using a principled approach to monitoring that connects the semantics of the logic and the operational semantics of monitors. The proposed framework supports the automatic, compositional synthesis of correct monitors from monitorable properties.</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Basic CCSdp; Conditional partial order graphs; VDM; Formal methods; Reconfiguration requirements; Workflow case study; Dynamic software reconfiguration</t>
+          <t>monitorability; monitor synthesis; linear-time and branching-time logics</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -3576,7 +3418,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -3584,17 +3426,17 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Incrementalizing lattice-based program analyses in Datalog</t>
+          <t>Continuous and Proactive Software Architecture Evaluation: An IoT Case</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Program analyses detect errors in code, but when code changes frequently as in an IDE, repeated re-analysis from-scratch is unnecessary: It leads to poor performance unless we give up on precision and recall. Incremental program analysis promises to deliver fast feedback without giving up on precision or recall by deriving a new analysis result from the previous one. However, Datalog and other existing frameworks for incremental program analysis are limited in expressive power: They only support the powerset lattice as representation of analysis results, whereas many practically relevant analyses require custom lattices and aggregation over lattice values. To this end, we present a novel algorithm called DRedL that supports incremental maintenance of recursive lattice-value aggregation in Datalog. The key insight of DRedL is to dynamically recognize increasing replacements of old lattice values by new ones, which allows us to avoid the expensive deletion of the old value. We integrate DRedL into the analysis framework IncA and use IncA to realize incremental implementations of strong-update points-to analysis and string analysis for Java. As our performance evaluation demonstrates, both analyses react to code changes within milliseconds.</t>
+          <t>Design-time evaluation is essential to build the initial software architecture to be deployed. However, experts’ assumptions made at design-time are unlikely to remain true indefinitely in systems that are characterized by scale, hyperconnectivity, dynamism, and uncertainty in operations (e.g. IoT). Therefore, experts’ design-time decisions can be challenged at run-time. A continuous architecture evaluation that systematically assesses and intertwines design-time and run-time decisions is thus necessary. This paper proposes the first proactive approach to continuous architecture evaluation of the system leveraging the support of simulation. The approach evaluates software architectures by not only tracking their performance over time, but also forecasting their likely future performance through machine learning of simulated instances of the architecture. This enables architects to make cost-effective informed decisions on potential changes to the architecture. We perform an IoT case study to show how machine learning on simulated instances of architecture can fundamentally guide the continuous evaluation process and influence the outcome of architecture decisions. A series of experiments is conducted to demonstrate the applicability and effectiveness of the approach. We also provide the architect with recommendations on how to best benefit from the approach through choice of learners and input parameters, grounded on experimentation and evidence.</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Static Analysis; Lattice; Language Workbench; Incremental Computing; Domain-Specific Language; Datalog</t>
+          <t>Continuous evaluation; software architecture evaluation; time series forecasting; IoT</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
@@ -3617,7 +3459,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>678</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -3625,30 +3467,26 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>How Configurable Is the Linux Kernel? Analyzing Two Decades of Feature-Model History</t>
+          <t>Incentive Mechanisms for Participatory Sensing: Survey and Research Challenges</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Today, the operating system Linux is widely used in diverse environments, as its kernel can be configured flexibly. In many configurable systems, managing such variability can be facilitated in all development phases with product-line analyses. These analyses often require knowledge about the system’s features and their dependencies, which are documented in a feature model. Despite their potential, product-line analyses are rarely applied to the Linux kernel in practice, as its feature model still challenges scalability and accuracy of analyses. Unfortunately, these challenges also severely limit our knowledge about two fundamental metrics of the kernel’s configurability, namely its number of features and configurations. We identify four key limitations in the literature related to the scalability, accuracy, and influence factors of these metrics, and, by extension, other product-line analyses: (1) Analysis results for the Linux kernel are not comparable, because relevant information is not reported; (2) there is no consensus on how to define features in Linux, which leads to flawed analysis results; (3) only few versions of the Linux kernel have ever been analyzed, none of which are recent; and (4) the kernel is perceived as complex, although we lack empirical evidence that supports this claim. In this article, we address these limitations with a comprehensive, empirical study of the Linux kernel’s configurability, which spans its feature model’s entire history from 2002 to 2024. We address the above limitations as follows: (1) We characterize parameters that are relevant when reporting analysis results; (2) we propose and evaluate a novel definition of features in Linux as a standardization effort; (3) we contribute torte, a tool that analyzes arbitrary versions of the Linux kernel’s feature model; and (4) we investigate the current and possible future configurability of the kernel on more than 3,000 feature-model versions. Based on our results, we highlight 11 major insights into the Linux kernel’s configurability and make 7 actionable recommendations for researchers and practitioners.</t>
+          <t>Participatory sensing is a powerful paradigm that takes advantage of smartphones to collect and analyze data beyond the scale of what was previously possible. Given that participatory sensing systems rely completely on the users’ willingness to submit up-to-date and accurate information, it is paramount to effectively incentivize users’ active and reliable participation. In this article, we survey existing literature on incentive mechanisms for participatory sensing systems. In particular, we present a taxonomy of existing incentive mechanisms for participatory sensing systems, which are subsequently discussed in depth by comparing and contrasting different approaches. Finally, we discuss an agenda of open research challenges in incentivizing users in participatory sensing.</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Linux kernel; feature modeling; software product lines; software variability</t>
+          <t>survey; research challenges; game theory; auction theory; QoI</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
@@ -3662,7 +3500,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>683</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -3670,30 +3508,26 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Identifying Non-Technical Skill Gaps in Software Engineering Education: What Experts Expect But Students Don’t Learn</t>
+          <t>odeToJava: A PSE for the Numerical Solution of IVPs</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>As the importance of non-technical skills in the software engineering industry increases, the skill sets of graduates match less and less with industry expectations. A growing body of research exists that attempts to identify this skill gap. However, only few so far explicitly compare opinions of the industry with what is currently being taught in academia. By aggregating data from three previous works, we identify the three biggest non-technical skill gaps between industry and academia for the field of software engineering: devoting oneself to continuous learning, being creative by approaching a problem from different angles, and thinking in a solution-oriented way by favoring outcome over ego. Eight follow-up interviews were conducted to further explore how the industry perceives these skill gaps, yielding 26 sub-themes grouped into six bigger themes: stimulating continuous learning, stimulating creativity, creative techniques, addressing the gap in education, skill requirements in industry, and the industry selection process. With this work, we hope to inspire educators to give the necessary attention to the uncovered skills, further mitigating the gap between the industry and the academic world.</t>
+          <t>Problem-solving environments (PSEs) offer a powerful yet flexible and convenient means for general experimentation with computational methods, algorithm prototyping, and visualization and manipulation of data. Consequently, PSEs have become the modus operandi of many computational scientists and engineers. However, despite these positive aspects, PSEs typically do not offer the level of granularity required by the specialist or algorithm designer to conveniently modify the details. In other words, the level at which PSEs are black boxes is often still too high for someone interested in modifying an algorithm as opposed to trying an alternative.In this article, we describe odeToJava, a Java-based PSE for initial-value problems in ordinary differential equations. odeToJava implements explicit and linearly implicit implicit-explicit Runge--Kutta methods with error and stepsize control and intra-step interpolation (dense output), giving the user control and flexibility over the implementational aspects of these methods. We illustrate the usage and functionality of odeToJava by means of computational case studies of initial-value problems (IVPs).</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Software engineering education; creativity; professional skills; software developer; industry requirements</t>
+          <t>Adaptive integration; Runge--Kutta; St\"{o}rmer--Verlet; additive Runge--Kutta; geometric integration; object-oriented; problem solving environment; software architecture; stepsize-control</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="n"/>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
@@ -3702,12 +3536,12 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -3715,30 +3549,26 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>A Job Finder Chatbot-Based Web Platform: A Use Case for Software Engineers</t>
+          <t>RAPID: Zero-Shot Domain Adaptation for Code Search with Pre-Trained Models</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Finding a job requires browsing through a vast number of position openings, usually at various online sites. This process becomes more complicated for users when they are considering different potential job locations. Even though existing tools that automate the process exist (e.g. sonara.ai, dream.jobs), they lack the element of interactivity with the user and the integration of external resources that contain information on the skills of the user. With the aim to bridge the gap between job seekers and potential employers by matching resumes and job listings more efficiently and effectively, in this work we are introducing an AI-driven chatbot-based web platform to assist job seeking. In the initial implementation, we are considering the job seeking needs of software engineers but more disciplines can be easily added. We have integrated the developer's CV and the user's GitHub account, and are describing the design and implementation process of the web platform, while a small scale user evaluation has also been performed. We argue that the chatbot can be used as a starting point for similar job seeking assistants. Copyright © 2025 by SCITEPRESS - Science and Technology Publications, Lda.</t>
+          <t>Code search, which refers to the process of identifying the most relevant code snippets for a given natural language query, plays a crucial role in software maintenance. However, current approaches heavily rely on labeled data for training, which results in performance decreases when confronted with cross-domain scenarios including domain- or project-specific situations. This decline can be attributed to their limited ability to effectively capture the semantics associated with such scenarios. To tackle the aforementioned problem, we propose a zeRo-shot domAin adaPtion with pre-traIned moDels framework for code search named RAPID. The framework first generates synthetic data by pseudo labeling, then trains the CodeBERT with sampled synthetic data. To avoid the influence of noisy synthetic data and enhance the model performance, we propose a mixture sampling strategy to obtain hard negative samples during training. Specifically, the mixture sampling strategy considers both relevancy and diversity to select the data that are hard to be distinguished by the models. To validate the effectiveness of our approach in zero-shot settings, we conduct extensive experiments and find that RAPID outperforms the CoCoSoDa and UniXcoder model by an average of 15.7% and 10%, respectively, as measured by the MRR metric. When trained on full data, our approach results in an average improvement of 7.5% under the MRR metric using CodeBERT. We observe that as the model’s performance in zero-shot tasks improves, the impact of hard negatives diminishes. Our observation also indicates that fine-tuning CodeT5 for generating pseudo labels can enhance the performance of the code search model, and using only 100-shot samples can yield comparable results to the supervised baseline. Furthermore, we evaluate the effectiveness of RAPID in real-world code search tasks in three GitHub projects through both human and automated assessments. Our findings reveal RAPID exhibits superior performance, e.g., an average improvement of 18% under the MRR metric over the top-performing model.</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Chatbots; Employment; Information systems; Information use; Knowledge management; Software engineering; Websites; Chatbots; Engineering position; Github; Hard skill; Interactivity; Job advert; Job-seeking; Online sites; Soft skills; Software engineering position; Engineers</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>IC2; IC5</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>Code search; zero-shot learning; software maintenance; pre-trained models; domain adaption</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="n"/>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
@@ -3747,12 +3577,12 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>IEEE Xplore</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>833</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -3760,17 +3590,17 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Validating a Set of Candidate Criteria for Evaluating Software Tools and Data Sources for National CSIRTs’ Cyber Incident Responses</t>
+          <t>IEEE Magazines</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>National Computer Security Incident Response Teams (CSIRTs) are established worldwide to coordinate responses to cyber security incidents at the national level. It is known that software tools (including open source ones) and public data are routinely used to facilitate incident response in national CSIRTs. However, there is a lack of an authoritative set of criteria that can be used for a systematic evaluation to decide which software tools and data sources should be used by national CSIRTs for incident response. A prior study identified a set of potential candidate criteria for such an evaluation. The study presented in this article aims to validate these candidate criteria empirically by asking staff members of several national CSIRTs how they perceive the candidate criteria’s practical usefulness and readiness for deployment in national CSIRTs’ operations. The study involved online semi-structured interviews with nine interviewees from nine national CSIRTs in Asia-Pacific, Africa and Europe. After validating the candidate criteria using semi-structured interviews with these nine interviewees, we applied the criteria to evaluate a selection of software tools and data sources by converting each criterion into one or more relevant metrics, such as ‘measuring the time taken by a tool to produce results’. Results from the study led to the following main findings: (1) all interviewees perceived the candidate criteria as practically useful for evaluating tools and data sources in the operations of national CSIRTs; (2) all interviewees agreed that the candidate criteria could be deployed in national CSIRTs and other types of CSIRTs and (3) the candidate criteria can be applied relatively easily in practice. These criteria are envisaged to help national CSIRTs select the most appropriate tools and data sources to facilitate effective incident response, improve their operational practices and improve the quality of wider security operations. © 2025 Copyright held by the owner/author(s).</t>
+          <t>A major concern among graduates of computing departments is the discrepancy between the expectations of software companies and the competencies provided by the academic departments. This ongoing problem makes co-op education inevitable, as it combines industrial experience with traditional education.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Computer aided software engineering; Computer software selection and evaluation; National security; Network security; Open systems; Security systems; CERT; Computer security incident response team; Criteria; Cybe incident response; Data evaluation; Incident response; National computer security incident response team; Security incident; Semi structured interviews; Tools evaluations; Open source software</t>
+          <t>Companies; Education; Employment; Software engineering; Recruitment; Software; Training; Computer science education; Educational courses; Career development</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
@@ -3793,7 +3623,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>927</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -3801,26 +3631,26 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Recruitment in SMEs: the role of managerial practices, technology and innovation</t>
+          <t>Desired Qualifications Sought in Entry Level Software Engineers</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Purpose: Various scholars suggest that there is a lack of research on the recruitment in small and medium-sized enterprises (SMEs) and also a scarcity of theoretical basis for the recruitment procedures used by these companies. As the vast majority of studies concentrate on larger organizations, they may not accurately reflect the challenges faced by smaller-sized entities to profoundly and accurately comprehend their recruitment procedures. In addition, the use of technology in recruitment has grown in importance in today’s quickly evolving business environment, particularly in light of the COVID-19 pandemic footprint. This study aims to examine the recruitment procedures used by SMEs and how they have been compelled to adjust to different extents to these technological improvements by the effects of the aforementioned epidemic. Design/methodology/approach: With the aim to investigate the current recruitment practices in SMEs and the extent to which digital technologies are embraced by these companies within human resources (HR) procedures, this research relied on interviews with SMEs representatives. The qualitative methods used provided access to relevant data and insights, as they allowed close interactions with top managers and CEOs of ten companies from various sectors. Thus, the research results draw a vivid and reliable image of the procedures and practices used by small and medium-sized companies to attract, select and retain their staff. Findings: This study’s findings are of increased interest to HR professionals, recruiters and managers in SMEs, who aim to attract and retain the best talent and optimize their recruitment strategies in a rapidly changing business environment, enabled by technological advancements. Effective HR recruitment procedures adapted to the specific needs of small and medium-sized companies can lead to several benefits for the organization, including improved employee selection, reduced turnover and increased organizational productivity. Research limitations/implications: Although the interviews examined here encompass recruitment techniques from SMEs in a variety of industries, the results’ generalizability is limited by the sample size and geography. Furthermore, the findings’ dependability is dependent on the accuracy of the data provided by the respondents. Practical implications: This investigation confirms some of the theoretical underpinnings which point to the lack of formalized structures and procedures in the recruitment process in SMEs, which enjoy more flexibility in managing HR processes. In addition, the results reinforce the arguments indicating an adjustment between HR strategies or policies and organizational goals in smaller enterprises which adapt faster to changes in the market. Moreover, it becomes apparent that there is a relationship between the quality of job descriptions and the successful fit in attracting the right candidates for the open positions. Furthermore, digital technologies offer opportunities for expanding the recruiters’ reach to a wider audience and also support the selection stage, thus increasing the chances of finding suitable staff. As the need to shift from traditional recruitment to e-recruitment in SMEs has been highlighted in the literature, the qualitative research revealed that this need was driven on the one hand by the COVID-19 pandemic when these companies successfully adapted and implemented new online methods of recruiting, but also by the lack of skilled labor, leading to the expansion of recruitment to other parts of the country or even to other countries. Social implications: With regard to the proportion of men and women used in small and medium-sized companies, there is a clear need to involve and train more women in the predominantly male-dominated industrial and IT sectors. From this point of view, companies tend to devote more interest to integrating communities of women in these industries, as well as in key management positions. Another point of interest that the study highlights is the fact that SMEs have started to get creative with the benefits package they propose to candidates and focus on remote work, hybrid office–home working, or seasonal work to offer future employees a better work–life balance. Originality/value: The added value of this investigation is filling the gaps in the current literature concerning recruitment procedures currently used by SMEs, the challenges they face and the solutions they advanced to solve them. Furthermore, SMEs often drive innovation and competition in the market and play a crucial role in the supply chain of larger companies, providing them with the goods and services they need to operate and supporting the availability and reliability of products from larger companies. They are often the driving force behind revitalizing local economies and creating new employment opportunities. Consequently, the underlying significance of this study is rooted in the need to modernize and simultaneously improve HR recruitment procedures through the integration of technology and a focus on innovation. © 2023, Emerald Publishing Limited.</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr"/>
+          <t>Global demand for software engineers continues to strain the technology sector with unfilled software engineering positions and stiff competition for hiring developers who are on the market. To attract more candidates, technology firms have increasingly been working closely with universities to recruit new graduates to fill their jobs. Universities hoping to minimize mismatches in job placement for new software developers should teach the skills and attributes that enable entry-level software developers to succeed. This paper presents a case study of hiring demands at one large, well-established technology company that reveals the most sought-after attributes in new hires. We discuss results of our interviews with five software development hiring managers and the results from a wide survey of engineers and architects from various levels and experiences. The interviews and surveys reveal that some qualifications are widely desired, and others have varying demand based on functional area, technology, or type of development. Ultimately, professional skills (e.g., teamwork) and personality traits (e.g., strong initiative) top the list of desired attributes, along with a few fundamentally broad technical skills. One key takeaway is that candidates who learn professional skills from university programs may be more readily hired into their first software engineering job than those whose education focused mostly on technical areas. © 2023 ACM.</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Employment; Engineering education; Professional aspects; Software design; Case-studies; Employer-seek skill; Engineering position; Global demand; Hireability; Hiring managers; Professional skills; Software developer; Technology companies; Technology sectors; Engineers</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>IC1; IC2</t>
+          <t>IC1; IC4</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="n"/>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
@@ -3838,7 +3668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3868,8 +3698,8 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Revisor 1</t>
@@ -3880,7 +3710,7 @@
           <t>Revisor 2</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -3888,12 +3718,246 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Job Market: Salaries, Trends &amp; Insights</t>
+          <t>Software Engineering | Future Students</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Why are entry-level data and software engineering roles so ...</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning with System/Software Engineering in ...</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Relationship between computer science and software ...</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>AI and Software Engineering: A Symbiotic Relationship</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Does familiarity with the attraction matter? Antecedents of ...</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>I am really into computers and I would love to study ...</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology Tests - Pre-Employment ...</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Levels and Titles</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Gartner for Software Engineering Leaders</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Information technology Review 1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Reliability assessment of AI systems - ISO/IEC AWI TS 25570</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sampling in Software Engineering Research:A Critical Review ...</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Computer Programming and Analysis (Software Engineering ...</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>37 Hybrid &amp; Onsite Software Engineering Jobs in Tallinn ...</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology Archives</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Information and Software Technology Journal</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology Course - Career Choices &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>A Preliminary Guide for Assertive Selection of Active ...</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/processed/export/APOLLO_Screening_Results.xlsx
+++ b/data/processed/export/APOLLO_Screening_Results.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,11 +34,23 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="00333333"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00C65911"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +63,20 @@
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -74,56 +98,26 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -255,16 +249,18 @@
     <author>APOLLO</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Inclusion Criteria (IC):
-IC1: Sources explicitly addressing R&amp;S processes for SE roles.
+        <t>IC1: Sources explicitly addressing R&amp;S processes for SE roles.
 IC2: Sources describing stages, pipelines, structures, or procedures of SE R&amp;S.
 IC3: Sources reporting challenges, frictions, or perceptions related to SE R&amp;S.
 IC4: Sources describing practices, assessment methods, or evaluation mechanisms.
-IC5: Sources providing empirical findings or practitioner-reported experiences.
-Exclusion Criteria (EC):
-EC1: Sources not written in English.
+IC5: Sources providing empirical findings or practitioner-reported experiences.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>EC1: Sources not written in English.
 EC2: Sources whose full text was unavailable.
 EC3: Short publications lacking sufficient methodological or experiential evidence (editorials, posters, extended abstracts).
 EC4: Sources published before 2015.
@@ -272,16 +268,18 @@
 EC6: Duplicate studies.</t>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Inclusion Criteria (IC):
-IC1: Sources explicitly addressing R&amp;S processes for SE roles.
+        <t>IC1: Sources explicitly addressing R&amp;S processes for SE roles.
 IC2: Sources describing stages, pipelines, structures, or procedures of SE R&amp;S.
 IC3: Sources reporting challenges, frictions, or perceptions related to SE R&amp;S.
 IC4: Sources describing practices, assessment methods, or evaluation mechanisms.
-IC5: Sources providing empirical findings or practitioner-reported experiences.
-Exclusion Criteria (EC):
-EC1: Sources not written in English.
+IC5: Sources providing empirical findings or practitioner-reported experiences.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>EC1: Sources not written in English.
 EC2: Sources whose full text was unavailable.
 EC3: Short publications lacking sufficient methodological or experiential evidence (editorials, posters, extended abstracts).
 EC4: Sources published before 2015.
@@ -582,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -671,7 +669,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -679,26 +677,30 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Goal-oriented assessment of product-line domains</t>
+          <t>Artificial Intelligence Enabled, Social Media Leveraging Job Matching System for Employers and Applicants</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Software product-line engineering is a method for improving the efficiency and effectiveness of software development. Introducing such a method into an industrial software development environment is potentially of great benefit, but one cannot afford to stop product development while doing so. Rather, in Avaya we apply an incremental adoption strategy and therefore must identify which part(s) of the product line we will create first. Since we consider a product line to consist of a number of domains, the problem is to identify the right domains to start with. We identified two driving factors for selecting product-line domains: corporate impact and likelihood of success. Our assessment of candidate domains is driven by these two goals, which we decompose further into a set of domain selection criteria and corresponding questions. The data, i.e., the answers to the questions, are gathered during interview sessions with our domain experts and evaluated according to our goal decomposition formulas. We illustrate the approach by an example application for which we assessed 20 different domains for one of Avaya's major product lines. © 2003 IEEE.</t>
+          <t>Social media is increasingly becoming a window to the user's personality. Hiring the right candidate is a formidable task for any organization and particularly in the highly competitive software industry. This paper presents a machine learning and natural language processing based system to leverage social media to assess job applicants for their suitability for a given job. We use LinkedIn profiles to assess the technical suitability and combine Twitter posts with them to assess the emotional intelligence of the applicant. The system thus indicates both the technical and soft skills perspective of the job applicants. The system can be used by both prospective employers and employees. Employers can use it to shortlist job applicants and prospective employees can use it to evaluate their chances, retrospect, and take any corrective action. The results from the created system are encouraging. © 2022 IEEE.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Application programs; Computer architecture; Computer programming; Computer software; Mathematical programming; Product development; Computer industry; Different domains; Domain experts; Driving factors; Goal-oriented; Industrial software development; Selection criteria; Software product line engineerings; Software design</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>Learning algorithms; Natural language processing systems; Personnel; Social networking (online); Software engineering; Hiring; Job applicant; Job matching; Language processing; Machine-learning; Matching system; Natural language processing; Natural languages; Regression; Social media; Machine learning</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -712,7 +714,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -720,26 +722,30 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>An Exploration of the Perceived Value of Information Technology Certification between Information Technology and Human Resources Professionals</t>
+          <t>ICode-An Unified Competitive Coding Profile Platform</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>During the decade of the 1990s, many firms engaged in widespread internal dissemination of information technology (IT) in an effort to leverage the capabilities of IT into greater organizational efficiencies. Information technologies such as electronic mail, office automation applications, and enterprise resource planning systems, are a few of the most popular examples of organizational IT initiatives from the past decade. Today, the use of information technology is an integral part of the ordinary course of business and provides technologically progressive firms with heretofore-unseen opportunities. For example, Dell Computers developed and maintains a competitive advantage in the retail technology sector based partly upon the use if information technology that did not exist 10 years ago. Although business applications of information technology present firms with vast opportunity, there is a myriad of complexities associated with organizational IT usage. Generally, this paper examines one critical area: the human resource aspect of organizational IT usage. Specifically, the research presented herein answers the question “Do human resource and information technology professionals perceive information technology certification differently?” The question is of practical relevance when examined, as in this study, within the context of the candidate selection process for a firm evaluating potential hires for an information technology-related position. Initially, the current paper presents a comprehensive overview of the theoretical foundations of certification. From theory, we construct a testing methodology that utilizes, as subjects, practicing human resource and information technology professionals. An analysis of the collected data revealed a marked difference in the perception of information technology certification among the subject groups. Based on the results of structured interviews with the study participants, we present concluding explanations regarding the statistically significant differences among groups. © 2009 by IGI Global. All rights reserved.</t>
+          <t>Although a software developer is capable of creating excellent software without the necessity for competitive coding. Having their hands in it may increase the project's efficiency and scalability. For every developer, problem solving is a must-required skill that is gained through competitive coding. Many technical recruiters use competitive programming as a barometer to assess a candidate's potential for the post of software engineer, including many prestigious Silicon Valley companies like Google, Facebook,etc. Since there is no such platform that helps students showcase their coding status on every registered platform, the proposed system helps to have such. ICode is a unified platform to help students visualize their coding profile status on a single site at one go. There is no public API that can be used to retrieve the data.from websites; hence, web scraping becomes relevant in this situation. It is one of the strategies of information retrieval.lnstead of manually copying data from the browser, with web scraping, it becomes easy to automatically extract the data. without any effort and perform analysis on it. The paper mainly targets the visualization of the data scrapped from competitive coding platforms to create a digital resume and perform analysis based on the scraped data. This is a digital resume.will be a revolution in the modern-day recruitment process since it will contain realtime user's details and coding platform ratings. and their analysis, project information, and digital bridges to platforms like Github and LinkedIn, where recruiters can actually review the users's information in a better way as compared to the old paper resume. © 2024 IEEE.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Enterprise resource planning; Information dissemination; Information use; Personnel selection; Automation applications; Enterprise resource planning systems; Information technology certification; Information technology professionals; Information technology usages; Organizational efficiency; Organizational information; Perceived value; Resource professionals; Value of information; Competition</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Data visualization; Visualization; API; Coding platform; Data; Digital resumes; Problem-solving; Project efficiency; Retrieval; Silicon valley; Software developer; Web scrapings; Websites</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -753,7 +759,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -761,22 +767,30 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Demand and Status of a Scientific Degree in the Non-Academic Labour Market: Regional Case; [Востребованность и статус учёной степени на неакадемическом рынке труда: региональный кейс]</t>
+          <t>Job2vec: Job title benchmarking with collective multi-view representation learning</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Technological leadership and innovation-driven growth have actualized the request for highly qualified personnel, which have recently been associated with holders of a scientific degree. In the academic field, a scientific degree is a testimony to the occupational status and an integral feature of professional growth and advancement. The reasonableness and significance of a scientific degree in the non-academic market are ambiguous. The purpose of this article is to investigate the opinion and assessments of the non-academic sphere representatives about the demand for the employees with a scientific degree and the status of a scientific degree outside the academic labour market. The research was conducted using the method of semi-structured interview with employers and representatives of seven enterprises in the south of Russia in the machine engineering, metalworking, ferrous metallurgy and IT sectors (n = 13). As a result of the study it was established that: in employment a scientific degree does not give competitive advantages to the applicant; a scientific degree has no value in the non-academic labour market, does not contribute to the advancement and occupation of a higher position in the enterprise; a scientific degree and the presence of employees with a scientific degree in the staff are considered as image-building, status marker and reputation capital of the enterprise; employers have stereotypes regarding scientific employees, which are associated both with the individual organization of labour processes and the compatibility of the scientific, creative and production process; the non-academic sector lacks a human resources strategy for dealing with such employees and a system of their incentives. The authors conclude that the demand for a scientific degree in the non-academic labour market is caused largely by a political request related with the belief that technological and innovative breakthroughs can provide highly qualified personnel with a scientific degree. The authors focus on the probable risks associated with the massification of degree holders, that can lead to a blurring of academic culture and loss of identity of the scientific community. © 2025 Moscow Polytechnic University. All rights reserved.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Job Title Benchmarking (JTB) aims at matching job titles with similar expertise levels across various companies. JTB could provide precise guidance and considerable convenience for both talent recruitment and job seekers for position and salary calibration/prediction. Traditional JTB approaches mainly rely on manual market surveys, which is expensive and labor intensive. Recently, the rapid development of Online Professional graph has accumulated a large number of talent career records, which provides a promising trend for data-driven solutions. However, it is still a challenging task since (1) the job title and job transition (job-hopping) data is messy which contains a lot of subjective and non-standard naming conventions for a same position (e.g., Programmer, Software Development Engineer, SDE, Implementation Engineer), (2) there is a large amount of missing title/transition information, and (3) one talent only seeks limited numbers of jobs which brings the incompleteness and randomness for modeling job transition patterns. To overcome these challenges, we aggregate all the records to construct a large-scale Job Title Benchmarking Graph (Job-Graph), where nodes denote job titles affiliated with specific companies and links denote the correlations between jobs. We reformulate the JTB as the task of link prediction over the Job-Graph that matched job titles should have links. Along this line, we propose a collective multi-view representation learning method (Job2Vec) by examining the Job-Graph jointly in (1) graph topology view (the structure of relationships among job titles), (2) semantic view (semantic meaning of job descriptions), (3) job transition balance view (the numbers of bidirectional transitions between two similar-level jobs are close), and (4) job transition duration view (the shorter the average duration of transitions is, the more similar the job titles are). We fuse the multi-view representations in the encode-decode paradigm to obtain an unified optimal representations for the task of link prediction. Finally, we conduct extensive experiments to validate the effectiveness of our proposed method. © 2019 Association for Computing Machinery.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Benchmarking; Compensation (personnel); Employment; Job analysis; Knowledge management; Learning systems; Semantics; Software design; Topology; Auto encoders; Job description; Learning methods; Multi-view learning; Representation Learning; Talent Intelligence; Transition duration; Transition patterns; Engineers</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
@@ -790,7 +804,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -798,22 +812,26 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Evaluating the effectiveness of E-recruitment in IT companies: Overcoming technological constraints and regulatory compliance</t>
+          <t>Employer brand and its unexplored impact on intent to join</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>As the Information Technology industry evolves, e-recruitment emerges as a pivotal tool for sourcing talent. However, challenges like technological constraints and regulatory compliance hinder its effectiveness. This cross-sectional study delves into the discerned effectiveness of e-recruitment methods and the associated barriers encountered by Information Technology companies in the adoption of these practices. A robust dataset comprising responses from 537 participants actively involved in recruitment activities across various sectors of the Information Technology industry was collected through a structured questionnaire. The analysis employed descriptive statistics to summarize sample demographics, inferential statistics including correlation and regression analyses to test hypotheses, and Harman's single-factor test to determine common method variance. The study identified several key findings aligned with its research objectives. Firstly, it confirmed a constructive association between the discerned effectiveness of e-recruitment methods and their adoption by Information Technology companies. However, it also revealed that technological constraints negatively impact the perceived effectiveness of e-recruitment, highlighting a critical barrier in the adoption process. Additionally, the study uncovered a significant association between the availability of skilled Information Technology professionals and the effectiveness of e-recruitment methods utilized by Information Technology firms. Moreover, it found that the integration of e-recruitment platforms with existing human resources systems positively influences their perceived effectiveness in the Information Technology sector, while regulatory compliance requirements pose significant barriers to their effective implementation. Furthermore, the study revealed that the user experience design in e-recruitment platforms affects their perceived effectiveness among Information Technology job seekers and human resources professionals. This study contributes novel insights by providing empirical evidence on the efficacy of e-recruitment methods in Information Technology organizations and the barriers hindering their adoption. Its findings offer insights for Information Technology companies and human resources professionals to enhance their recruitment strategies and address potential challenges, thereby unlocking the potential of e-recruitment in the Information Technology field. © The Author(s) 2025.</t>
+          <t>Purpose: The purpose for this paper is to determine the various dimensions of employer brand in the IT sector of India and analyse their impact on the final intent of the candidates to join an organisation. A five-factor employer brand (EB) model and three-factor intent to join (ITJ) model have been tested for reliability and validity through confirmatory factor analysis (CFA). A structural model is empirically tested with EB as independent variable and ITJ as dependent variable through structured equation modelling. Design/methodology/approach: The items for the independent variable EB are generated with the help of literature and semi-structured interviews with final-year student placement coordinators of B.Tech and MCA, studying in central, state and deemed universities of India. For ITJ, the variables are adopted from the literature and confirmed through CFA in the Indian context. Structured equation modelling has been used to analyse the relationship between EB and ITJ. Findings: Five dimensions of EB were explored as growth and development opportunity, company’s reputation, acceptance and belongingness, work–life balance and ethics and CSR. ITJ was found to be composed of intent to pursue, employer’s attractiveness and employer’s reputation. EB has been found to be an effective contributor to ITJ. Research limitations/implications: The current study has been conducted in the IT sector, and other sectors have not been included. The universities considered for the study were limited to central, state and deemed universities of India. Apart from intention to join, there are other attitudinal and behavioural aspects that have not been included in the current study. Originality/value: This study gives empirical evidence on EB to be an important antecedent of ITJ from the perspective of prospective employees of a developing nation. © 2018, Emerald Publishing Limited.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IC1; IC2; IC3; IC4</t>
+          <t>IC1; IC4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
@@ -822,12 +840,12 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -835,26 +853,30 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Assessing technical candidates on the social web</t>
+          <t>MetaAgents: Large Language Model Based Agents for Decision-Making on Teaming</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>The Social Web provides comprehensive and publicly available information about software developers, identifying them as contributors to open source projects, experts at maintaining ties on social network sites, or active participants on knowledge-sharing sites. These signals, when aggregated and summarized, could be used to define potential candidates' individual profiles: potential employers could qualitatively evaluate job seekers, even those lacking a formal degree or changing their career path, by assessing candidates' online contributions. At the same time, developers are aware of the Web's public nature and the possible uses of published information when they determine what to share with the world. Some might even try to manipulate public signals of technical qualifications, soft skills, and reputation in their favor. Assessing candidates on the Web for technical positions presents challenges to recruiters, the most serious being the interpretation of the provided signals. An in-depth discussion proposes guidelines for software engineers and recruiters to help recruiters interpret the value and trouble with the signals and metrics they use to assess a candidate's characteristics and skills. © 1984-2012 IEEE.</t>
+          <t>Significant advancements have occurred in the application of Large Language Models (LLMs) for social simulations. Despite this, their abilities to perform teaming in task-oriented social events are underexplored. Such capabilities are crucial if LLMs are to effectively mimic human-like social behaviors and form efficient teams to solve tasks. To bridge this gap, we introduce MetaAgents, a social simulation framework populated with LLM-based agents. MetaAgents facilitates agent engagement in conversations and a series of decision making within social contexts, serving as an appropriate platform for investigating interactions and interpersonal decision-making of agents. In particular, we construct a job fair environment as a case study to scrutinize the team assembly and skill-matching behaviors of LLM-based agents. We take advantage of both quantitative metrics evaluation and qualitative text analysis to assess their teaming abilities at the job fair. Our evaluation demonstrates that LLM-based agents perform competently in making rational decisions to develop efficient teams. However, we also identify limitations that hinder their effectiveness in more complex team assembly tasks. Our work provides valuable insights into the role and evolution of LLMs in task-oriented social simulations.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Computer supported cooperative work; Human computer interaction; Knowledge management; Knowledge representation; Social networking (online); Social sciences computing; Career paths; Group and organization interfaces; Information interfaces; Job seekers; Knowledge retrieval; Knowledge-sharing; Open source projects; Social Networks; Soft skills; Software developer; Software engineers; Technical qualification; Employment</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>collaborative and social computing; large language models; social simulation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC4</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -863,12 +885,12 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -876,22 +898,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>“This Gig Is Not for Women”: Gender Stereotyping in Online Hiring</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>This study examines gender segregation in the context of the so-called gig economy. In particular, it explores the role that stereotypes about male and female occupations play in sorting men and women into different jobs in an online freelance marketplace. The findings suggest that gender stereotypes are particularly salient in online hiring because employers typically contract for short-term, relatively low-value jobs based on limited information about job applicants. These conditions trigger the use of cognitive shortcuts about intrinsic gender characteristics linked to different skills and occupations. The results corroborate that female candidates are less likely to be hired for male-typed jobs (e.g., software development) but more likely to be hired for female-typed jobs (e.g., writing and translation) than equally qualified male candidates. Further, the study investigates three mechanisms predicted to attenuate the female penalty in male-typed jobs. The penalty is found to be self-reinforcing, as it perpetuates gender imbalances in worker activity across job categories that strengthen the sex typing of occupations. © The Author(s) 2019.</t>
-        </is>
-      </c>
+          <t>Empowering career development: a comprehensive AI-driven system for personalised guidance and recommendations</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -900,12 +922,12 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -913,26 +935,22 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>A model for navigating interview processes in requirements elicitation</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Experts in requirements elicitation have interviews to stakeholders using various levels of knowledge to grasp and elicit user's requirements. This paper analyzes interview processes of these experts and explores a computation model for simulating them. This model can be used to navigate novice analysts' interview processes. It is a mixture consisting of a blackboard model and a state transition model in order to narrow the candidates for the questions that an expert analyst will ask the stakeholders next in the interview process. The candidates are selected based on the information that has been elicited from the stakeholders until now, and the blackboard model is for holding this information in the form of IEEE 830, a standard form of requirements specification documents. We have analyzed the experts' interview processes and constructed the instance of the computation model in sales management domain. And we recorded novices' processes, simulated it on the novices' ones, and showed that we could improve them by means of the model.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Computer simulation; Mathematical models; Software engineering; Specifications; Requirements elicitation; Software requirements specification; Requirements engineering</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>AI Ethics in Practice: Exploring Racial and Ethnic Stereotypes in Synthetic Resumes Written by ChatGPT</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC3</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -941,12 +959,12 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -954,22 +972,22 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Education as a signal of trainability: Results from a vignette study with Italian employers</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Drawing on queuing theory, this study explores the relationship between education and labour market entry from the perspective of employers. On the basis of vignette study, we simulated a hiring process with a sample of recruiters and human resource managers. We analysed the role of education in the screening of applicants' resumes for job openings in the Information, Communication, and Technology sector in the Italian labour market. Findings reveal that employers attach importance to fine-grained indicators of school performance, such as grades and study duration to formulate their hiring decisions, in line with queuing theory. However, internships are disregarded as signals. Results are explained in light of the institutional arrangements that characterize the Italian school-to-work transition system: a standardized education system, poorly specific vocational tracks, weakly developed linkages between schools and firms, a remarkably high dropout rate before study completion. © 2014 © The Author 2014. Published by Oxford University Press. All rights reserved.</t>
-        </is>
-      </c>
+          <t>Understanding mindsets, skills, current practices, and barriers of adoption of digital accessibility in Kuwait’s software development landscape</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -978,12 +996,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -991,26 +1009,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Hiring and Intra-occupational Gender Segregation in Software Engineering</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Women tend to be segregated into different subspecialties than men within male-dominated occupations, but the mechanisms contributing to such intra-occupational gender segregation remain obscure. In this study, I use data from an online recruiting platform and a survey to examine the hiring mechanisms leading to gender segregation within software engineering and development. I find that women are much more prevalent among workers hired in software quality assurance than in other software subspecialties. Importantly, jobs in software quality assurance are lower-paying and perceived as lower status than jobs in other software subspecialties. In examining the origins of this pattern, I find that it stems largely from women being more likely than men to apply for jobs in software quality assurance. Further, such gender differences in job applications are attenuated among candidates with stronger educational credentials, consistent with the idea that relevant accomplishments help mitigate gender differences in self-assessments of competence and belonging in these fields. Demand-side selection processes further contribute to gender segregation, as employers penalize candidates with quality assurance backgrounds, a subspecialty where women are overrepresented, when they apply for jobs in other, higher-status software subspecialties. © American Sociological Association 2020.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>engineering; gender disparity; gender identity; gender relations; labor market; occupation; software; womens employment; womens status; workplace</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>Generalization of Logistic Regression to Improve Prediction: An Application on Training and Placement Data</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1019,12 +1033,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1032,26 +1046,30 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Automated Question Generation for Technical Interviews Using Deep Learning Models</t>
+          <t>A Review of Peer Code Review in Higher Education</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>The process of hiring technical talent often demands a thorough and effective evaluation method, though creating interview questions by hand can be slow and lead to uneven results. This paper introduces a tool that automatically generates targeted interview questions from job descriptions, using a specially adjusted BART model. The software, it depends on a selected dataset covering Software Engineering, Cloud Engineering, and Data Science, produces distinct, relevant, and varied questions that are suitable for specific task requirement. Also, it makes use of candidate and recruiter feedback via Reinforcement Learning from Human feedback (RLHF) in order to constantly improve its output, boosting the questions' fit and quality. The experiments using ROUGE metrics show this method not only improves the hiring process but also allows an adaptable way to boost the level of consistency of technical evaluations. © 2025 IEEE.</t>
+          <t>Peer review is the standard process within academia for maintaining publication quality, but it is also widely employed in other settings, such as education and industry, for improving work quality and for generating actionable feedback to content authors. For example, in the software industry peer review of program source code—or peer code review—is a key technique for detecting bugs and maintaining coding standards. In a programming education context, although peer code review offers potential benefits to both code reviewers and code authors, individuals are typically less experienced, which presents a number of challenges. Some of these challenges are similar to those reported in the educational literature on peer review in other academic disciplines, but reviewing code presents unique difficulties. Better understanding these challenges and the conditions under which code review can be taught and implemented successfully in computer science courses is of value to the computing education community. In this work, we conduct a systematic review of the literature on peer code review in higher education to examine instructor motivations for conducting peer code review activities, how such activities have been implemented in practice, and the primary benefits and difficulties that have been reported. We initially identified 187 potential studies and analyzed 51 empirical studies pertinent to our goals. We report the most commonly cited benefits (e.g., the development of programming-related skills) and barriers (e.g., low student engagement), and we identify a wide variety of tools that have been used to facilitate the peer code review process. While we argue that more empirical work is needed to validate currently reported results related to learning outcomes, there is also a clear need to address the challenges around student motivation, which we believe could be an important avenue for future research.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Deep learning; Employment; Feedback; Job analysis; Software engineering; Automated question generation; BART; Interview question generation; Language processing; Natural language processing; Natural languages; Recruitment automation; Reinforcement learning from human feedback; Reinforcement learnings; Technical interview; Automation</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>Peer review; code review; higher education; peer code review; programming course; systematic literature review; systematic review</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
@@ -1060,12 +1078,12 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1073,26 +1091,22 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Comparative analysis study of open source GIS in Malaysia</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Open source origin might appear like a major prospective change which is qualified to deliver in various industries and also competing means in developing countries. The leading purpose of this research study is to basically discover the degree of adopting Open Source Software (OSS) that is connected with Geographic Information System (GIS) application within Malaysia. It was derived based on inadequate awareness with regards to the origin ideas or even on account of techie deficiencies in the open origin instruments. This particular research has been carried out based on two significant stages; the first stage involved a survey questionnaire: to evaluate the awareness and acceptance level based on the comparison feedback regarding OSS and commercial GIS. This particular survey was conducted among three groups of candidates: government servant, university students and lecturers, as well as individual. The approaches of measuring awareness in this research were based on a comprehending signal plus a notion signal for each survey questions. These kinds of signs had been designed throughout the analysis in order to supply a measurable and also a descriptive signal to produce the final result. The second stage involved an interview session with a major organization that carries out available origin internet GIS; the Federal Department of Town and Country Planning Peninsular Malaysia (JPBD). The impact of this preliminary study was to understand the particular viewpoint of different groups of people on the available origin, and also their insufficient awareness with regards to origin ideas as well as likelihood may be significant root of adopting level connected with available origin options. © Published under licence by IOP Publishing Ltd.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Malaysia; Developing countries; Open source software; Remote sensing; Software engineering; Surveys; Comparative analysis; Federal Department; Internet GIS; Malaysia; Open sources; Open-source GIS; Research studies; University students; comparative study; developing world; GIS; instrumentation; questionnaire survey; software; urban planning; Geographic information systems</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>Gender Discrimination in the Hiring of Skilled Professionals in Two Male-Dominated Occupational Fields: A&amp;#xa0;Factorial Survey Experiment with Real-World Vacancies and Recruiters in Four European Countries</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
@@ -1101,12 +1115,12 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Scopus</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1114,26 +1128,22 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Searching, examining, and exploiting in-demand technical (SEE IT) skills using web data mining</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>There has always been a mismatch between academic education and industry demands in various industry fields. Especially, in the computer related jobs such as software developers or engineers, employers and job seekers are experiencing a large curriculum or skill gap compared to other industry fields due to its fast-changing nature. In order to minimize the gap, identifying the current job skill trends and offering/learning relevant skills are critically important for both educators and students in the fast-paced job market. However, due to the lack of relative information about the trends of in demand technical skills in certain regions or around the nation, it is difficult for educators to keep up with these changes and determine what needs to be conveyed to students so they can be ready for the job on day one. In this paper, in order to address these challenges, we focused on the analysis of in demand technical skills and their trends in software developer and engineer jobs around the nation. We collected and analyzed over 120,000 software developer or engineer job postings and summarized demanding and required skills from different regions throughout the nation. © 2020 Knowledge Systems Institute Graduate School. All rights reserved.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Curricula; Engineers; Software engineering; Students; Academic education; Job postings; Job seekers; Job skills; Relative information; Software developer; Technical skills; Web data mining; Data mining</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>IC1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>Web-Based Human Resource Information System Design AT PT. Cakra Mandala Sakti Surabaya</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
@@ -1147,7 +1157,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1155,18 +1165,22 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Gender Discrimination in Hiring Decisions: Evidence from a Field Experiment</t>
+          <t>Topic Modeling for&amp;#xa0;Skill Extraction from&amp;#xa0;Job Postings</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1180,7 +1194,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1188,7 +1202,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Uncovering the skillsets required in computer science jobs using social network analysis</t>
+          <t>Blockchain-Enabled Intelligent Solution Using Structured Equation Modelling Based on the UTAUT Framework</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
@@ -1196,10 +1210,14 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
@@ -1213,7 +1231,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1221,7 +1239,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>AI ethics and governance in business management: challenges, opportunities, and a comparative analysis</t>
+          <t>A theory of factors affecting continuous experimentation (FACE)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -1229,10 +1247,14 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
@@ -1241,12 +1263,12 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1254,26 +1276,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Synthesising Privacy by Design Knowledge Toward Explainable Internet of Things Application Designing in Healthcare</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Privacy by Design (PbD) is the most common approach followed by software developers who aim to reduce risks within their application designs, yet it remains commonplace for developers to retain little conceptual understanding of what is meant by privacy. A vision is to develop an intelligent privacy assistant to whom developers can easily ask questions to learn how to incorporate different privacy-preserving ideas into their IoT application designs. This article lays the foundations toward developing such a privacy assistant by synthesising existing PbD knowledge to elicit requirements. It is believed that such a privacy assistant should not just prescribe a list of privacy-preserving ideas that developers should incorporate into their design. Instead, it should explain how each prescribed idea helps to protect privacy in a given application design context—this approach is defined as “Explainable Privacy.” A total of 74 privacy patterns were analysed and reviewed using ten different PbD schemes to understand how each privacy pattern is built and how each helps to ensure privacy. Due to page limitations, we have presented a detailed analysis in Reference [3]. In addition, different real-world Internet of Things (IoT) use-cases, including a healthcare application, were used to demonstrate how each privacy pattern could be applied to a given application design. By doing so, several knowledge engineering requirements were identified that need to be considered when developing a privacy assistant. It was also found that, when compared to other IoT application domains, privacy patterns can significantly benefit healthcare applications. In conclusion, this article identifies the research challenges that must be addressed if one wishes to construct an intelligent privacy assistant that can truly augment software developers’ capabilities at the design phase.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Internet of Things; privacy; privacy by design; privacy assistant; knowledge engineering; healthcare; explainable privacy</t>
-        </is>
-      </c>
+          <t>A Literature Review Based Insight into Agile Mindset Through a Lens of Six C’s Grounded Theory Model</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
@@ -1282,12 +1300,12 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1295,26 +1313,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>A Review of Peer Code Review in Higher Education</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Peer review is the standard process within academia for maintaining publication quality, but it is also widely employed in other settings, such as education and industry, for improving work quality and for generating actionable feedback to content authors. For example, in the software industry peer review of program source code—or peer code review—is a key technique for detecting bugs and maintaining coding standards. In a programming education context, although peer code review offers potential benefits to both code reviewers and code authors, individuals are typically less experienced, which presents a number of challenges. Some of these challenges are similar to those reported in the educational literature on peer review in other academic disciplines, but reviewing code presents unique difficulties. Better understanding these challenges and the conditions under which code review can be taught and implemented successfully in computer science courses is of value to the computing education community. In this work, we conduct a systematic review of the literature on peer code review in higher education to examine instructor motivations for conducting peer code review activities, how such activities have been implemented in practice, and the primary benefits and difficulties that have been reported. We initially identified 187 potential studies and analyzed 51 empirical studies pertinent to our goals. We report the most commonly cited benefits (e.g., the development of programming-related skills) and barriers (e.g., low student engagement), and we identify a wide variety of tools that have been used to facilitate the peer code review process. While we argue that more empirical work is needed to validate currently reported results related to learning outcomes, there is also a clear need to address the challenges around student motivation, which we believe could be an important avenue for future research.</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Peer review; code review; higher education; peer code review; programming course; systematic literature review; systematic review</t>
-        </is>
-      </c>
+          <t>Within-project and cross-project defect prediction based on model averaging</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
@@ -1323,12 +1337,12 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1336,26 +1350,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>XCoS: Explainable Code Search Based on Query Scoping and Knowledge Graph</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>When searching code, developers may express additional constraints (e.g., functional constraints and nonfunctional constraints) on the implementations of desired functionalities in the queries. Existing code search tools treat the queries as a whole and ignore the different implications of different parts of the queries. Moreover, these tools usually return a ranked list of candidate code snippets without any explanations. Therefore, the developers often find it hard to choose the desired results and build confidence on them. In this article, we conduct a developer survey to better understand and address these issues and induct some insights from the survey results. Based on the insights, we propose XCoS, an explainable code search approach based on query scoping and knowledge graph. XCoS extracts a background knowledge graph from general knowledge bases like Wikidata and Wikipedia. Given a code search query, XCoS identifies different parts (i.e., functionalities, functional constraints, nonfunctional constraints) from it and use the expressions of functionalities and functional constraints to search the codebase. It then links both the query and the candidate code snippets to the concepts in the background knowledge graph and generates explanations based on the association paths between these two parts of concepts together with relevant descriptions. XCoS uses an interactive user interface that allows the user to better understand the associations between candidate code snippets and the query from different aspects and choose the desired results. Our evaluation shows that the quality of the extracted background knowledge and the concept linkings in codebase is generally high. Furthermore, the generated explanations are considered complete, concise, and readable, and the approach can help developers find the desired code snippets more accurately and confidently.</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Code search; explainability; knowledge; concept</t>
-        </is>
-      </c>
+          <t>Discovering smell relations between temporary field and design smells: an empirical analysis</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
@@ -1369,7 +1379,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1377,7 +1387,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Usage of&amp;#xa0;Generative Artificial Intelligence for&amp;#xa0;the&amp;#xa0;Design of&amp;#xa0;Graphic User Interfaces: Initial Approaches</t>
+          <t>Fairness-aware machine learning engineering: how far are we?</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1385,10 +1395,14 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
@@ -1402,7 +1416,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1410,7 +1424,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Achieving a Data-Driven Risk Assessment Methodology for Ethical AI</t>
+          <t>Measuring readiness for nurse-led shared decision making in clinical practice: development and first testing of the RSDM-N scale</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
@@ -1418,10 +1432,14 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -1430,12 +1448,12 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1443,26 +1461,22 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Impacts of an Industrial Partnership with a Historically Black University on the Computing Career Decisions of Black Undergraduate Students</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>In order to rectify the historical marginalization of Black workers in computing fields, many academic and industrial initiatives have been established to increase the diversity and inclusion in the tech industry. In this study, we explored how one particular post-secondary education program at one historically black institution known as the Google in Residence (GIR) program impacted students’ interests and their pursuit of computing-related careers. Data on employment outcomes at this institution showed that the GIR participants who obtained internships and full-time employment at Google were predominantly international students, not African American students who make up the majority of the undergraduate student and about half of the GIR participants. To understand this phenomenon better, we interviewed 27 students who spanned all 4 years of study and included African American and international students. The interviews were structured to elicit a wide range of factors influencing career decisions. Our analysis describes the impact of a particular GIR introductory-level programming course and other GIR program impacts beyond the introductory-level course. We found that the GIR introductory course was engaging, inspired students to change their degree in a more computing-oriented direction and supported internship applications. The informational workshops, networking events, mock-interviews, and advising of the computer science club, which were supported by the GIR program, built students’ confidence in interviewing and obtaining full-time employment within the tech industry. While the GIR course and program had a positive influence on students of all backgrounds, the reputation of Google was especially motivating for international students. However, the African American students in this study generally had career aspirations and goals that were less tied to specific companies or industries. Based on our findings, potential improvements could include broadening awareness and access of the GIR course to non-computer science majors, offering summer programs to increase students’ computational confidence, and increasing the diversity of GIR and computer science instructors.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>inclusion; internships; industrial partnerships</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>What makes a code review useful to OpenDev developers? An empirical investigation</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -1476,7 +1490,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1484,7 +1498,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Workplace Experiences of Muslim Women in STEM in Canada: An Intersectional Qualitative Analysis</t>
+          <t>Impact of Big Data and Artificial Intelligence on Industry: Developing a Workforce Roadmap for a Data Driven Economy</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -1492,10 +1506,14 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -1509,7 +1527,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1517,7 +1535,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Revolutionizing software developmental processes by utilizing continuous software approaches</t>
+          <t>An Application with Fuzzy AHP for Making the Assignment Aimed at the Holistic Benefit Over the Person Evaluation as Required by the Requirements and Evaluations of Individuals</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -1525,10 +1543,14 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
@@ -1537,12 +1559,12 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1550,18 +1572,30 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>On Using Large Language Models Pre-trained on&amp;#xa0;Digital Twins as&amp;#xa0;Oracles to&amp;#xa0;Foster the&amp;#xa0;Use of&amp;#xa0;Formal Methods in&amp;#xa0;Practice</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+          <t>ATE-FS: An Average Treatment Effect-Based Feature Selection Technique for Software Fault Prediction</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>In software development, software fault prediction (SFP) models aim to identify code sections with a high likelihood of faults before the testing process. SFP models achieve this by analyzing data about the structural properties of the software’s previous versions. Consequently, the accuracy and interpretation of SFP models depend heavily on the chosen software metrics and how well they correlate with patterns of fault occurrence. Previous research has explored improving SFP model performance through feature selection (metric selection). Yet inconsistencies in conclusions arose due to the presence of inconsistent and correlated software metrics. Relying solely on correlations between metrics and faults makes it difficult for developers to take actionable steps, as the causal relationships remain unclear. To address this challenge, this work investigates the use of Causal Inference (CI) methods to understand the causal relationships between software project characteristics, development practices, and the fault-proneness of code sections. We propose a CI-based technique called Average Treatment Effect for Feature Selection (ATE-FS). This technique leverages the CI concept to quantify the cause-and-effect relationships between software metrics and fault-proneness. ATE-FS utilizes Average Treatment Effect (ATE) features to identify code metrics that are most suitable for building SFP models. These ATE features capture the causal impact of a metric on fault-proneness. Through an experimental analysis involving twenty-seven SFP datasets, we validate the performance of ATE-FS. We further compare its performance with other state-of-the-art feature selection techniques. The results demonstrate that ATE-FS achieves a significant performance for fault prediction. Additionally, ATE-FS improved consistency in feature selection across diverse SFP datasets.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Software Fault Prediction; Causal Inference; Average Treatment Effect; Empirical Analysis</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -1575,7 +1609,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1583,7 +1617,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>From Requirements to Prototyping: Proposal and Evaluation of an Artifact to Support Interface Design in the Context of Autism</t>
+          <t>UMLDS: A Round-Trip Engineering Support Tool to&amp;#xa0;Avoid Unintended Design Changes</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -1591,10 +1625,14 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -1608,7 +1646,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1616,7 +1654,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Enhancing continuous integration predictions: a hybrid LSTM-GRU deep learning framework with evolved DBSO algorithm</t>
+          <t>A snapshot of cancer in Chile II: an update on research, strategies and analytical frameworks for equity, innovation and national development</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
@@ -1627,7 +1665,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
@@ -1641,7 +1683,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1649,7 +1691,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Technology, multidisciplinarianism, and the university</t>
+          <t>The Eco-label Blue Angel for Software—Development and Components</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
@@ -1657,10 +1699,14 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -1674,7 +1720,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1682,7 +1728,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>An Automated Approach to&amp;#xa0;Identify Source Code Files Affected by&amp;#xa0;Architectural Technical Debt</t>
+          <t>Biochemical-free enrichment or depletion of RNA classes in real-time during direct RNA sequencing with RISER</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
@@ -1690,10 +1736,14 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
@@ -1707,7 +1757,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1715,7 +1765,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Documenting research software in engineering science</t>
+          <t>Spaceward senses: examining retronasal aroma and mouthfeel perception in simulated space-microgravity environments</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
@@ -1723,10 +1773,14 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
@@ -1740,7 +1794,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1748,7 +1802,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>What is an app store? The software engineering perspective</t>
+          <t>Competitiveness Through Development of Strategic Talent Management and Agile Management Ecosystems</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -1756,10 +1810,14 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
@@ -1773,7 +1831,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1781,7 +1839,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Prioritizing unit tests using object-oriented metrics, centrality measures, and machine learning algorithms</t>
+          <t>IT Project Management Complexity Framework: Managing and&amp;#xa0;Understanding Complexity in&amp;#xa0;IT Projects in&amp;#xa0;a&amp;#xa0;Remote Working Environment</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
@@ -1789,10 +1847,14 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
@@ -1806,7 +1868,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1814,7 +1876,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>A comprehensive analysis of challenges and strategies for software release notes on GitHub</t>
+          <t>Marketplace for Multi-party Development of Artificial Intelligence Systems: Perceptions on Value Creation</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
@@ -1822,10 +1884,14 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
@@ -1839,7 +1905,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1847,7 +1913,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>A data-driven API recommendation approach for service mashup composition</t>
+          <t>A comprehensive analysis of challenges and strategies for software release notes on GitHub</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
@@ -1855,10 +1921,14 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
@@ -1872,7 +1942,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1880,7 +1950,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Productivity with&amp;#xa0;AI During the&amp;#xa0;Development of&amp;#xa0;an&amp;#xa0;ISMS: Case Kempower</t>
+          <t>It Takes a Village</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
@@ -1888,10 +1958,14 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
@@ -1905,7 +1979,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1913,18 +1987,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Potential Candidate Selection Using Information Extraction and Skyline Queries</t>
+          <t>Candidate Classification and Skill Recommendation in a CV Recommender System</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
       <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
@@ -1938,7 +2016,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1946,7 +2024,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Creating of a General Purpose Language for the Construction of Dynamic Reports</t>
+          <t>Can instability variations warn developers when open-source projects boost?</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr"/>
@@ -1954,10 +2032,14 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
@@ -1971,7 +2053,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1979,7 +2061,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Method for Eliciting Requirements in the Area of Digital Sovereignty (MERDigS)</t>
+          <t>Empowering Digital Innovation by Diverse Leadership in ICT – A Roadmap to a Better Value System in Computer Algorithms</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr"/>
@@ -1987,10 +2069,14 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC3</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
@@ -2004,7 +2090,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2012,7 +2098,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Gender disparity in U.S. patenting</t>
+          <t>Energy Efficient Software in&amp;#xa0;an&amp;#xa0;Engineering Course</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr"/>
@@ -2020,10 +2106,14 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
@@ -2037,7 +2127,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2045,7 +2135,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>AI Driving Game Changing Trends in Project Delivery and Enterprise Performance</t>
+          <t>Developers talking about code quality</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr"/>
@@ -2056,7 +2146,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
@@ -2070,7 +2164,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2078,7 +2172,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Runtime monitoring of operational design domain to safeguard machine learning components</t>
+          <t>Fuzzy Reinforcement Learning Algorithm for Efficient Task Scheduling in Fog-Cloud IoT-Based Systems</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr"/>
@@ -2086,10 +2180,14 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
@@ -2103,7 +2201,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -2111,7 +2209,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>&lt;span&gt;prompt4vis&lt;/span&gt;: prompting large language models with example mining for tabular data visualization</t>
+          <t>Understanding the need for assistance in software modeling: interviews with experts</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
@@ -2119,10 +2217,14 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
@@ -2136,7 +2238,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -2144,7 +2246,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Operationalising AI governance through ethics-based auditing: an industry case study</t>
+          <t>New product development process and case studies for deep-tech academic research to commercialization</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
@@ -2152,10 +2254,14 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -2169,7 +2275,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -2177,7 +2283,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Research, Learning, and Innovation Through Industry-Academia Synergy with the Industry Interaction Cell Model</t>
+          <t>Decision support software-guided medication reviews in elderly patients with polypharmacy: a prospective analysis of routine data from community pharmacies (OPtiMed study protocol)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
@@ -2185,10 +2291,14 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -2197,12 +2307,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -2210,18 +2320,30 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Data-access performance anti-patterns in data-intensive systems</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
+          <t>SIP: Optimal Product Selection from Feature Models Using Many-Objective Evolutionary Optimization</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>A feature model specifies the sets of features that define valid products in a software product line. Recent work has considered the problem of choosing optimal products from a feature model based on a set of user preferences, with this being represented as a many-objective optimization problem. This problem has been found to be difficult for a purely search-based approach, leading to classical many-objective optimization algorithms being enhanced either by adding in a valid product as a seed or by introducing additional mutation and replacement operators that use an SAT solver. In this article, we instead enhance the search in two ways: by providing a novel representation and by optimizing first on the number of constraints that hold and only then on the other objectives. In the evaluation, we also used feature models with realistic attributes, in contrast to previous work that used randomly generated attribute values. The results of experiments were promising, with the proposed (SIP) method returning valid products with six published feature models and a randomly generated feature model with 10,000 features. For the model with 10,000 features, the search took only a few minutes.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Product selection</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
@@ -2235,7 +2357,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -2243,7 +2365,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Configuring Participatory Design of ICT for Aging Well as Matters of Care</t>
+          <t>Exploring and Characterizing Ad-Hoc Requirements - A Case Study at a Large-Scale Systems Provider</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
@@ -2251,10 +2373,14 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>EC2; EC4</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
@@ -2268,7 +2394,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -2276,7 +2402,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Revolutionizing User Testing: AI-Powered Feedback with Personalized Personas</t>
+          <t>What distinguishes great software engineers?</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
@@ -2284,10 +2410,14 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
@@ -2301,7 +2431,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -2309,7 +2439,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Competing for Technology Talent: Listed Companies Versus Funded Startups in India</t>
+          <t>Intervention Model with Data Mining Techniques to Work with Dating Violence Victims Using a Social Support Network</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr"/>
@@ -2317,10 +2447,14 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
@@ -2334,7 +2468,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -2342,7 +2476,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>A meta-analysis on social exchange relationships and employee innovation in teams</t>
+          <t>Contextual Personas - A Method for Capturing the Digital Work Environment of Users</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
@@ -2350,10 +2484,14 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
@@ -2367,7 +2505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -2375,7 +2513,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Modelling the quantification of requirements technical debt</t>
+          <t>Distribution-free Bayesian analyses with the DFBA statistical package</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
@@ -2386,7 +2524,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
@@ -2395,12 +2537,12 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Web of Science</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -2408,17 +2550,17 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Inductive Synthesis of Structurally Recursive Functional Programs from Non-recursive Expressions</t>
+          <t>Analysis of Agile Project Manager Competencies From Recruitment Signals</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>We present a novel approach to synthesizing recursive functional programs from input-output examples. Synthesizing a recursive function is challenging because recursive subexpressions should be constructed while the target function has not been fully defined yet. We address this challenge by using a new technique we call block-based pruning. A block refers to a recursion- and conditional-free expression (i.e., straight-line code) that yields an output from a particular input. We first synthesize as many blocks as possible for each input-output example, and then we explore the space of recursive programs, pruning candidates that are inconsistent with the blocks. Our method is based on an efficient version space learning, thereby effectively dealing with a possibly enormous number of blocks. In addition, we present a method that uses sampled input-output behaviors of library functions to enable a goal-directed search for a recursive program using the library. We have implemented our approach in a system called Trio and evaluated it on synthesis tasks from prior work and on new tasks. Our experiments show that Trio outperforms prior work by synthesizing a solution to 98% of the benchmarks in our benchmark suite.</t>
+          <t>As Agile project management has become increasingly popular as a project management methodology, Agile project managers (AgPM) are important in leading and managing Agile projects. However, professional project management bodies and the academic literature lag behind industry practices in articulating competency frameworks for understanding the requirements of AgPM. This study examines the organizational expectations for AgPM competencies as signaled to the job market through advertisements. Using an integrated framework of Agile project competencies, we conduct a content analysis of AgPM job advertisements from the Australian and New Zealand job market. Our results identified the frequently signaled personal, practice and perspective competencies, including the co-occurrences of these competencies, for recruiting AgPM. Additionally, we identified the more frequently utilized individual personal and project-related practice competencies, as well as the less utilized Agile-focused perspective competencies. The findings of this study will help the Agile movement consider the competencies that are more important for organizations to learn; allow employers to articulate their competency requirements for potential jobs; and enable job seekers to understand and develop the required competencies for successful application to AgPM roles. Overall, this study provides an empirical grounding in the specific competencies required for the AgPM role in industry.</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Programming by Example; Recursive Functional Programs; Synthesis</t>
+          <t>Organizations; Project management; Recruitment; Software; Uncertainty; Stakeholders; Receivers; Agile project management (APM); Agile project manager (AgPM); competencies; job advertisements; signaling theory</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2427,7 +2569,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
@@ -2436,12 +2582,12 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Web of Science</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -2449,18 +2595,30 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Dynamic Retrieval Augmented Generation of Ontologies using Artificial Intelligence (DRAGON-AI)</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>Open Source Resume (OSR): A Visualization Tool for Presenting OSS Biographies of Developers</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>In order to recruit appropriate developers for software projects, it is important to have a clarified understanding on the practical experience and expertise of each candidate. However, traditional resume only shows experiences claimed by developers, and very few evidence or information regarding their actual development activities can be obtained. In this paper, we propose an approach to extract developers' practical activities from their participated open source software (OSS) projects, and generate the biographies that reflect their OSS contributions. We applied the approach on the largest code hosting service, GitHub. By investigating the resumes generated from the extracted dataset, recruiters of software projects can be given a clearer view on whether the developers' experiences fulfill the qualifications. Moreover, based on the approach, we present a web-based visualization tool, named as Open Source Resume (OSR). We believe our tool is useful to help recruiters from software development organizations to search for suitable developers, and then construct development teams in software projects based on their OSS contributions.</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Open Source Software; Mining Software Repositories; Developer Expertise; Visualization Tool</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC3</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
@@ -2469,12 +2627,12 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>248</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -2482,18 +2640,30 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Iran Obesity and Metabolic Surgery (IOMS) Cohort Study: Rationale and Design</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
+          <t>Applications and Challenges of Fairness APIs in Machine Learning Software</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning software systems are frequently used in our day-to-day lives. Some of these systems are used in various sensitive environments to make life-changing decisions. Therefore, it is crucial to ensure that these AI/ML systems do not make any discriminatory decisions for any specific groups or populations. In that vein, different bias detection and mitigation open-source software libraries (aka API libraries) are being developed and used. In this paper, we conduct a qualitative study to understand in what scenarios these open-source fairness APIs are used in the wild, how they are used, and what challenges the developers of these APIs face while developing and adopting these libraries. We have analyzed 204 GitHub repositories (from a list of 1885 candidate repositories) which used 13 APIs that are developed to address bias in ML software. We found that these APIs are used for two primary purposes (i.e., learning and solving real-world problems), targeting 17 unique use-cases. Our study suggests that developers are not well-versed in bias detection and mitigation; they face lots of troubleshooting issues, and frequently ask for opinions and resources. Our findings can be instrumental for future bias-related software engineering research, and for guiding educators in developing more state-of-the-art curricula.</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>bias; api; github; fairness</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
@@ -2502,12 +2672,12 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>249</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -2515,18 +2685,30 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Towards fair machine learning using combinatorial methods</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
+          <t>Searching entangled program spaces</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Many problem domains, including program synthesis and rewrite-based optimization, require searching astronomically large spaces of programs. Existing approaches often rely on building specialized data structures—version-space algebras, finite tree automata, or e-graphs—to compactly represent such spaces. At their core, all these data structures exploit independence of subterms; as a result, they cannot efficiently represent more complex program spaces, where the choices of subterms are entangled. We introduce equality-constrained tree automata (ECTAs), a new data structure, designed to compactly represent large spaces of programs with entangled subterms. We present efficient algorithms for extracting programs from ECTAs, implemented in a performant Haskell library, ecta. Using the ecta library, we construct Hectare, a type-driven program synthesizer for Haskell. Hectare significantly outperforms a state-of-the-art synthesizer Hoogle+—providing an average speedup of 8\texttimes{}—despite its implementation being an order of magnitude smaller.</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Haskell; e-graphs; program synthesis; type systems</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
@@ -2535,12 +2717,12 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -2548,18 +2730,30 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>The Personalized Learning Interaction Framework in Practice (PLIFs): Current Implementations According to Chief Learning Officers and Learning Leaders</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
+          <t>“I Want It That Way”: Enabling Interactive Decision Support Using Large Language Models and Constraint Programming</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>A critical factor in the success of many decision support systems is the accurate modeling of user preferences. Psychology research has demonstrated that users often develop their preferences during the elicitation process, highlighting the pivotal role of system-user interaction in developing personalized systems. This paper introduces a novel approach, combining Large Language Models (LLMs) with Constraint Programming to facilitate interactive decision support. We study this hybrid framework through the lens of meeting scheduling, a time-consuming daily activity faced by a multitude of information workers. We conduct three studies to evaluate the novel framework, including a diary study to characterize contextual scheduling preferences, a quantitative evaluation of the system’s performance, and a user study to elicit insights with a technology probe that encapsulates our framework. Our work highlights the potential for a hybrid LLM and optimization approach for iterative preference elicitation, and suggests design considerations for building systems that support human-system collaborative decision-making processes.</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Decision support; large language models; constraint programming; preference elicitation; meeting scheduling</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>EC2</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
@@ -2568,12 +2762,12 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -2581,18 +2775,30 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Gamification in software engineering: the mediating role of developer engagement and job satisfaction</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
+          <t>Automated Soap Opera Testing Directed by LLMs and Scenario Knowledge: Feasibility, Challenges, and Road Ahead</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Exploratory testing (ET) harnesses tester's knowledge, creativity, and experience to create varying tests that uncover unexpected bugs from the end-user's perspective. Although ET has proven effective in system-level testing of interactive systems, the need for manual execution has hindered large-scale adoption. In this work, we explore the feasibility, challenges and road ahead of automated scenario-based ET (a.k.a soap opera testing). We conduct a formative study, identifying key insights for effective manual soap opera testing and challenges in automating the process. We then develop a multi-agent system leveraging LLMs and a Scenario Knowledge Graph (SKG) to automate soap opera testing. The system consists of three multi-modal agents, Planner, Player, and Detector that collaborate to execute tests and identify potential bugs. Experimental results demonstrate the potential of automated soap opera testing, but there remains a significant gap compared to manual execution, especially under-explored scenario boundaries and incorrectly identified bugs. Based on the observation, we envision road ahead for the future of automated soap opera testing, focusing on three key aspects: the synergy of neural and symbolic approaches, human-AI co-learning, and the integration of soap opera testing with broader software engineering practices. These insights aim to guide and inspire the future research.</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge Graph; Large Language Models; Soap Opera Testing</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
@@ -2601,12 +2807,12 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -2614,18 +2820,30 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Distribution-free Bayesian analyses with the DFBA statistical package</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
+          <t>A Survey of AI-Generated Content (AIGC)</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Recently, Artificial Intelligence Generated Content (AIGC) has gained significant attention from society, especially with the rise of Generative AI (GAI) techniques such as ChatGPT, GPT-4 [165], DALL-E-3 [184], and Sora [137]. AIGC involves using AI models to create digital content, such as images, music, and natural language, with the goal of making the content creation process more efficient and accessible. Large-scale models have become increasingly important in AIGC as they provide better intent extraction and generation results. This survey provides a comprehensive review of the history of generative models and recent advances in AIGC, focusing on both unimodal and multimodal interaction. From the perspective of unimodality, we introduce the generation tasks and relative models of text and image. From the perspective of multimodality, we introduce the cross-application between the modalities mentioned above. Finally, the survey discusses the existing open problems and future challenges in AIGC. Overall, this survey serves as a valuable resource for individuals interested in understanding the background and secrets behind the impressive performance of AIGC techniques.</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Generative AI; AI-generated content; multimodal machine learning</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
@@ -2634,12 +2852,12 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Web of Science</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -2647,26 +2865,30 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>The Evaluation of Founder Failure and Success by Hiring Firms: A Field Experiment</t>
+          <t>Bob or Bot: Exploring ChatGPT's Answers to University Computer Science Assessment</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Organizations tout the importance of innovation and entrepreneurship. Yet, when hiring it remains unclear how they evaluate entrepreneurial human capital-namely, job candidates with founder experience. How hiring firms evaluate this experience-and especially how this evaluation varies by entrepreneurial success and failure-reveals insights into the structures and processes within organizations. Organizations research points to two perspectives related to the evaluation of founder experience: Former founders may be advantaged, due to founder experience signaling high-quality capabilities and human capital, or disadvantaged, due to concerns related to fit and commitment. To identify the dominant class of mechanisms driving the evaluation of founder experience, it is important to consider how these evaluations differ, depending on whether the founder's venture failed or succeeded. To isolate demand-side mechanisms and hold supply-side factors constant, we conducted a field experiment. We sent applications varying the candidate's founder experience to 2,400 software engineering positions in the United States at random. We find that former founders received 43% fewer callbacks than nonfounders and that this difference is driven by older hiring firms. Further, this founder penalty is greatest for former successful founders, who received 33% fewer callbacks than former failed founders. Our results highlight that mechanisms related to concerns about fit and commitment, rather than information asymmetry about quality, are most influential when hiring firms evaluate former founders in our context.</t>
+          <t>Cheating has been a long-standing issue in university assessments. However, the release of ChatGPT and other free-to-use generative AI tools has provided a new and distinct method for cheating. Students can run many assessment questions through the tool and generate a superficially compelling answer, which may or may not be accurate.&amp;nbsp;We ran a dual-anonymous “quality assurance” marking exercise across four end-of-module assessments across a distance university computer science (CS) curriculum. Each marker received five ChatGPT-generated scripts alongside 10 student scripts. A total of 90 scripts were marked; every ChatGPT-generated script for the undergraduate modules received at least a passing grade (&amp;gt;40%), with all of the introductory module CS1 scripts receiving a distinction (&amp;gt;85%). None of the ChatGPT-taught postgraduate scripts received a passing grade (&amp;gt;50%). We also present the results of interviewing the markers and of running our sample scripts through a GPT-2 detector and the TurnItIn AI detector, which both identified every ChatGPT-generated script but differed in the number of false positives. As such, we contribute a baseline understanding of how the public release of generative AI is likely to significantly impact quality assurance processes. Our analysis demonstrates that in most cases, across a range of question formats, topics, and study levels, ChatGPT is at least capable of producing adequate answers for undergraduate assessment.</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>careers; entrepreneurship; evaluations; failure; experiment; founders; hiring; labor markets</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2; IC3; IC4; IC5</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>ChatGPT; generative AI; cheating; quality assurance; university assessment’</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
@@ -2675,12 +2897,12 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Web of Science</t>
+          <t>ACM Digital Library</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>401</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2688,17 +2910,17 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>ACHIEVING JOB PERFORMANCE FROM EMPOWERMENT THROUGH THE MEDIATION OF EMPLOYEE ENGAGEMENT: AN EMPIRICAL STUDY</t>
+          <t>Cat and Mouse Game: Patching Bureaucratic Work Relations by Patching Technologies</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>In present scenario, business organization understood the importance of sophisticated employee behavior for the development of overall job performance. It is important for an organization to perform effectively for that it enhances their employee's job performance. Many study supports that an empowered employee recognizes and attaches himself or herself with the wider extent of organizational objectives. An engaged employee has more ownership and able to contribute towards his/her own growth and overall productivity. Boston focuses on implementing feedback given by employees with immediate effect and has 43% employees who are highly engaged. Facebook has a culture of contribution and each employee is recognized for his contribution to the overall goal of the company "to make the world more open and connected ". This policy of contributing culture is communicated to all the candidates during recruitment process. That is why Facebook is not only known for being one of the most popular social networking platforms but for its highly engaging culture as well. Under this study, the focus is to understand the relationship between employee empowerment and job performance. The study also tries to explore empirically the mediating effect of employee engagement in this regard. It was conducted on IT sector in Delhi NCR region with a sample size of 182 employees. The finding of the study reflects that engagement has its mediation effect on job performance with respect to employee empowerment.</t>
+          <t>This article uses findings from a field study of the world's largest guaranteed employment scheme (NREGA) in India to understand how digital technology mediates work relations and power dynamics within a bureaucracy. In this initiative, upper-level bureaucrats in the south Indian state of Andhra Pradesh built a digital network to remove local discretion at the "last mile" of an implementation of NREGA. I show how digital infrastructure affords actors at both the first and last mile opportunities to modify software to control as well as subvert certain practices. This article refers to this dialectic phenomenon as "governance by patching" and defines it as a socio-technical instantiation of a top-down process that focuses on small changes, iterative, and political process for positive change. Governance by patching is, therefore, neither a purely technical process nor an exclusively administrative one. Rather, it refers to the ability to fix unanticipated problems that arise in the implementation of governance programs by altering the socio-technical systems. The struggle for power continues, but on the new digital terrain.</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Employee engagement; Employee empowerment; Job Performance; Mediation; Regression</t>
+          <t>bureaucracy; governance; ictd; infrastructures; last-mile; nrega; patching</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2707,7 +2929,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
@@ -2721,7 +2947,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>413</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -2729,17 +2955,17 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Transformative and Troublesome? Students' and Professional Programmers' Perspectives on Difficult Concepts in Programming</t>
+          <t>A Survey of AIOps in the Era of Large Language Models</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Programming skills are an increasingly desirable asset across disciplines; however, learning to program continues to be difficult for many students. To improve pedagogy, we need to better understand the concepts that students find difficult and which have the biggest impact on their learning. Threshold-concept theory provides a potential lens on student learning, focusing on concepts that are troublesome and transformative. However, there is still a lack of consensus as to what the most relevant threshold concepts in programming are. The challenges involved are related to concept granularity and to evidencing some of the properties expected of threshold concepts. In this article, we report on a qualitative study aiming to address some of these concerns. The study involved focus groups with undergraduate students of different-year groups as well as professional software developers so as to gain insights into how perspectives on concepts change over time. Four concepts emerged from the data, where the majority of participants agreed on their troublesome nature—including abstract classes and data structures. Some of these concepts are considered transformative, too, but the evidence base is weaker. However, even though these concepts may not be considered transformative in the “big” sense of threshold concept theory, we argue the “soft” transformative effect of such concepts means they can provide important guidance for pedagogy and the design of programming courses. Further analysis of the data identified additional concepts that may hinder rather than help the learning of these threshold concepts, which we have called “accidental complexities.” We conclude the article with a critique of the use of threshold concepts as a lens for studying students’ learning of programming.</t>
+          <t>As large language models (LLMs) grow increasingly sophisticated and pervasive, their application to various Artificial Intelligence for IT Operations (AIOps) tasks has garnered significant attention. However, a comprehensive understanding of the impact, potential, and limitations of LLMs in AIOps remains in its infancy. To address this gap, we conducted a detailed survey of LLM4AIOps, focusing on how LLMs can optimize processes and improve outcomes in this domain. We analyzed 183 research articles published between January 2020 and December 2024 to answer four key research questions (RQs). In RQ1, we examine the diverse failure data sources utilized, including advanced LLM-based processing techniques for legacy data and the incorporation of new data sources enabled by LLMs. RQ2 explores the evolution of AIOps tasks, highlighting the emergence of novel tasks and the publication trends across these tasks. RQ3 investigates the various LLM-based methods applied to address AIOps challenges. Finally, RQ4 reviews evaluation methodologies tailored to assess LLM-integrated AIOps approaches. Based on our findings, we discuss the state-of-the-art advancements and trends, identify gaps in existing research, and propose promising directions for future exploration.</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Threshold concepts; accidental complexities; computer science curriculum; focus groups; learning programming</t>
+          <t>Large language model; AIOps; metrics; logs; time series; incident report; failure perception; anomaly detection; root cause analysis; assisted remediation</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2748,7 +2974,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
@@ -2762,7 +2992,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>420</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2770,17 +3000,17 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Can GPT-4 Replicate Empirical Software Engineering Research?</t>
+          <t>Virtual Environment Model Generation for CPS Goal Verification using Imitation Learning</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Empirical software engineering research on production systems has brought forth a better understanding of the software engineering process for practitioners and researchers alike. However, only a small subset of production systems is studied, limiting the impact of this research. While software engineering practitioners could benefit from replicating research on their own data, this poses its own set of challenges, since performing replications requires a deep understanding of research methodologies and subtle nuances in software engineering data. Given that large language models (LLMs), such as GPT-4, show promise in tackling both software engineering- and science-related tasks, these models could help replicate and thus democratize empirical software engineering research.In this paper, we examine GPT-4’s abilities to perform replications of empirical software engineering research on new data. We specifically study their ability to surface assumptions made in empirical software engineering research methodologies, as well as their ability to plan and generate code for analysis pipelines on seven empirical software engineering papers. We perform a user study with 14 participants with software engineering research expertise, who evaluate GPT-4-generated assumptions and analysis plans (i.e., a list of module specifications) from the papers. We find that GPT-4 is able to surface correct assumptions, but struggles to generate ones that apply common knowledge about software engineering data. In a manual analysis of the generated code, we find that the GPT-4-generated code contains correct high-level logic, given a subset of the methodology. However, the code contains many small implementation-level errors, reflecting a lack of software engineering knowledge. Our findings have implications for leveraging LLMs for software engineering research as well as practitioner data scientists in software teams.</t>
+          <t>Cyber-Physical Systems (CPS) continuously interact with their physical environments through embedded software controllers that observe the environments and determine actions. Field Operational Tests (FOT) are essential to verify to what extent the CPS under analysis can achieve certain CPS goals, such as satisfying the safety and performance requirements, while interacting with the real operational environment. However, performing many FOTs to obtain statistically significant verification results is challenging due to its high cost and risk in practice. Simulation-based verification can be an alternative to address the challenge, but it still requires an accurate virtual environment model that can replace the real environment interacting with the CPS in a closed loop.In this article, we propose ENVI (ENVironment Imitation), a novel approach to automatically generate an accurate virtual environment model, enabling efficient and accurate simulation-based CPS goal verification in practice.To do this, we first formally define the problem of the virtual environment model generation and solve it by leveraging Imitation Learning (IL), which has been actively studied in machine learning to learn complex behaviors from expert demonstrations. The key idea behind the model generation is to leverage IL for training a model that imitates the interactions between the CPS controller and its real environment as recorded in (possibly very small) FOT logs. We then statistically verify the goal achievement of the CPS by simulating it with the generated model. We empirically evaluate ENVI by applying it to the verification of two popular autonomous driving assistant systems. The results show that ENVI can reduce the cost of CPS goal verification while maintaining its accuracy by generating accurate environment models from only a few FOT logs. The use of IL in virtual environment model generation opens new research directions, further discussed at the end of the article.</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Large language models; study replication; empirical software engineering</t>
+          <t>Cyber-physical system (CPS); software controller; simulation-based CPS goal verification; environment modeling; imitation learning (IL)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2789,7 +3019,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
@@ -2803,7 +3037,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>440</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -2811,17 +3045,17 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Towards Automated Accessibility Report Generation for Mobile Apps</t>
+          <t>Relational program synthesis</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Many apps have basic accessibility issues, like missing labels or low contrast. To supplement manual testing, automated tools can help developers and QA testers find basic accessibility issues, but they can be laborious to use or require writing dedicated tests. To motivate our work, we interviewed eight accessibility QA professionals at a large technology company. From these interviews, we synthesized three design goals for accessibility report generation systems. Motivated by these goals, we developed a system to generate whole app accessibility reports by combining varied data collection methods (e.g., app crawling, manual recording) with an existing accessibility scanner. Many such scanners are based on single-screen scanning, and a key problem in whole app accessibility reporting is to effectively de-duplicate and summarize issues collected across an app. To this end, we developed a screen grouping model with 96.9% accuracy (88.8% F1-score) and UI element matching heuristics with 97% accuracy (98.2% F1-score). We combine these technologies in a system to report and summarize unique issues across an app, and enable a unique pixel-based ignore feature to help engineers and testers better manage reported issues across their app’s lifetime. We conducted a user study where 19 accessibility engineers and testers used multiple tools to create lists of prioritized issues in the context of an accessibility audit. Our system helped them create lists they were more satisfied with while addressing key limitations of current accessibility scanning tools.</t>
+          <t>This paper proposes relational program synthesis, a new problem that concerns synthesizing one or more programs that collectively satisfy a relational specification. As a dual of relational program verification, relational program synthesis is an important problem that has many practical applications, such as automated program inversion and automatic generation of comparators. However, this relational synthesis problem introduces new challenges over its non-relational counterpart due to the combinatorially larger search space. As a first step towards solving this problem, this paper presents a synthesis technique that combines the counterexample-guided inductive synthesis framework with a novel inductive synthesis algorithm that is based on relational version space learning. We have implemented the proposed technique in a framework called Relish, which can be instantiated to different application domains by providing a suitable domain-specific language and the relevant relational specification. We have used the Relish framework to build relational synthesizers to automatically generate string encoders/decoders as well as comparators, and we evaluate our tool on several benchmarks taken from prior work and online forums. Our experimental results show that the proposed technique can solve almost all of these benchmarks and that it significantly outperforms EUSolver, a generic synthesis framework that won the general track of the most recent SyGuS competition.</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>UI understanding; app crawling; accessibility</t>
+          <t>Counterexample Guided Inductive Synthesis; Relational Program Synthesis; Version Space Learning</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2830,7 +3064,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
@@ -2844,7 +3082,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>441</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -2852,17 +3090,17 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>"Innovative Technologies or Invasive Technologies?": Exploring Design Challenges of Privacy Protection With Smart Home in Jordan</t>
+          <t>Toward an Objective Measure of Developers’ Cognitive Activities</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>The growing adoption of smart devices has fuelled privacy concerns, and prior research has highlighted the privacy of bystanders: individuals who are subjected to the smart device use of others. Most of this research has focused on households in Western contexts (i.e., Europe and North America), but few studies have explored the design challenges of protecting bystanders, and even fewer have explored these in Muslim Arab Middle Eastern settings, such as Jordan.We conduct 44 interviews with users (i.e., families, domestic workers), local and international business leaders, and smart device designers to explore design challenges for privacy protection in the Jordanian context. Our analysis highlights the importance of considering contextual influences and power dynamics, localization and design guidelines, innovative technologies, awareness to design, and regulation. This paper concludes with recommendations for technical, social, business, and legal interventions to improve data protection design of smart devices in Jordan.</t>
+          <t>Understanding how developers carry out different computer science activities with objective measures can help to improve productivity and guide the use and development of supporting tools in software engineering. In this article, we present two controlled experiments involving 112 students to explore multiple computing activities (code comprehension, code review, and data structure manipulations) using three different objective measures including neuroimaging (functional near-infrared spectroscopy (fNIRS) and functional magnetic resonance imaging (fMRI)) and eye tracking. By examining code review and prose review using fMRI, we find that the neural representations of programming languages vs. natural languages are distinct. We can classify which task a participant is undertaking based solely on brain activity, and those task distinctions are modulated by expertise. We leverage insights from the psychological notion of spatial ability to decode the neural representations of several fundamental data structures and their manipulations using fMRI, fNIRS, and eye tracking. We examine list, array, tree, and mental rotation tasks and find that data structure and spatial operations use the same focal regions of the brain but to different degrees: they are related but distinct neural tasks. We demonstrate best practices and describe the implication and tradeoffs between fMRI, fNIRS, eye tracking, and self-reporting for software engineering research.</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>bystander; design; jordan; privacy; protection; security; smart device; smart home</t>
+          <t>Neuroimaging; code comprehension; data structures; eye tracking; prose review</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2871,7 +3109,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
@@ -2885,7 +3127,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>516</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -2893,26 +3135,26 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>On the Role of Structural Holes in Requirements Identification: An Exploratory Study on Open-Source Software Development</t>
+          <t>Gene Expressions, Hippocampal Volume Loss, and MMSE Scores in Computation of Progression and Pharmacologic Therapy Effects for Alzheimer's Disease</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Requirements identification is a human-centric activity that involves interaction among multiple stakeholders. Traditional requirements engineering (RE) techniques addressing stakeholders’ social interaction are mainly part of a centralized process intertwined with a specific phase of software development. However, in open-source software (OSS) development, stakeholders’ social interactions are often decentralized, iterative, and dynamic. Little is known about new requirements identification in OSS and the stakeholders’ organizational arrangements supporting such an activity. In this article, we investigate the theory of structural hole from the context of contributing new requirements in OSS projects. Structural hole theory suggests that stakeholders positioned in the structural holes in their social network are able to produce new ideas. In this study, we find that structural hole positions emerge in stakeholders’ social network and these positions are positively related to contributing a higher number of new requirements. We find that along with structural hole positions, stakeholders’ role is also an important part in identifying new requirements. We further observe that structural hole positions evolve over time, thereby identifying requirements to realize enriched features. Our work advances the fundamental understanding of the RE process in a decentralized environment and opens avenues for improved techniques supporting this process.</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Requirements identification; brokerage; open-source requirements engineering; social capital; social information foraging theory; stakeholders’ social network; structural hole</t>
-        </is>
-      </c>
+          <t>We build personalized relevance parameterization method (&amp;lt;sc&amp;gt;pr&amp;lt;/sc&amp;gt;e&amp;lt;sc&amp;gt;p-ad&amp;lt;/sc&amp;gt;) based on artificial intelligence (&amp;lt;sc&amp;gt;ai&amp;lt;/sc&amp;gt;) techniques to compute Alzheimer's disease (&amp;lt;sc&amp;gt;ad&amp;lt;/sc&amp;gt;) progression for patients at the mild cognitive impairment (&amp;lt;sc&amp;gt;mci&amp;lt;/sc&amp;gt;) stage. Expressions of &amp;lt;sc&amp;gt;ad&amp;lt;/sc&amp;gt; related genes, mini mental state examination (&amp;lt;sc&amp;gt;mmse&amp;lt;/sc&amp;gt;) scores, and hippocampal volume measurements of &amp;lt;sc&amp;gt;mci&amp;lt;/sc&amp;gt; patients are obtained from the Alzheimer‘s Disease Neuroimaging Initiative (&amp;lt;sc&amp;gt;adni&amp;lt;/sc&amp;gt;) database. In evaluation of cognitive changes under pharmacological therapies, patients are grouped based on available clinical measurements and the type of therapy administered, namely donepezil monotherapy and polytherapy of donepezil with memantine. Average leave one out cross validation (&amp;lt;sc&amp;gt;loocv&amp;lt;/sc&amp;gt;) error rates are calculated for &amp;lt;sc&amp;gt;pr&amp;lt;/sc&amp;gt;e&amp;lt;sc&amp;gt;p-ad&amp;lt;/sc&amp;gt; results as less than 8 percent when &amp;lt;sc&amp;gt;mmse&amp;lt;/sc&amp;gt; scores are used to compute disease progression for a 60 month period, and 3 percent with hippocampal volume measurements for 12 months. Statistical significance is calculated as &amp;lt;inline-formula&amp;gt;&amp;lt;tex-math notation="LaTeX"&amp;gt;$p = 0.003$&amp;lt;/tex-math&amp;gt;&amp;lt;alternatives&amp;gt;&amp;lt;mml:math&amp;gt;&amp;lt;mml:mrow&amp;gt;&amp;lt;mml:mi&amp;gt;p&amp;lt;/mml:mi&amp;gt;&amp;lt;mml:mo&amp;gt;=&amp;lt;/mml:mo&amp;gt;&amp;lt;mml:mn&amp;gt;0&amp;lt;/mml:mn&amp;gt;&amp;lt;mml:mo&amp;gt;.&amp;lt;/mml:mo&amp;gt;&amp;lt;mml:mn&amp;gt;003&amp;lt;/mml:mn&amp;gt;&amp;lt;/mml:mrow&amp;gt;&amp;lt;/mml:math&amp;gt;&amp;lt;inline-graphic xlink:href="saribudak-ieq1-2870363.gif"/&amp;gt;&amp;lt;/alternatives&amp;gt;&amp;lt;/inline-formula&amp;gt; for using &amp;lt;sc&amp;gt;ad&amp;lt;/sc&amp;gt; related genes in disease progression and as &amp;lt;inline-formula&amp;gt;&amp;lt;tex-math notation="LaTeX"&amp;gt;$p &amp;lt; 0.05$&amp;lt;/tex-math&amp;gt;&amp;lt;alternatives&amp;gt;&amp;lt;mml:math&amp;gt;&amp;lt;mml:mrow&amp;gt;&amp;lt;mml:mi&amp;gt;p&amp;lt;/mml:mi&amp;gt;&amp;lt;mml:mo&amp;gt;&amp;lt;&amp;lt;/mml:mo&amp;gt;&amp;lt;mml:mn&amp;gt;0&amp;lt;/mml:mn&amp;gt;&amp;lt;mml:mo&amp;gt;.&amp;lt;/mml:mo&amp;gt;&amp;lt;mml:mn&amp;gt;05&amp;lt;/mml:mn&amp;gt;&amp;lt;/mml:mrow&amp;gt;&amp;lt;/mml:math&amp;gt;&amp;lt;inline-graphic xlink:href="saribudak-ieq2-2870363.gif"/&amp;gt;&amp;lt;/alternatives&amp;gt;&amp;lt;/inline-formula&amp;gt; for the results computed by &amp;lt;sc&amp;gt;pr&amp;lt;/sc&amp;gt;e&amp;lt;sc&amp;gt;p-ad&amp;lt;/sc&amp;gt;. These relatively small average &amp;lt;sc&amp;gt;loocv&amp;lt;/sc&amp;gt; errors and &amp;lt;inline-formula&amp;gt;&amp;lt;tex-math notation="LaTeX"&amp;gt;$p$&amp;lt;/tex-math&amp;gt;&amp;lt;alternatives&amp;gt;&amp;lt;mml:math&amp;gt;&amp;lt;mml:mi&amp;gt;p&amp;lt;/mml:mi&amp;gt;&amp;lt;/mml:math&amp;gt;&amp;lt;inline-graphic xlink:href="saribudak-ieq3-2870363.gif"/&amp;gt;&amp;lt;/alternatives&amp;gt;&amp;lt;/inline-formula&amp;gt;-values suggest that our &amp;lt;sc&amp;gt;pr&amp;lt;/sc&amp;gt;e&amp;lt;sc&amp;gt;p-ad&amp;lt;/sc&amp;gt; methods employing gene expressions, &amp;lt;sc&amp;gt;mmse&amp;lt;/sc&amp;gt; scores and hippocampal volume loss measurements can be useful in supporting pharmacologic therapy decisions during early stages of &amp;lt;sc&amp;gt;ad&amp;lt;/sc&amp;gt;.</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>EC5</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
@@ -2926,7 +3168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>523</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -2934,17 +3176,17 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>An Empirical Study of Self-Admitted Technical Debt in Machine Learning Software</t>
+          <t>Eliminating Backdoors in Neural Code Models for Secure Code Understanding</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>The emergence of open-source ML libraries such as TensorFlow and Google Auto ML has enabled developers to harness state-of-the-art ML algorithms with minimal overhead. However, during this accelerated ML development process, said developers may often make sub-optimal design and implementation decisions, leading to the introduction of technical debt that, if not addressed promptly, can significantly impact on the quality of ML-based software. Developers frequently acknowledge these sub-optimal design and development choices through code comments written during development. These comments, which often highlight areas requiring additional work or refinement in the future are known as self-admitted technical debt (SATD). While prior research has demonstrated that SATD can serve as a reliable indicator of technical debt and has extensively studied SATD in traditional (non-ML) software, little attention has been given to this issue in the context of ML. This paper aims to investigate the occurrence of SATD in ML code by analyzing 318 open-source ML projects across five domains, along with 318 non-ML projects. We detected SATD in source code comments in various snapshots of the studied projects, conducted a manual analysis of a sample of the identified SATD to comprehend the nature of technical debt in the ML code, and performed a survival analysis of the SATD to understand the evolution dynamics of such debts. Our analyses yielded the following observations: (i) Machine learning projects have a median percentage of SATD that is twice that of non-machine learning projects. (ii) ML pipeline stages for data preprocessing and model generation logic are more susceptible to debt than model validation and deployment stages. (iii) SATDs appear in ML projects earlier in the development process compared to non-ML projects. (iv) Long-lasting SATDs are typically introduced during extensive code changes that span multiple files, which exhibit low complexity.Our research contributes to the understanding of technical debt in an ML context and underscores the need for targeted debt management strategies. This contribution is particularly relevant for developers and stakeholders in ML projects by aiding them in identifying and addressing technical debt proactively and paving the way for future research in developing automated tools and methodologies for managing SATD in an ML environment.</t>
+          <t>Neural code models (NCMs) have been widely used to address various code understanding tasks, such as defect detection. However, numerous recent studies reveal that such models are vulnerable to backdoor attacks. Backdoored NCMs function normally on normal/clean code snippets, but exhibit adversary-expected behavior on poisoned code snippets injected with the adversary-crafted trigger. It poses a significant security threat. For example, a backdoored defect detection model may misclassify user-submitted defective code as non-defective. If this insecure code is then integrated into critical systems, like autonomous driving systems, it could jeopardize life safety. Therefore, there is an urgent need for effective techniques to detect and eliminate backdoors stealthily implanted in NCMs. To address this issue, in this paper, we innovatively propose a backdoor elimination technique for secure code understanding, called EliBadCode. EliBadCode eliminates backdoors in NCMs by inverting/reverse-engineering and unlearning backdoor triggers. Specifically, EliBadCode first filters the model vocabulary for trigger tokens based on the naming conventions of specific programming languages to reduce the trigger search space and cost. Then, EliBadCode introduces a sample-specific trigger position identification method, which can reduce the interference of non-backdoor (adversarial) perturbations for subsequent trigger inversion, thereby producing effective inverted backdoor triggers efficiently. Backdoor triggers can be viewed as backdoor (adversarial) perturbations. Subsequently, EliBadCode employs a Greedy Coordinate Gradient algorithm to optimize the inverted trigger and designs a trigger anchoring method to purify the inverted trigger. Finally, EliBadCode eliminates backdoors through model unlearning. We evaluate the effectiveness of in eliminating backdoors implanted in multiple NCMs used for three safety-critical code understanding tasks. The results demonstrate that EliBadCode can effectively eliminate backdoors while having minimal adverse effects on the normal functionality of the model. For instance, on defect detection tasks, EliBadCode substantially decreases the average Attack Success Rate (ASR) of the advanced backdoor attack from 99.76% to 2.64%, significantly outperforming the three baselines. The clean model produced by EliBadCode exhibits an average decrease in defect prediction accuracy of only 0.01% (the same as the baseline).</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Self-Admitted Technical Debt; Machine Learning; Survival Analysis; Mining Software Repositories; ML Pipeline; Empirical Software Engineering</t>
+          <t>Backdoor Defense; Neural Code Models; Trigger Inversion</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2953,7 +3195,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
@@ -2967,7 +3213,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>547</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -2975,17 +3221,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>A Survey of AIOps in the Era of Large Language Models</t>
+          <t>CNCFuzzer: Directed Blackbox Fuzzing of Computer Numerical Control System Based on Message Behaviour Guidance</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>As large language models (LLMs) grow increasingly sophisticated and pervasive, their application to various Artificial Intelligence for IT Operations (AIOps) tasks has garnered significant attention. However, a comprehensive understanding of the impact, potential, and limitations of LLMs in AIOps remains in its infancy. To address this gap, we conducted a detailed survey of LLM4AIOps, focusing on how LLMs can optimize processes and improve outcomes in this domain. We analyzed 183 research articles published between January 2020 and December 2024 to answer four key research questions (RQs). In RQ1, we examine the diverse failure data sources utilized, including advanced LLM-based processing techniques for legacy data and the incorporation of new data sources enabled by LLMs. RQ2 explores the evolution of AIOps tasks, highlighting the emergence of novel tasks and the publication trends across these tasks. RQ3 investigates the various LLM-based methods applied to address AIOps challenges. Finally, RQ4 reviews evaluation methodologies tailored to assess LLM-integrated AIOps approaches. Based on our findings, we discuss the state-of-the-art advancements and trends, identify gaps in existing research, and propose promising directions for future exploration.</t>
+          <t>In the era of the Industrial Internet of Things, Computer Numerical Control (CNC) Systems are confronted with a pervasive threat from attackers. Uncovering their security vulnerabilities before being exploited becomes imperative. Enterprise-level CNC devices often pose significant challenges in obtaining firmware, limiting vulnerability analysis to black-box fuzzing. However, the communication protocols used by CNC devices are characterized by heterogeneity, complexity, and proprietary formats. This inherent complexity not only makes it difficult to build high-quality test cases, but also significantly exceeds the search space of traditional black-box fuzzing methods, thus reducing their efficiency and effectiveness. In this paper, we propose CNCFuzzer, a directed black-box fuzzing approach based on message behaviour guidance. The insights of CNCFuzzer are that if a communication Application Programming Interface (API) is high-risk, the probability that other communication APIs with similar behaviour are high-risk increases. Firstly, we design a black-box directed fuzzing method based on the similarity of the behaviour of machining messages. The key to this solution is that we design graphs of message behaviour as the maps for directed fuzzing. Then, a Transformer-based seq2seq model is employed to train a proprietary protocol traffic generator, which generates high-quality test cases that meet protocol formats. Finally, We design a cyber-physical fusion monitor, which observes the current and voltage of the controllers to monitor the vulnerability of CNC devices and proactive network requests to distinguish the functional command injection and memory corruption. We have implemented CNCFuzzer and evaluated it on 6 enterprise-level CNC devices from 3 brands. Results show that CNCFuzzer outperforms 5 existing black-box fuzzing tools and identified 63 previously unknown vulnerabilities, including 30 memory corruption and 33 functional command injection.</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Large language model; AIOps; metrics; logs; time series; incident report; failure perception; anomaly detection; root cause analysis; assisted remediation</t>
+          <t>Cyber-Physical System; Directed Black-box Fuzzing; Proprietary Protocols; Vulnerabilities</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2994,7 +3240,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
@@ -3008,7 +3258,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>548</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -3016,17 +3266,17 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>A Stack-Propagation Framework for Low-Resource Personalized Dialogue Generation</t>
+          <t>Survey on Factuality in Large Language Models</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>With the resurgent interest in building open-domain dialogue systems, the dialogue generation task has attracted increasing attention over the past few years. This task is usually formulated as a conditional generation problem, which aims to generate a natural and meaningful response given dialogue contexts and specific constraints, such as persona. And maintaining a consistent persona is essential for the dialogue systems to gain trust from the users. Although tremendous advancements have been brought, traditional persona-based dialogue models are typically trained by leveraging a large number of persona-dense dialogue examples. Yet, such persona-dense training data are expensive to obtain, leading to a limited scale. This work presents a novel approach to learning from limited training examples by regarding consistency understanding as a regularization of response generation. To this end, we propose a novel stack-propagation framework for learning a generation and understanding pipeline. Specifically, the framework stacks a Transformer encoder and two Transformer decoders, where the first decoder models response generation and the second serves as a regularizer and jointly models response generation and consistency understanding. The proposed framework can benefit from the stacked encoder and decoders to learn from much smaller personalized dialogue data while maintaining competitive performance. Under different low-resource settings, subjective and objective evaluations prove that the stack-propagation framework outperforms strong baselines in response quality and persona consistency and largely overcomes the shortcomings of traditional models that rely heavily on the persona-dense dialogue data.</t>
+          <t>This survey addresses the crucial issue of factuality in Large Language Models (LLMs). As LLMs find applications across diverse domains, the reliability and accuracy of their outputs become vital. We define the “factuality issue” as the probability of LLMs to produce content inconsistent with established facts. We first delve into the implications of these inaccuracies. Subsequently, we analyze the mechanisms through which LLMs store and process facts, seeking the primary causes of factual errors. Our discussion then transitions to methodologies for evaluating LLM factuality, emphasizing key metrics, benchmarks, and studies. We further explore strategies for enhancing LLM factuality. Our survey offers a structured guide for researchers aiming to fortify the factual reliability of LLMs. We consistently maintain and update the related open-source materials at .</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Open-domain dialogue; personalized dialogue generation; stack-propagation; low-resource</t>
+          <t>Factuality; large language models; knowledge; retrieval augmentation</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -3035,7 +3285,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
@@ -3049,7 +3303,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>554</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -3057,17 +3311,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Psychometrics in Behavioral Software Engineering: A Methodological Introduction with Guidelines</t>
+          <t>An Empirical Study on Challenges of Event Management in Microservice Architectures</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>A meaningful and deep understanding of the human aspects of software engineering (SE) requires psychological constructs to be considered. Psychology theory can facilitate the systematic and sound development as well as the adoption of instruments (e.g., psychological tests, questionnaires) to assess these constructs. In particular, to ensure high quality, the psychometric properties of instruments need evaluation. In this article, we provide an introduction to psychometric theory for the evaluation of measurement instruments for SE researchers. We present guidelines that enable using existing instruments and developing new ones adequately. We conducted a comprehensive review of the psychology literature framed by the Standards for Educational and Psychological Testing. We detail activities used when operationalizing new psychological constructs, such as item pooling, item review, pilot testing, item analysis, factor analysis, statistical property of items, reliability, validity, and fairness in testing and test bias. We provide an openly available example of a psychometric evaluation based on our guideline. We hope to encourage a culture change in SE research towards the adoption of established methods from psychology. To improve the quality of behavioral research in SE, studies focusing on introducing, validating, and then using psychometric instruments need to be more common.</t>
+          <t>Microservices emerged as a popular architectural style over the last decade. Although designed to be self-contained, microservices must communicate to realize business capabilities, creating dependencies among their data and functionalities. Developers then resort to asynchronous, event-based communication to fulfill such dependencies while reducing coupling. However, developers are often oblivious to the inherent challenges of the event-based communication paradigm, leading to pitfalls that ultimately prompt them to reconsider adopting microservices. To make matters worse, literature is scarce on the practices and challenges of designing, implementing, testing, monitoring, and troubleshooting event-based microservices.To fill this gap, this paper provides the first comprehensive characterization of event management practices and challenges in microservices, based on a repository mining study of over 8000 Stack Overflow questions. We find that developers encounter a gamut of problems, including handling large event payloads, modeling event schemas, auditing and debugging event flows, and managing event dependencies and ordering constraints, suggesting that current practices and technologies do not sufficiently serve developers. We review the state of the art and practice through the lens of unveiled challenges and provide actionable implications for developers, providers, and researchers. As a result, our study will support advancing event management solutions in microservices.</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Empirical software engineering; psychology; behavioral software engineering; methodology; questionnaire design</t>
+          <t>microservice; asynchronous; event; streams; pubsub; decoupling; event-driven architecture</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -3076,7 +3330,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
@@ -3090,7 +3348,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>582</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -3098,17 +3356,17 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Market-aware Long-term Job Skill Recommendation with Explainable Deep Reinforcement Learning</t>
+          <t>Agency and Amplification: A Comparison of Manual and Computational Thematic Analyses by Public Health Researchers</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Continuously learning new skills is essential for talents to gain a competitive advantage in the labor market. Despite extensive efforts on relevance- or preference-based skill recommendations, little attention has been given to the practical effects of job skills in the market. To bridge this gap, we propose an explainable personalized skill learning recommendation system that considers the long-term learning benefits and costs. Specifically, we model skill learning utilities based on salary and learning cost associated with job positions and propose a multi-objective deep reinforcement learning framework to model and maximize long-term utilities. Furthermore, we propose a Self-explaining Skill Recommendation Deep Q-network (SeSRDQN) that captures and prototypes prevalent skill sets in the market into representative exemplars for decision-making. SeSRDQN quantitatively decomposes the talent’s long-term learning utility into contributions from each exemplar, offering a comprehensive and multi-factorial explanation across various skill learning options. To tackle the combinatorial complexity of the skill space, we develop an MCTS-based optimization-decoding iterative training procedure for explanation fidelity and human understandability. In this way, talents will receive a tailored roadmap of essential skills, complemented by exemplar-based explanations, to effectively plan their careers. Extensive experiments on a real-world dataset validate the effectiveness and explainability of our approach.</t>
+          <t>Computational techniques offer a means to overcome the amplified complexity and resource-intensity of qualitative research on online communities. However, we lack an understanding of how these techniques are integrated by researchers in practice, and how to address concerns about researcher agency in the qualitative research process. To explore this gap, we deployed the Computational Thematic Analysis Toolkit to a team of public health researchers, and compared their analysis to a team working with traditional tools and methods. Each team independently conducted a thematic analysis of a corpus of comments from Canadian news sites to understand discourses around vaccine hesitancy. We then compared the analyses to investigate how computational techniques may have influenced their research process and outcomes. We found that the toolkit provided access to advanced computational techniques for researchers without programming expertise, facilitated their interaction and interpretation of the data, but also found that it influenced how they approached their thematic analysis.</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Skill Recommendation; Explainable Recommendation; Reinforcement Learning; Deep Q Network; Case-based Reasoning; Prototype Learning; Self-Interpretable Neural Network</t>
+          <t>thematic analysis; field deployment; computational methods; comparison; case study</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -3117,7 +3375,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
@@ -3131,7 +3393,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>599</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -3139,17 +3401,17 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>A Method to Analyze Multiple Social Identities in Twitter Bios</t>
+          <t>Cross-Lingual Topic Discovery From Multilingual Search Engine Query Log</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Twitter users signal social identity in their profile descriptions, or bios, in a number of important but complex ways that are not well-captured by existing characterizations of how identity is expressed in language. Better ways of defining and measuring these expressions may therefore be useful both in understanding how social identity is expressed in text, and how the self is presented on Twitter. To this end, the present work makes three contributions. First, using qualitative methods, we identify and define the concept of a personal identifier, which is more representative of the ways in which identity is signaled in Twitter bios. Second, we propose a method to extract all personal identifiers expressed in a given bio. Finally, we present a series of validation analyses that explore the strengths and limitations of our proposed method. Our work opens up exciting new opportunities at the intersection between the social psychological study of social identity and the study of how we compose the self through markers of identity on Twitter and in social media more generally.</t>
+          <t>Today, major commercial search engines are operating in a multinational fashion to provide web search services for millions of users who compose search queries by different languages. Hence, the search engine query log, which serves as the backbone of many search engine applications, records millions of users’ search history in a wide spectrum of human languages and demonstrates a strong multilingual phenomenon. However, with its salience, the multilingual nature of a search engine query log is usually ignored by existing works, which usually consider query log entries of different languages as being orthogonal and independent. This kind of oversimplified assumption heavily distorts the underlying structure of web search data. In this article, we pioneer in recognition of the multilingual nature of a query log and make the first attempt to cross the language barrier in query logs. We propose a novel model named Cross-Lingual Query Log Topic Model (CL-QLTM) to analyze query logs from a cross-lingual perspective and derive the latent topics of web search data. The CL-QLTM comprehensively integrates web search data in different languages by collectively utilizing cross-lingual dictionaries, as well as the co-occurrence relations in the query log. In order to relieve the efficiency bottleneck of applying the CL-QLTM on voluminous query logs, we propose an efficient parameter inference algorithm based on the MapReduce computing paradigm. Both qualitative and quantitative experimental results show that the CL-QLTM is able to effectively derive cross-lingual topics from multilingual query logs and spawn a wide spectrum of new search engine applications.</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>computational social science; self-presentation; social identity; twitter</t>
+          <t>query log; probabilistic topic model; Search engine</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -3158,7 +3420,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
@@ -3172,7 +3438,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>642</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -3180,17 +3446,17 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Understanding is a Two-Way Street: User-Initiated Repair on Agent Responses and Hearing in Conversational Interfaces</t>
+          <t>Going Beyond Obscurity: Organizational Approaches to Data Anonymization</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Although methods for repairing prior turns in natural conversation are critical for enabling mutual understanding, or successful communication, these methods are seldom built into conversational user interfaces systematically. Chatbots and voice assistants tend to ask users to paraphrase what they said if it was not understood, but users cannot do the same if they encounter trouble in understanding what the agent said. Understanding is a one-way street in most (intent-based) conversation-like interfaces. An exception to this is Moore and Arar (2019), who demonstrate nine types of user-initiated repair on agent responses that are common in natural conversation and who have shown that users will employ these repair features correctly in text-based interfaces if taught. In this small-scale study, we test these user-initiated repairs (in second position) in a voice-based interface. With understanding-oriented repairs, we found that participants employed them much the same way in text and voice. In addition, we examine some hearing- and speaking-oriented repairs that emerged from the use of our novel multi-modal interface. We found that participants used them to manage troubles specific to the voice modality. Analysis of user logs and transcripts suggests that user-initiated repair features are valuable components of conversational interfaces.</t>
+          <t>Anonymization is viewed as a solution to over-exposure of personal information in a data-driven society. Yet how organizations apply anonymization techniques to data for regulatory, ethical or commercial reasons remains underexplored. We investigate how such measures are applied in organizations, asking whether anonymization practices are used, what approaches are considered practical and adequate, and how decisions are made to protect the privacy of data subjects while preserving analytical value. Our findings demonstrate that anonymization is applied to data far less pervasively than expected. Organizations that do employ anonymization often view their practices as sensitive and resort to anonymity by obscurity alongside technical means. Rather than being a purely technical question of applying the right algorithms, anonymization in practice is a complex socio-technical process that relies on multi-stakeholder collaborations. Organizational decision-making about appropriate approaches and the management of responsibility can result in workarounds necessary to negotiate the technical complexity.</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>chatbots; conversational agents; conversational ai; conversational user interfaces; conversational ux; user-initiated repair</t>
+          <t>anonymization; decision making; gdpr; located accountabilities; organizational practices; privacy</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -3199,7 +3465,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
@@ -3213,7 +3483,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>698</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -3221,17 +3491,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>A Survey of Asynchronous Programming Using Coroutines in the Internet of Things and Embedded Systems</t>
+          <t>Cost-Effective Conceptual Design for Information Extraction</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Many Internet of Things and embedded projects are event driven, and therefore require asynchronous and concurrent programming. Current proposals for C++20 suggest that coroutines will have native language support. It is timely to survey the current use of coroutines in embedded systems development. This article investigates existing research which uses or describes coroutines on resource-constrained platforms. The existing research is analysed with regard to: software platform, hardware platform, and capacity; use cases and intended benefits; and the application programming interface design used for coroutines. A systematic mapping study was performed, to select studies published between 2007 and 2018 which contained original research into the application of coroutines on resource-constrained platforms. An initial set of 566 candidate papers, collated from on-line databases, were reduced to only 35 after filters were applied, revealing the following taxonomy. The C 8 C++ programming languages were used by 22 studies out of 35. As regards hardware, 16 studies used 8- or 16-bit processors while 13 used 32-bit processors. The four most common use cases were concurrency (17 papers), network communication (15), sensor readings (9), and data flow (7). The leading intended benefits were code style and simplicity (12 papers), scheduling (9), and efficiency (8). A wide variety of techniques have been used to implement coroutines, including native macros, additional tool chain steps, new language features, and non-portable assembly language. We conclude that there is widespread demand for coroutines on resource-constrained devices. Our findings suggest that there is significant demand for a formalised, stable, well-supported implementation of coroutines in C++, designed with consideration of the special needs of resource-constrained devices, and further that such an implementation would bring benefits specific to such devices.</t>
+          <t>It is well established that extracting and annotating occurrences of entities in a collection of unstructured text documents with their concepts improves the effectiveness of answering queries over the collection. However, it is very resource intensive to create and maintain large annotated collections. Since the available resources of an enterprise are limited and/or its users may have urgent information needs, it may have to select only a subset of relevant concepts for extraction and annotation. We call this subset a conceptual design for the annotated collection. In this article, we introduce and formally define the problem of cost-effective conceptual design where, given a collection, a set of relevant concepts, and a fixed budget, one likes to find a conceptual design that most improves the effectiveness of answering queries over the collection. We provide efficient algorithms for special cases of the problem and prove it is generally NP-hard in the number of relevant concepts. We propose three efficient approximations to solve the problem: a greedy algorithm, an approximate popularity maximization (APM for short), and approximate annotation-benefit maximization (AAM for short). We show that, if there are no constraints regrading the overlap of concepts, APM is a fully polynomial time approximation scheme. We also prove that if the relevant concepts are mutually exclusive, the greedy algorithm delivers a constant approximation ratio if the concepts are equally costly, APM has a constant approximation ratio, and AAM is a fully polynomial-time approximation scheme. Our empirical results using a Wikipedia collection and a search engine query log validate the proposed formalization of the problem and show that APM and AAM efficiently compute conceptual designs. They also indicate that, in general, APM delivers the optimal conceptual designs if the relevant concepts are not mutually exclusive. Also, if the relevant concepts are mutually exclusive, the conceptual designs delivered by AAM improve the effectiveness of answering queries over the collection more than the solutions provided by APM.</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>scheduling; resource-constrained; direct style; asynchronous; Embedded</t>
+          <t>information extraction; effective query answering; Conceptual design</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -3240,7 +3510,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
@@ -3249,12 +3523,12 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>922</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -3262,26 +3536,30 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Recruitment Promotion via Twitter: A Network-centric Approach of Analyzing Community Engagement Using Social Identity</t>
+          <t>Implementation of an online pragmatic randomized controlled trial: A methodological case study</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>With the proliferation of online technologies, social media recruitment has become an essential part of any company’s outreach campaign. A social media platform can provide marketing posts with access to a large pool of candidates and at a low cost. It also provides the opportunity to quickly customize and refine messages in response to the reception. With online marketing, the key question is: which communities are attracted by recruitment tweets on social media? In this work, we profile the Twitter accounts that interact with a set of recruitment tweets by the U.S. Army’s Recruitment Command through a network-centric perspective. By harnessing how users signal their affiliations through user information, we extract and analyze communities of social identities. From Social Identity Theory, these social identities can be critical drivers of behavior, like the decision to enlist in the military. With this framework, we evaluate the effectiveness of the U.S. Army’s recruitment campaign on Twitter, observing that these campaigns typically attract communities with military exposure like veterans or those that identify with professional careers and fitness (e.g., student, professionals, athletes). The campaign also attracts, but at a much lower level, interaction from those in the digital industries—data scientists, cybersecurity professionals, and so forth. When analyzing the accounts in terms of their degree of automation, we find a set of intent-unknown bot accounts interacting with the tweets, and that many of the recruitment accounts are perceived as automated accounts. These observations can aid in campaign refinement: targeting the digital community and getting a broader reach for online recruitment publicity campaigns.</t>
+          <t>Rigorous evaluation of eHealth interventions is acutely needed but can be challenging to execute in a cost- and time-efficient way. The purpose of this study is to describe a randomized controlled trial carried out as part of an approach that evaluates and informs product development throughout an intervention's life cycle. We present the methodological case of a pragmatic randomized controlled trial evaluating the effectiveness of the web-based intervention "Daily Challenge." We conducted the trial entirely online and leveraged existing resources to implement it quickly and within budget. One thousand five hundred three participants were recruited in 49 days (17.1 % of candidates assessed for eligibility). Then, 68.7 % of participants were reached for follow-up at 30 days and 62.5 % at 90 days. Data collection (baseline to 90-day follow-up) was completed within 5 months. Rigorous trials can be conducted efficiently and in a timely manner, enabling evaluation on a continuous basis. Development should include ongoing empirical input to inform product iterations. © 2013 The Author(s).</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Twitter; bot detection; network analysis; social signaling; social identity</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>adult; article; female; follow up; health; human; male; methodology; online system; priority journal; randomized controlled trial (topic); telehealth; wellbeing</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>EC4</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
@@ -3290,12 +3568,12 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>939</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -3303,26 +3581,26 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>SnappView, a Software Development Kit for Supporting End-user Mobile Interface Review</t>
+          <t>Selecting working teams for information technology outsourcing projects through a combination of methodologies</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>This paper presents SnappView, an open-source software development kit that facilitates end-user review of graphical user interfaces for mobile applications and streamlines their input into a continuous design life cycle. SnappView structures this user interface review process into four cumulative stages: (1) a developer creates a mobile application project with user interface code instrumented by only a few instructions governing SnappView and deploys the resulting application on an application store; (2) any tester, such as an end-user, a designer, a reviewer, while interacting with the instrumented user interface, shakes the mobile device to freeze and capture its screen and to provide insightful multimodal feedback such as textual comments, critics, suggestions, drawings by stroke gestures, voice or video records, with a level of importance; (3) the screenshot is captured with the application, browser, and status data and sent with the feedback to SnappView server; and (4) a designer then reviews collected and aggregated feedback data and passes them to the developer to address raised usability problems. Another cycle then initiates an iterative design. This paper presents the motivations and process for performing mobile application review based on SnappView. Based on this process, we deployed on the AppStore "WeTwo", a real-world mobile application to find various personal activities over a one-month period with 420 active users. This application served for a user experience evaluation conducted with N1=14 developers to reveal the advantages and shortcomings of the toolkit from a development point of view. The same application was also used in a usability evaluation conducted with N2=22 participants to reveal the advantages and shortcomings from an end-user viewpoint.</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>GUI testing; application review; code instrumentation; heuristic evaluation; mobile computing; remote evaluation; software development kit; usability evaluation; usability problem; user interface evaluation</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>This paper deals with a problem that Information Technology outsourcing suppliers generally face when selecting a working team technically capable for specific roles in software development projects. A combination of methodologies, interactively integrated, is proposed. They are Soft System Methodology to structure the problem, Repertory Grid for individual interviews and elicitation of the selection criteria, DRV Processes to assess the candidates and to generate knowledge and consensus on the selection process and Linear Programming to assign people to each position. This multimethodology allowed finding a more comprehensive solution than that initially requested by the company, since it helped to establish the necessary transformations for the selection model to operate in the right way, set the competencies to be considered as selection criteria, develop a consensus estimate of the weighted criteria, and award global values to candidates, optimizing the assignment of roles in the group for the project. © 2017 Brazilian Operations Research Society.</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
@@ -3331,12 +3609,12 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>944</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -3344,17 +3622,17 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>An Architectural Viewpoint for Benefit-Cost-Risk-Aware Decision-Making in Self-Adaptive Systems</t>
+          <t>Greedynas: Towards fast one-shot NAS with greedy supernet</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Self-adaptation equips a software system with a feedback loop that resolves uncertainties during operation and adapts the system to deal with them when necessary. Most self-adaptation approaches today use decision-making mechanisms that select for execution the adaptation option with the best-estimated benefit expressed as a set of adaptation goals. A few approaches also consider the estimated (one-off) cost of executing the candidate adaptation options. We argue that besides benefit and cost, decision-making in self-adaptive systems should also consider the estimated risk the system or its users would be exposed to if an adaptation option were selected for execution. Balancing all three concerns when evaluating the options for adaptation to mitigate uncertainty is essential for satisfying stakeholders’ concerns and ensuring the safety and public acceptance of self-adaptive systems. In this article, we present a reference model for decision-making in self-adaptation that considers the estimated benefit, cost, and risk as core concerns of each adaptation option. Leveraging this model, we then present an ISO/IEC/IEEE 42010 compatible architectural viewpoint that aims at supporting software architects responsible for designing robust decision-making mechanisms for self-adaptive systems. We demonstrate the applicability, usefulness, and understandability of the viewpoint through a case study where participants with experience in the engineering of self-adaptive systems performed a set of design tasks in DeltaIoT, an Internet-of-Things exemplar for research on self-adaptive systems.</t>
+          <t>Training a supernet matters for one-shot neural architecture search (NAS) methods since it serves as a basic performance estimator for different architectures (paths). Current methods mainly hold the assumption that a supernet should give a reasonable ranking over all paths. They thus treat all paths equally, and spare much effort to train paths. However, it is harsh for a single supernet to evaluate accurately on such a huge-scale search space (e.g., 721). In this paper, instead of covering all paths, we ease the burden of supernet by encouraging it to focus more on evaluation of those potentially-good ones, which are identified using a surrogate portion of validation data. Concretely, during training, we propose a multi-path sampling strategy with rejection, and greedily filter the weak paths. The training efficiency is thus boosted since the training space has been greedily shrunk from all paths to those potentially-good ones. Moreover, we further adopt an exploration and exploitation policy by introducing an empirical candidate path pool. Our proposed method GreedyNAS is easy-to-follow, and experimental results on ImageNet dataset indicate that it can achieve better Top-1 accuracy under same search space and FLOPs or latency level, but with only ∼60% of supernet training cost. By searching on a larger space, our GreedyNAS can also obtain new state-of-the-art architectures. © 2020 IEEE</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>self-adaptive; risk; cost; benefit; viewpoint; decision-making</t>
+          <t>Computer science; Computers; Electrical engineering; Software engineering; Exploration and exploitation; Neural architectures; Performance estimator; Search spaces; State of the art; Training costs; Training efficiency; Validation data; Pattern recognition</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
@@ -3363,7 +3641,11 @@
           <t>EC5</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
@@ -3372,12 +3654,12 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Scopus</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>993</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -3385,276 +3667,30 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Adventures in monitorability: from branching to linear time and back again</t>
+          <t>Cyber-vetting and impression management: Moderating role of personality traits in the Indian IT industry</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>This paper establishes a comprehensive theory of runtime monitorability for Hennessy-Milner logic with recursion, a very expressive variant of the modal µ-calculus. It investigates the monitorability of that logic with a linear-time semantics and then compares the obtained results with ones that were previously presented in the literature for a branching-time setting. Our work establishes an expressiveness hierarchy of monitorable fragments of Hennessy-Milner logic with recursion in a linear-time setting and exactly identifies what kinds of guarantees can be given using runtime monitors for each fragment in the hierarchy. Each fragment is shown to be complete, in the sense that it can express all properties that can be monitored under the corresponding guarantees. The study is carried out using a principled approach to monitoring that connects the semantics of the logic and the operational semantics of monitors. The proposed framework supports the automatic, compositional synthesis of correct monitors from monitorable properties.</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>monitorability; monitor synthesis; linear-time and branching-time logics</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>Purpose: This study is undertaken to find out the effect of Cyber-vetting (CV) on Impression Management (IM) and the moderating role of personality traits (PT) in the association between two constructs in the Indian IT Industry. Design/ Methodology/ Approach: The constructs chosen for the study are Cyber-vetting, Impression Management and Personality Traits. The model is tested by applying structural equation modelling (SEM). The data collection done from 51 HR Professionals working in IT sector in Bangalore, India. The reliability of the dimensions is established through Confirmatory Factor Analysis (CFA). Findings: The results show a positive association exists between Cyber-vetting, Impression Management and Personality Traits dampens the association between CV and IM. Research Limitation: The study has been undertaken in the IT sector in Bangalore India, the results cannot be generalized across the industry. Practical Implications: This study shifts an attention towards usage of social media platforms as a way of extracting the information about applicants’ qualification, personality traits and consequently the involvement of applicants into impression management Originality/ Value: The research is unique in empirically testing the relationship between CV and IM. The role personality traits play in the association between CV and IM has been empirically tested for the first time in Indian Context. Paper Type: Research Paper. © 2019, Institute of Advanced Scientific Research, Inc.. All rights reserved.</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC4; IC5</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>ACM Digital Library</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Continuous and Proactive Software Architecture Evaluation: An IoT Case</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>Design-time evaluation is essential to build the initial software architecture to be deployed. However, experts’ assumptions made at design-time are unlikely to remain true indefinitely in systems that are characterized by scale, hyperconnectivity, dynamism, and uncertainty in operations (e.g. IoT). Therefore, experts’ design-time decisions can be challenged at run-time. A continuous architecture evaluation that systematically assesses and intertwines design-time and run-time decisions is thus necessary. This paper proposes the first proactive approach to continuous architecture evaluation of the system leveraging the support of simulation. The approach evaluates software architectures by not only tracking their performance over time, but also forecasting their likely future performance through machine learning of simulated instances of the architecture. This enables architects to make cost-effective informed decisions on potential changes to the architecture. We perform an IoT case study to show how machine learning on simulated instances of architecture can fundamentally guide the continuous evaluation process and influence the outcome of architecture decisions. A series of experiments is conducted to demonstrate the applicability and effectiveness of the approach. We also provide the architect with recommendations on how to best benefit from the approach through choice of learners and input parameters, grounded on experimentation and evidence.</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>Continuous evaluation; software architecture evaluation; time series forecasting; IoT</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>ACM Digital Library</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Incentive Mechanisms for Participatory Sensing: Survey and Research Challenges</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>Participatory sensing is a powerful paradigm that takes advantage of smartphones to collect and analyze data beyond the scale of what was previously possible. Given that participatory sensing systems rely completely on the users’ willingness to submit up-to-date and accurate information, it is paramount to effectively incentivize users’ active and reliable participation. In this article, we survey existing literature on incentive mechanisms for participatory sensing systems. In particular, we present a taxonomy of existing incentive mechanisms for participatory sensing systems, which are subsequently discussed in depth by comparing and contrasting different approaches. Finally, we discuss an agenda of open research challenges in incentivizing users in participatory sensing.</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>survey; research challenges; game theory; auction theory; QoI</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>ACM Digital Library</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>odeToJava: A PSE for the Numerical Solution of IVPs</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Problem-solving environments (PSEs) offer a powerful yet flexible and convenient means for general experimentation with computational methods, algorithm prototyping, and visualization and manipulation of data. Consequently, PSEs have become the modus operandi of many computational scientists and engineers. However, despite these positive aspects, PSEs typically do not offer the level of granularity required by the specialist or algorithm designer to conveniently modify the details. In other words, the level at which PSEs are black boxes is often still too high for someone interested in modifying an algorithm as opposed to trying an alternative.In this article, we describe odeToJava, a Java-based PSE for initial-value problems in ordinary differential equations. odeToJava implements explicit and linearly implicit implicit-explicit Runge--Kutta methods with error and stepsize control and intra-step interpolation (dense output), giving the user control and flexibility over the implementational aspects of these methods. We illustrate the usage and functionality of odeToJava by means of computational case studies of initial-value problems (IVPs).</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>Adaptive integration; Runge--Kutta; St\"{o}rmer--Verlet; additive Runge--Kutta; geometric integration; object-oriented; problem solving environment; software architecture; stepsize-control</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>EC4</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
-      <c r="L79" s="2" t="n"/>
-      <c r="M79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>ACM Digital Library</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>RAPID: Zero-Shot Domain Adaptation for Code Search with Pre-Trained Models</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>Code search, which refers to the process of identifying the most relevant code snippets for a given natural language query, plays a crucial role in software maintenance. However, current approaches heavily rely on labeled data for training, which results in performance decreases when confronted with cross-domain scenarios including domain- or project-specific situations. This decline can be attributed to their limited ability to effectively capture the semantics associated with such scenarios. To tackle the aforementioned problem, we propose a zeRo-shot domAin adaPtion with pre-traIned moDels framework for code search named RAPID. The framework first generates synthetic data by pseudo labeling, then trains the CodeBERT with sampled synthetic data. To avoid the influence of noisy synthetic data and enhance the model performance, we propose a mixture sampling strategy to obtain hard negative samples during training. Specifically, the mixture sampling strategy considers both relevancy and diversity to select the data that are hard to be distinguished by the models. To validate the effectiveness of our approach in zero-shot settings, we conduct extensive experiments and find that RAPID outperforms the CoCoSoDa and UniXcoder model by an average of 15.7% and 10%, respectively, as measured by the MRR metric. When trained on full data, our approach results in an average improvement of 7.5% under the MRR metric using CodeBERT. We observe that as the model’s performance in zero-shot tasks improves, the impact of hard negatives diminishes. Our observation also indicates that fine-tuning CodeT5 for generating pseudo labels can enhance the performance of the code search model, and using only 100-shot samples can yield comparable results to the supervised baseline. Furthermore, we evaluate the effectiveness of RAPID in real-world code search tasks in three GitHub projects through both human and automated assessments. Our findings reveal RAPID exhibits superior performance, e.g., an average improvement of 18% under the MRR metric over the top-performing model.</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>Code search; zero-shot learning; software maintenance; pre-trained models; domain adaption</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>IEEE Xplore</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>833</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>IEEE Magazines</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>A major concern among graduates of computing departments is the discrepancy between the expectations of software companies and the competencies provided by the academic departments. This ongoing problem makes co-op education inevitable, as it combines industrial experience with traditional education.</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>Companies; Education; Employment; Software engineering; Recruitment; Software; Training; Computer science education; Educational courses; Career development</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="n"/>
-      <c r="L81" s="2" t="n"/>
-      <c r="M81" s="2" t="n"/>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Scopus</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Desired Qualifications Sought in Entry Level Software Engineers</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>Global demand for software engineers continues to strain the technology sector with unfilled software engineering positions and stiff competition for hiring developers who are on the market. To attract more candidates, technology firms have increasingly been working closely with universities to recruit new graduates to fill their jobs. Universities hoping to minimize mismatches in job placement for new software developers should teach the skills and attributes that enable entry-level software developers to succeed. This paper presents a case study of hiring demands at one large, well-established technology company that reveals the most sought-after attributes in new hires. We discuss results of our interviews with five software development hiring managers and the results from a wide survey of engineers and architects from various levels and experiences. The interviews and surveys reveal that some qualifications are widely desired, and others have varying demand based on functional area, technology, or type of development. Ultimately, professional skills (e.g., teamwork) and personality traits (e.g., strong initiative) top the list of desired attributes, along with a few fundamentally broad technical skills. One key takeaway is that candidates who learn professional skills from university programs may be more readily hired into their first software engineering job than those whose education focused mostly on technical areas. © 2023 ACM.</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>Employment; Engineering education; Professional aspects; Software design; Case-studies; Employer-seek skill; Engineering position; Global demand; Hireability; Hiring managers; Professional skills; Software developer; Technology companies; Technology sectors; Engineers</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC4</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3668,303 +3704,1702 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="75" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Palavra-Chaves</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CIs1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CEs1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Revisor 1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CIs2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CEs2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Revisor 2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Decision</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Revisor 1</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Revisor 2</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>iiitsurat.ac.in</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GL-140</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Indian Institute of Information Technology Surat</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>(No web content scraped)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>EC2; EC5</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering | Future Students</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>news.mit.edu</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GL-234</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Can AI really code? Study maps the roadblocks ...</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>(No web content scraped)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>EC3; EC5</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Why are entry-level data and software engineering roles so ...</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>www.getharvest.com</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GL-250</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The Easiest &amp; Most Effective Ways for Software Developers to Track Time</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Effective Time Tracking for Software Developers
+The Harvest Blog
+Advice to help you keep work running smoothly.
+Categories
+Product News
+Managing Time
+Leading Teams
+Handling Clients
+Managing Projects
+Expert Tips
+Engineering
+Managing Time
+The Easiest &amp; Most Effective Ways for Software Developers to Track Time
+April 14, 2026
+What Are Effective Ways for Software Developers to Track Time?
+Effective time tracking for software developers is about choosing strategies that align with their unique workflows and project demands. Traditional methods like manual time tracking using spreadsheets or notes can work well for those who prefer a hands-on approach. However, these methods are often prone to errors and can be inaccurate by as much as 20-40% compared to digital solutions, as noted by
+kickidler.com
+.
+Modern approaches, such as automated time tracking tools, offer more precision and ease of use. These tools can automatically log time spent on different tasks, providing developers with precise data without the hassle of manual entry. Automated systems reduce the chance of error and can integrate seamlessly with project management software, enhancing overall productivity.
+Another effective method is the Pomodoro Technique, which breaks work into intervals (usually 25 minutes) followed by short breaks. This technique helps maintain focus and can be easily tracked with simple timers or specialized apps. For teams using Agile methodologies, logging time against specific tasks or bugs during sprints can improve velocity tracking and sprint planning.
+Ultimately, the best method depends on your team's workflow. If you need flexibility, manual methods might suffice. For accuracy and data-driven insights, automated tools are the way to go. Whatever the method, the key is consistency and using the data to identify inefficiencies and improve workflow.
+Best Time Tracking Tools for Developers
+When it comes to choosing a time tracking tool, developers have several excellent options tailored to their needs. Each tool offers unique features that cater to different aspects of software development.
+Harvest is a popular choice among developers for its user-friendly interface and robust integration capabilities with tools like Asana, Trello, and Jira. It not only tracks time but also helps in managing project budgets and generating detailed reports, which can be invaluable for both freelancers and team leaders.
+Clockify is another versatile tool, offering a free plan that suits individual developers or small teams. Its ability to export data in formats such as PDF, CSV, or Excel makes it easy to share insights with stakeholders. Meanwhile, tools like Toggl Track focus on simplicity and ease of use, providing real-time tracking and reporting features that help developers understand time allocation without overwhelming them with unnecessary complexity.
+For those who require more detailed analytics, Time Doctor provides features like screen monitoring and activity levels. This can be particularly useful for remote teams to ensure accountability and productivity across different time zones.
+Choosing the right tool depends on your specific needs. If you prioritize integrations and project management features, Harvest might be your best bet. For simple, straightforward tracking, Toggl Track is ideal. And if detailed analytics are crucial, consider Time Doctor. Each tool can help streamline your time management, enabling better productivity and efficiency.
+How to Integrate Time Tracking into Existing Workflows
+Integrating time tracking into your existing workflows can be done smoothly with a few strategic steps. Start by clearly defining the objectives of implementing time tracking. Understanding what you aim to achieve—whether it's improving productivity, enhancing project estimates, or ensuring compliance—will guide the process.
+Next, choose a tool that aligns with your current systems. If your team already uses a project management tool like Jira or Trello, consider a time tracking solution that integrates seamlessly with these platforms. This minimizes disruption and leverages existing infrastructure for more cohesive operations.
+Training is crucial. Ensure that all team members understand how to use the new system effectively. This includes setting clear expectations and providing resources or tutorials. According to
+webwork-tracker.com
+, companies that provide comprehensive training often see higher adoption rates and more accurate data.
+Finally, regularly review the time tracking data and adjust your workflow as needed. Use insights gained from the data to refine processes, address bottlenecks, and enhance overall efficiency. By making time tracking a part of your everyday workflow rather than an add-on, you'll likely see improvements in both productivity and team satisfaction.
+Benefits of Time Tracking for Project Management
+Time tracking offers numerous benefits for project management, particularly in the software development sector. It enhances efficiency by providing clear insights into how time is spent, enabling more accurate project estimates and resource allocation. This can lead to significant productivity gains, with some reports suggesting improvements of up to 30% for teams that implement structured time tracking protocols.
+In project management, time tracking is invaluable for maintaining control over project timelines and budgets. By having a detailed understanding of how long tasks actually take, managers can make more informed decisions about deadlines and resource allocations. This precision helps in avoiding scope creep and ensuring projects stay within budget.
+Moreover, time tracking data can improve team accountability. When developers log their time against specific tasks, it provides transparency and a factual basis for performance reviews and project assessments. This can lead to a more motivated workforce as team members see how their contributions fit into the bigger picture.
+For software development teams working in Agile environments, time tracking aids in measuring velocity and planning better sprints. According to
+timetrak.com
+, tracking helps identify bottlenecks and optimize processes, leading to more predictable and successful project outcomes.
+Common Mistakes in Time Tracking and How to Avoid Them
+Common mistakes in time tracking can significantly hinder productivity, especially for software developers. One of the most prevalent pitfalls is inconsistent time tracking. Developers often forget to log their hours regularly, leading to inaccurate data that can skew project timelines and budget estimates. To combat this, it’s crucial to establish a routine. Automated time tracking tools like Harvest can help by reminding you to log time consistently, ensuring that your data remains accurate and reliable.
+Another common error is choosing the wrong tool for your specific needs. Some developers opt for overly complex systems that offer more features than necessary, making the process cumbersome and discouraging regular use. Opt for a tool that integrates seamlessly with your existing workflows. For example, if your team uses project management platforms like Asana or Trello, consider a time tracking tool that supports these integrations for a more streamlined experience.
+A surprising number of developers also neglect to analyze the data they collect. According to a study, companies that review and adjust their time tracking processes regularly can experience up to a 25% increase in productivity and fewer missed deadlines
+kickidler.com
+. Taking the time to review tracked data can reveal inefficiencies and provide insights into better time management strategies.
+Lastly, transparency in time tracking is often overlooked. Without clear communication about the purpose and benefits of time tracking, developers may view it as a form of micromanagement rather than a tool for personal productivity enhancement. Be sure to communicate how time tracking data will be used to improve workflows and support professional development, not just to monitor hours worked.
+What is the 40 20 40 Rule in Software Engineering?
+The 40 20 40 rule in software engineering is a guideline for allocating time across different phases of a project: 40% for planning, 20% for coding, and 40% for testing and debugging. This rule emphasizes the importance of thorough planning and testing, often overlooked in favor of coding. By adhering to this rule, developers can achieve more balanced and efficient project timelines.
+Planning is critical as it sets the foundation for the entire project. A well-thought-out plan helps anticipate potential challenges and allocate resources effectively. According to
+factorialhr.com
+, neglecting the planning phase can lead to projects that are up to 30% more likely to miss deadlines or exceed budgets. This highlights the need for developers to invest time upfront in detailed planning.
+The coding phase, while crucial, is often where developers prefer to focus their efforts. However, the 40 20 40 rule reminds us that coding should not overshadow other critical aspects of software development. Proper balance ensures that the code is not only functional but also aligns with the project's overall goals and quality standards.
+Finally, the significant portion allocated to testing and debugging emphasizes the importance of quality assurance. By dedicating adequate time to this phase, developers can catch errors early and refine the product, reducing the risk of costly fixes after deployment. This structured approach ultimately leads to more successful project outcomes and enhances the team's ability to meet client expectations.
+What is the 80 20 Rule in Software Development?
+The 80 20 rule, or Pareto Principle, in software development suggests that 80% of the effects come from 20% of the causes. This principle can be a game-changer for developers aiming to maximize productivity. By identifying and focusing on the most impactful tasks, developers can use their time more efficiently.
+In practice, this means recognizing which parts of the project deliver the most value and directing efforts accordingly. For instance, if a particular feature or function is responsible for the majority of user engagement, prioritizing its development can lead to significant improvements in overall product success. According to
+insightful.io
+, focusing on these key areas can lead to productivity boosts of up to 30%.
+A common misconception is that the 80 20 rule only applies to large-scale projects or teams. However, even individual developers can leverage this principle. By regularly reviewing tasks and outcomes, developers can continually refine their focus and ensure that effort aligns with impact. This not only enhances productivity but also reduces burnout by eliminating unnecessary tasks.
+To implement the 80 20 rule effectively, start by analyzing past projects to identify recurring high-impact tasks. Use time tracking tools to measure where your time goes and adjust priorities based on these insights. This strategic focus helps ensure that you're not just working hard but working smart, aligning efforts with results.
+How to Get Started with Tracking Your Coding Hours
+Getting started with tracking your coding hours can seem daunting, but with a few strategic steps, you can integrate this practice seamlessly into your routine. Begin by defining clear objectives for why you want to track time. Are you looking to improve productivity, manage projects more effectively, or simply gain insights into your work habits? Knowing your goals will guide your choice of tools and methods.
+Next, choose a time tracking tool that fits your workflow. There are numerous options available, ranging from simple timers to comprehensive project management suites. For instance, tools like Harvest offer integrations with popular platforms like GitHub and Jira, making it easier to log hours directly within your existing workflow. Such integrations are particularly helpful for developers who want to minimize the disruption caused by time tracking.
+Once you have selected a tool, set up a consistent routine. Begin by logging your time at the start and end of each coding session. Over time, this will become a habit, ensuring that your records remain accurate and comprehensive. According to
+webwork-tracker.com
+, automated tracking solutions can reduce the time spent on this task by up to 40%, allowing you to focus more on coding itself.
+Finally, regularly review your data to identify trends and areas for improvement. This step is crucial for making data-driven decisions that enhance your productivity and efficiency. By understanding how you spend your coding hours, you can optimize your workflow and ensure your efforts are aligned with your goals.
+Frequently Asked Questions
+What is the best way for software developers to track time?
+The best way for software developers to track time is by using dedicated time tracking tools like Clockify or Toggl. These tools offer features such as automated tracking, reporting, and integration with project management software, allowing developers to log their hours efficiently. Additionally, they provide insights into productivity and project timelines, which can help in estimating future work more accurately.
+How can time tracking benefit software project management?
+Time tracking can significantly enhance software project management by providing accurate data on how long tasks take. This information helps project managers make informed decisions about resource allocation, budgeting, and timelines. Furthermore, it can identify bottlenecks in workflows, improve team accountability, and ultimately lead to more successful project outcomes.
+What are the top tools for tracking developer time?
+Some of the top tools for tracking developer time include Clockify, Toggl, Harvest, and JIRA. These tools offer user-friendly interfaces, integration capabilities, and features like reporting and analytics. Choosing the right tool depends on your team's specific needs and the complexity of your projects.
+How do I integrate time tracking in my workflow?
+To integrate time tracking into your workflow, start by selecting a suitable time tracking tool that aligns with your team's needs. Encourage team members to log their time consistently and provide training on how to use the tool effectively. Regularly review the tracked data to identify patterns, adjust workflows, and improve productivity.
+What is the 40 20 40 rule?
+The 40 20 40 rule suggests that developers should spend 40% of their time on core development, 20% on learning new skills or technologies, and 40% on collaboration and communication. This balanced approach helps maintain productivity while fostering continuous improvement and teamwork, ultimately leading to better project outcomes.
+What is the 80 20 rule?
+The 80 20 rule, or Pareto Principle, states that 80% of results come from 20% of efforts. For software developers, this means that focusing on the most impactful tasks can lead to significant improvements in productivity and project success. Identifying and prioritizing these key tasks can help streamline workflows and optimize time management.
+HARVEST
+Get updates in your inbox
+Subscribe to our emails to receive newsletters, product updates, and marketing communications.
+Related Articles
+Start tracking time today
+Join 70,000+ companies spending their time wisely with Harvest.
+Try Harvest free
+Free 30-day trial. No credit card required.
+Track time the way it should be
+Join 70,000+ teams using Harvest to run smarter projects.
+Try Harvest Free</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Machine Learning with System/Software Engineering in ...</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>www.ctm-it.com</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>GL-273</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Security Screening</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Security Screening | ctm Information Technology
+Save even more!
+Reduce your Microsoft 365 bill by
+up to 100%
+when you introduce other businesses to ctm
+Referral Programme
+Our site uses cookies
+This site uses optional cookies for performance and quality purposes in line with out
+Cookie Policy
+.
+Accept cookies
+Cookie settings
+Working at ctm
+Security Screening
+As we provide our customers with security-related services, all of our staff are required to pass a BS7858 security screening, both before starting employment and on an annual basis thereafter.
+For new applicants, please be aware that we only run these checks once you have accepted a job offer and with your consent, not before.
+What do we check for?
+Check
+First Check
+for new employees
+Annual Checks
+or upon change of job role
+Why do we check this?
+ID Verification
+We need to ensure you are who you say you are
+DBS Basic
+Criminal record check to ensure you have not been convicted of any crimes which would compromise the reputation of the company
+UK Credit Check
+Financial troubles may make you more susceptible to manipulation by a bad actor
+UK Directorship Check
+Running your own business whilst working for us may cause a conflict of interest
+UK Driving Licence Check
+Only for employees that need to drive our vehicles, to ensure you're legally allowed to under the terms of our insurance
+Right to Work
+We need to ensure you are legally allowed to work for us in the UK
+Employment History
+We need to verify that your employment history is correct
+Employer References
+We ask for two references from previous employers to further verify your employment history
+What should I do if I'm worried about this?
+Speak to us in confidence before we undertake the checks. The results of the above checks are not a pass/fail, and we consider all circumstances and individuals on a per-case basis.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Relationship between computer science and software ...</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>www.hse.ru</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GL-354</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Process Analysis for Software Engineering</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Process Analysis for Software Engineering – HSE University Course Catalogue – Higher School of Economics National Research University
+В старых версиях браузеров сайт может отображаться некорректно. Для оптимальной работы с сайтом рекомендуем воспользоваться современным браузером.
+We use cookies in order to improve the quality and usability of the HSE website. More information about the use of cookies is available
+here
+, and the regulations on processing personal data can be found
+here
+. By continuing to use the site, you hereby confirm that you have been informed of the use of cookies by the HSE website and agree with our rules for processing personal data. You may disable cookies in your browser settings.
+✖
+A
+A
+A
+ABC
+ABC
+ABC
+А
+А
+А
+А
+А
+Regular version of the site
+{"id":20591,"title":"Russian","name":"ru"}
+Bachelor
+2022/2023
+Process Analysis for Software Engineering
+Type:
+Elective course (
+Software Engineering
+)
+Area of studies:
+Software Engineering
+Delivered by:
+School of Software Engineering
+Where:
+Faculty of Computer Science
+When:
+4 year, 1-3 module
+Mode of studies:
+offline
+Open to:
+students of one campus
+Instructors:
+Alexey A. Mitsyuk
+Language:
+Russian
+ECTS credits:
+10
+Contact hours:
+60</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>EC1; EC2; EC3; EC5</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>AI and Software Engineering: A Symbiotic Relationship</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>www.thisdot.co</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GL-363</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>The Importance of a Scientific Mindset in Software ...</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>The Importance of a Scientific Mindset in Software Engineering: Part 1 (Source Evaluation &amp; Literature Review) - This Dot Labs
+Skip to content
+The Importance of a Scientific Mindset in Software Engineering: Part 1 (Source Evaluation &amp; Literature Review)
+Today, I will write about something very dear to me - science. But not about science as a field of study but rather as a way of thinking.
+It's easy nowadays to get lost in the sea of information, fall for marketing hype, or even be trolled by a hallucinating LLM. A scientific mindset can be a powerful tool for navigating the complex modern world and the world of software engineering in particular.
+Not only is it a powerful tool, but I'll argue that it's a must nowadays if you want to make informed decisions, solve problems effectively, and become a better engineer.
+As software engineers, we are constantly confronted with an overwhelming array of frameworks, technologies, and infrastructure choices. Sometimes, it feels like there's a new tool or platform every day, each accompanied by its own wave of hype and marketing. It's easy to feel lost in the myriad of information or even suffer from FOMO and insecurity about not jumping on the latest bandwagon.
+But it's not only about the abundance of information and making technological decisions. As engineers, we often write documentation, blog posts, talks, or even books. We need to be able to communicate our ideas clearly and effectively. Furthermore, we have to master the art of debugging code, which is essentially a scientific process where we form hypotheses, test them, and iterate until we find the root cause of the problem.
+Therefore, here's my hot take: engineering is a science; hence, to deserve an engineer title, one needs to think like a scientist.
+So, let's
+review
+(pun intended) what it means to think like a scientist in the context of software engineering.
+Systematic Review
+In science, systematic review is not only an essential means to understand a topic and map the current state of knowledge in the field, but it also has a well-defined methodology. You can't just google whatever supports your hypothesis and call it a day. You must define your research question, choose the databases you will search, set your inclusion and exclusion criteria, systematically search for relevant studies, evaluate their quality, and synthesize the results. Most importantly, you must be transparent about and describe your methodology in detail.
+The general process of systematic review can be summarized in the following steps:
+Define your research question(s)
+Choose databases and other sources to search
+Define keywords and search terms
+Define inclusion and exclusion criteria
+a. Define practical criteria such as publication date, language, etc.
+b. Define methodological criteria such as study design, sample size, etc.
+Search for relevant studies
+Evaluate the quality of the studies
+Synthesize the results
+Source:
+Conducting Research Literature Reviews: From the Internet to Paper by Dr. Fink
+I'm pretty sure you can see where I'm going with this. There are many use cases in software engineering where a process similar to systematic review can be applied. Whether you're evaluating a new technology, choosing a tech stack for a new project, or researching for a blog post or a conference talk, it's important to be systematic in your approach, transparent about your methodology, and honest about the limitations of your research.
+Of course, when choosing a tech stack to learn or researching for a blog post, you don't have to be as rigorous as in a scientific study. But a few of these steps will always be worth following. Let's focus on those and see how we can apply them in the context of software engineering.
+Defining Your Research Question(s)
+Before you start researching, it's important to define your research questions. What are you trying to find out? What problem are you trying to solve? What are the goals of your research? These questions will help you stay focused and avoid focusing on irrelevant information.
+A practical example:
+If you're evaluating, say, whether to use bundler
+A
+or bundler
+B
+without a clear research question, you might end up focusing on marketing claims about how bundler
+A
+is faster than bundler
+B
+or how bundler
+B
+is more popular than bundler
+A
+, even though such aspects may have minimal impact on your project. With a clear research question, you can focus on what really matters for your project, like how well each bundler integrates with your existing tools, how well they handle your specific use case, or how well they are maintained.
+A research question is not a hypothesis - you don't have to have a clear idea of the answer. It's more about defining the scope of your research and setting clear goals. It can be as simple and general as "What are the pros and cons of using React vs. Angular for a particular project?" but also more specific and focused, like "What are the legal implications of using open-source library
+X
+for purpose
+Y
+in project
+Z
+?". You can have multiple research questions, but keeping them focused and relevant to your goals is essential.
+In my personal opinion, part of the scientific mindset is automatically having at least a vague idea of a research question in your head whenever you're facing a problem or a decision, and that alone can make you a more confident and effective engineer.
+Choosing Databases and Other Sources to Search
+In engineering, some information (especially when researching rare bugs) can be scarce, and you have to search wherever and take what you can get. Hence, this step is arguably much easier in science, where you can include well-established databases and publications in your search. Information in science is simply more standardized and easier to find.
+There are, however, still some decisions to be made about where to search. Do you want to include community websites like
+StackOverflow
+or
+Reddit
+? Do you want to include marketing materials from the companies behind the technologies you're evaluating? These can all be valid sources of information, but they have their limitations and biases, and it's important to be aware of them.
+Or do you want to ask a LLM? I hadn't included LLMs in the list of valid sources of information on purpose as they are not literature databases in the traditional sense, and I wouldn't consider them a search source for literature research. And for a very good reason - they are essentially a black box, and therefore, you cannot reliably describe a reproducible methodology of your search.
+That doesn't mean you shouldn't ask an LLM for inspiration or a TL;DR, but you should always verify the information you get from them and be aware of their limitations.
+Defining Keywords and Search Terms
+This section will be short, as most of you are familiar with the concept of keywords and search terms and how to use search engines. However, I still wanted to highlight the importance of knowing how to search effectively for a software engineer. It's not just about typing in a few keywords and hoping for the best. It's about learning how to use advanced search operators, filter out irrelevant results, and find the information you need quickly and efficiently.
+If you're not familiar with advanced search operators, I highly recommend you take some time to learn them, for example, at
+FreeCodeCamp
+. Please note, however, that the article is specific to Google and different search engines may have different operators and syntax. This is especially true for scientific databases, which often have their own search syntax and operators. So, if you're doing more formal research, familiarize yourself with the database's search syntax. The underlying principles, however, are pretty much the same everywhere; just the syntax and UI might differ.
+With a solid search strategy in place, the next critical step is to assess the quality of the information we find.
+Methodological Criteria and Evaluation of Sources
+This is where things get interesting. In science, evaluating the quality of the studies is a crucial step in the systematic review process. You can't just take the results of a study at face value - you need to critically evaluate its design, the sample size, the methodology, and the conclusions - and you need to be aware of the limitations of the study and the potential biases that may have influenced the results.
+In science, there is a pretty straightforward yet helpful categorization of sources that my students surprisingly needed help understanding because no one ever explained it to them. So let me lay out and explain the three categories to you now:
+1. Primary sources
+Primary sources represent original research. You can find them in studies, conference papers, etc. In science, this is what you generally want to cite in your own research.
+However, remember that only some of what you find in an original research paper is a primary source. Only the parts that present the original research are primary sources. For example, the introduction can contain citations to other studies, which are not primary, but secondary sources.
+While primary sources can sometimes be perceived as hard to read and understand, in many cases, they can actually be easier to reach and understand as the methods and results are usually presented in a condensed form in the abstract, and often you can only skim the introduction and discussion to get a good idea of the study.
+In software engineering, primary sources can sometimes be papers, but more often, they are original documentation, case studies, or even blog posts that present original research or data. For example, if you're evaluating a new technology, the official documentation, case studies, and blog posts from its developers can be considered primary sources.
+2. Secondary sources
+Secondary sources are typically reviews, meta-analyses, and other sources that summarize, analyze, or reference the primary sources. A good way to identify a source as secondary is to look for citations to other studies. If a claim has a citation, it's likely a secondary source. On the other hand, something is likely wrong if it doesn't have a citation and doesn't seem to present original research.
+Secondary sources can be very useful for getting an overview of a topic, understanding the current state of knowledge, and finding relevant primary sources. Meta-analyses, in particular, can provide a beneficial point of view on a subject by combining the results of multiple studies and looking for patterns and trends.
+The downside of secondary sources is that they can introduce information noise, as they are basically introducing another layer of interpretation and analysis. So, it's always a good idea to go back to the primary sources and verify the information you get from secondary sources.
+Secondary sources in software engineering include blog posts, talks, or articles that summarize, analyze, or reference primary sources. For example, if you're researching a new technology, a blog post that compares different technologies based on their documentation and/or studies made by their authors can be considered a secondary source.
+3. Tertiary sources
+Tertiary sources represent a further level of abstraction. They are typically textbooks, encyclopedias, and other sources that summarize, analyze, or reference secondary sources. They are useful for getting a broad overview of a topic, understanding the basic concepts, and finding relevant secondary sources.
+One example I see as a tertiary source is
+Wikipedia
+, and while you shouldn't ever cite Wikipedia in academic research, it can be a good starting point for getting an overview of a topic and finding relevant primary and secondary sources as you can easily click through the references.
+Note: It's fine to reference Wikipedia in a blog post or a talk to give your audience a convenient explanation of a term or concept. I'm even doing it in this post. However, you should always verify that the article is up to date and that the information is correct.
+The distinction between primary, secondary, and tertiary sources in software engineering is not as clear-cut as in science, but the general idea still applies. When researching a topic, knowing the different types of sources and their limitations is essential. Primary sources are generally the most reliable and should be your go-to when seeking evidence to support your claims. Secondary sources can help get an overview of a topic, but they should be used cautiously, as they can introduce bias and noise. Tertiary sources are good for getting a broad overview of a topic but should not be used as evidence in academic research.
+Evaluating Sources
+Now that we have the categories laid out let's talk about evaluating the quality of the sources because, realistically, not all sources are created equal.
+In science, we have some well-established criteria for evaluating the quality of a source. Some focus on the general credibility of the source, like the reputation of the journal or the author. In contrast, others focus on the quality of the study itself, like the study design, the sample size, and the methodology.
+First, we usually look at the
+number of citations
+and the
+impact factor
+of the journal in which the study was published. These numbers can give us an idea of how well the scientific community received the study and how much other researchers have cited it.
+In software engineering, we don't have the concept of impact factor when it comes to researching a concept or a technology, but we can still look at how many people are sharing the particular piece of information and how well the professional community receives it and how reputable the person sharing the information is.
+Second, we look at the
+study design
+and the
+methodology
+. Does the study have a clear research question? Is the study design appropriate for the research question? Are the methods well-described and reproducible? Are the results presented clearly and honestly? Do the data support the conclusions?
+Arguably, in software engineering, the honest and clear presentation of the method and results can be even more important than in science, given the amounts of money circulating in the industry and the potential for conflicts of interest. Therefore, it's important to understand where the data is coming from, how it was collected, and how it was analyzed.
+If a company (or their DevRel person) is presenting data that show their product is the best (fastest, most secure...), it's important to be aware of the potential biases and conflicts of interest that may have influenced the results.
+The ways in which the results can be skewed may include:
+Missing, incomplete, or inappropriate methodology
+. Often, the methodology is not described in enough detail to be reproducible, or the whole experiment is designed in a way that doesn't actually answer the research question properly. For example, the methodology can omit important details, such as the environment in which the experiment was conducted or even the way the data was collected (e.g., to hide selection bias).
+Selection bias
+can be a common issue in software engineering experiments. For example, if someone is comparing two technologies, they might choose a dataset that they expect to perform better with one of the technologies or a metric that they expect to show a difference. Selection bias can lead to skewed results that don't reflect the technologies' real-world performance.
+Publication bias
+is a common issue in science, where studies that show a positive result are more likely to be published than studies that show a negative outcome. In software engineering, this can manifest as a bias towards publishing success stories and case studies, while ignoring failures and negative results.
+Confirmation bias
+is a problem in science and software engineering alike. It's the tendency to look for evidence that confirms your hypothesis and ignore evidence that contradicts it. Confirmation bias can lead to cherry-picking data, misinterpreting results, and drawing incorrect conclusions.
+Conflict of interest
+. While less common in academic research, conflicts of interest can be a big issue in industry research. If a company is funding a study that shows its product in a positive light, it's important to be aware of the potential biases that may have influenced the results.
+Another thing we look at is the
+conclusions
+. Do the data support the conclusions? Are they reasonable and justified? Are they overstated or exaggerated? Are the limitations of the study acknowledged? Are the implications of the study discussed? It all goes back to honesty and transparency, which is crucial for evaluating the quality of the source.
+Last but not least, we should look at the
+citations and references
+included in the source. In the same way we apply the systematic review process to our research, we should also apply it to the sources we use. I would argue that this is even more important in software engineering, where the information is often less standardized, and you come across many unsupported claims. If a source doesn't provide citations or references to back up their claims, it's a red flag that the information may not be reliable.
+This brings us to something called
+anecdotal evidence
+. Anecdotal evidence is a personal story or experience used to support a claim. While anecdotal evidence can be compelling and persuasive, it is generally considered a weak form of evidence, as it is based on personal experience rather than empirical data. So when someone tells you that X is better than Y because they tried it and it worked for them, or that Z is true because they heard it from someone, take it with a massive grain of salt and look for more reliable sources of information.
+That, of course, doesn't mean you should ask for a source under every post on social media, but it's important to recognize what's a personal opinion and what's a claim based on evidence.
+Synthesizing the Results
+Once you have gathered all the relevant information, it's time to synthesize the results. This is where you combine all the evidence you have collected, analyze it, and draw conclusions.
+In science, this is often done as part of a
+meta-analysis
+, where the results of multiple studies are combined and analyzed to look for patterns and trends using statistical methods. A meta-analysis is a powerful tool for synthesizing the results of multiple studies and drawing more robust conclusions than can be drawn from any single study.
+You might not be doing a formal meta-analysis in software engineering, but you can still apply the same principles to your research. Look for common themes and trends in the information you have gathered, compare and contrast different sources, and draw conclusions based on the evidence.
+Conclusion
+Adopting a scientific way of thinking isn't just a nice-to-have in software engineering - it's essential to make informed decisions, solve problems effectively, and navigate the vast amount of information around you with confidence. Applying systematic review principles to your research allows you to gather reliable information, evaluate it critically, and draw sound conclusions based on evidence.
+Let's summarize what such a systematic research approach can look like:
+Define Clear Research Questions:
+Start every project or decision-making process by clearly stating what you aim to achieve or understand.
+Example: "What factors should influence our choice between Cloud Service A and Cloud Service B for our application's specific needs?"
+Critically Evaluate Sources:
+Identify the type of sources (primary, secondary, tertiary) and assess their credibility.
+Be wary of biases and seek out multiple perspectives for a well-rounded understanding.
+Be Aware of Biases:
+Recognize common biases that can cloud judgment, such as confirmation or selection bias.
+Actively counteract these biases by seeking disconfirming evidence and questioning assumptions.
+Systematically Synthesize Information:
+Organize your findings and analyze them methodically.
+Use tools and frameworks to compare options based on defined criteria relevant to your project's goals.
+I encourage you to embrace this scientific approach in your daily work. The next time you're facing a critical decision - be it selecting a technology stack, debugging complex code, or planning a project - apply these principles:
+Start with a Question:
+Clearly define what you need to find out.
+Gather and Evaluate Information:
+Seek out reliable sources and scrutinize them.
+Analyze Systematically:
+Organize your findings and look for patterns or insights.
+Make Informed Decisions:
+Choose the path supported by evidence and sound reasoning.
+By doing so, you will enhance your problem-solving skills and contribute to a culture of thoughtful, evidence-based practice in the software engineering community.
+The best part is that once you start applying a critical and systematic approach to your sources of information, it becomes second nature. You'll automatically start asking questions like, "Where did this information come from?" "Is it reliable?" and "Can I reproduce the results?" Doing so will make you much less susceptible to hype, marketing, and new shiny things, ultimately making you happier and more confident.
+In the next part of this series, we'll look at applying the scientific mindset to debugging and using hypothesis testing and experimentation principles to solve problems more effectively.
+Hire us
+About the author(s)
+Jan Kaiser
+Software engineer passionate about everything web-related. Particularly loves Angular, SCSS, TypeScript, soccer and dachshunds
+@
+honzikec
+@
+honzikec
+Let's innovate together!
+We're ready to be your trusted technical partners in your digital innovation journey.
+Whether it's modernization or custom software solutions, our team of experts can guide you through best practices and how to build scalable, performant software that lasts.
+Name
+Email address
+Name
+Email address
+Let's innovate together!
+How did you hear about us?
+Send message
+Prefer email?
+hi@thisdot.co
+This Dot is a consultancy dedicated to guiding companies through their modernization and digital transformation journeys. Specializing in replatforming, modernizing, and launching new initiatives, we stand out by taking true ownership of your engineering projects.
+We love helping teams with projects that have missed their deadlines or helping keep your strategic digital initiatives on course. Check out
+our case studies
+and
+our clients
+that trust us with their engineering.
+Tech Turnarounds and Unveiling Health Tech's Potential: Insights from Fractional C-Suite Executive Denise Smith
+Tracy Lee sits down with Denise Smith, an accomplished fractional C-suite executive specializing in technology turnarounds, mergers, and acquisitions. In this conversation, they explore the world of health tech, and discuss the critical role engineering leaders play in understanding and navigating the financial aspects of their businesses.
+Denise’s journey into the tech world began with a degree in chemistry from Spelman College. She found her niche in technology by coding SQL databases and working on Y2K projects. This pivot marked her entry into technology consulting and set the stage for her career in the industry. Her current role involves being a fractional C-suite executive, such as a CTO, CEO, or COO, for companies in need of turnaround expertise or support during mergers and acquisitions.
+The Exciting Landscape of Health Tech:
+Denise's specialization in health tech offers her unique insights into the convergence of technology and healthcare. She highlights the opportunities to leverage technology to help people thrive in the digital age, focusing on digital equity and how solutions can empower populations to access vital information quickly. In the context of health tech, technology can play a crucial role in aiding first responders during emergencies and improving overall response times.
+Pivoting and Adaptation in the Face of Challenges:
+The interview explores the impact of the COVID-19 pandemic on tech companies, particularly those focusing on COVID-related solutions. Denise acknowledges that many companies faced challenges when the immediate need for their products diminished as the pandemic situation improved. She emphasizes the importance of pivoting business strategies to discover new opportunities and income streams. Denise's role often involves analyzing customer segments and generating product roadmaps to drive revenue growth.
+Guiding Principles for Successful Leadership:
+Denise's expertise extends beyond technology to financial literacy and leadership strategy. She emphasizes the significance of engineering leaders understanding their company's financials, such as customer acquisition costs and customer long-term value. This knowledge empowers leaders to make informed decisions and contribute to the overall growth and success of the business. Additionally, she stresses the importance of empathetic leadership and fostering a positive company culture during times of change and adaptation.
+Unexpected Paths to Leadership Success:
+One of the standout aspects of the interview is Denise's recommendation to explore unconventional routes for leadership development. She shares her experience with the BLCK VC program (Black Venture Capital), which exposed her to venture funding and financial insights that significantly impacted her leadership journey. Denise's story underscores the value of embracing unique learning opportunities that broaden leadership skillsets.
+Denise Smith's insightful interview provides valuable takeaways for engineering leaders seeking to navigate business challenges and drive growth. From understanding financial metrics to fostering empathy and embracing non-traditional learning experiences, her journey and expertise offer a refreshing perspective on the intersection of technology, leadership, and business success....
+Aug 16, 2023
+2
+mins
+Software Engineering
+Engineering Leadership</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Does familiarity with the attraction matter? Antecedents of ...</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>towardsdatascience.com</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>GL-365</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Data Analysis Is a Form of Software Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>(No web content scraped)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>I am really into computers and I would love to study ...</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>spb.hse.ru</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>GL-377</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Student Theses</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Student Theses — Bachelor's Programme in Applied Mathematics and Information Science — HSE University
+В старых версиях браузеров сайт может отображаться некорректно. Для оптимальной работы с сайтом рекомендуем воспользоваться современным браузером.
+We use cookies in order to improve the quality and usability of the HSE website. More information about the use of cookies is available
+here
+, and the regulations on processing personal data can be found
+here
+. By continuing to use the site, you hereby confirm that you have been informed of the use of cookies by the HSE website and agree with our rules for processing personal data. You may disable cookies in your browser settings.
+✖
+A
+A
+A
+ABC
+ABC
+ABC
+А
+А
+А
+А
+А
+Regular version of the site
+РУС
+EN
+Search
+Advanced search
+Bachelor’s Programme 'Applied Mathematics and Information Science'
+About
+Programme Curriculum
+For Prospective Students
+For Prospective Students
+For Students
+Notice Board
+The online service «Student» - Saint Petersburg
+РУС
+EN
+For visually-impaired
+Search
+Advanced search
+Menu
+HSE Campus in St. Petersburg
+HSE Campus in St. Petersburg
+Bachelor's programmes
+School of Computer Science, Physics and Technology
+Bachelor's Programme in Applied Mathematics and Information Science
+Student Theses
+Bachelor’s Programme 'Applied Mathematics and Information Science'
+About
+Programme Curriculum
+For Prospective Students
+For Students
+Notice Board
+The online service «Student» - Saint Petersburg
+For Students:
+Notice Board
+The online service «Student» - Saint Petersburg
+International Admissions
+Courses
+Faculty
+Timetable
+Documents
+Academic Supervisor
+Alexander I. Khrabrov
+Contacts
+3a Kantemirovskaya Ulitsa
+, Room 331
+St. Petersburg, 193171, Russia
+Phone: +7 (812) 644-59-11 ext. 61578
+Strategic partner
+Feedback
+Got ideas on how to make HSE University better? Share them here.
+Have you spotted a
+typo
+?
+Highlight it, click Ctrl+Enter and send us a message. Thank you for your help!
+To be used only for spelling or punctuation mistakes.
+Student Theses
+HSE Campus in St. Petersburg
+→
+Bachelor's programmes
+→
+School of Computer Science, Physics and Technology
+→
+Bachelor's Programme in Applied Mathematics and Information Science
+→
+Student Theses
+ABOUT
+Partnerships
+Faculty &amp; Staff
+HSE - St.Petersburg on the Map
+STUDIES
+International Admissions
+Summer School
+Preparatory Year
+Incoming Mobility
+Outgoing Mobility
+RESEARCH
+Research Centres
+Research Projects
+Monitoring Studies
+Conferences &amp; Seminars
+Academic Jobs
+MEDIA &amp; RESOURCES
+Publications by Staff
+HSE Journals
+iq.hse.ru: commentary by HSE experts
+Economic &amp; Social Data Archive
+Video
+Edit
+© HSE University 1993–2026
+Contacts
+Copyright
+Privacy Policy
+Site Map
+HSE Sans and HSE Slab fonts developed by the HSE Art and Design School</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>EC1; EC2; EC3; EC5</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Information Technology Tests - Pre-Employment ...</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>www.securityclearedjobs.com</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GL-38</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer DV Information Technology jobs in ...</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>(No web content scraped)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering Levels and Titles</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>addyosmani.com</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GL-406</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>The Next Two Years of Software Engineering</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AddyOsmani.com - The Next Two Years of Software Engineering
+The software industry sits at a strange inflection point. AI coding has evolved from autocomplete on steroids to agents that can autonomously execute development tasks. The economic boom that fueled tech’s hiring spree has given way to an efficiency mandate: companies now often favor profitability over growth, experienced hires over fresh graduates, and smaller teams armed with better tools.
+Meanwhile, a new generation of developers is entering the workforce with a different calculus: pragmatic about career stability, skeptical of hustle culture, and raised on AI assistance from day one.
+What happens next is genuinely uncertain. Below are five critical questions that may shape software engineering through 2026, with two contrasting scenarios for each. These aren’t really predictions, but lenses for preparation. The goal is a clear roadmap for handling what comes next, grounded in current data and tempered by the healthy skepticism this community is known for.
+1. The Junior developer question
+The bottom line: Junior developer hiring could collapse as AI automates entry-level tasks, or rebound as software spreads into every industry. Both futures require different survival strategies.
+The traditional pathway of “learn to code, get junior job, grow into senior” is wobbling. A
+Harvard study of 62 million workers
+found that when companies adopt generative AI, junior developer employment drops by about 9-10% within six quarters, while senior employment barely budges.
+Big tech hired 50% fewer fresh graduates
+over the past three years. As
+one engineer cynically put it
+: ~”Why hire a junior for $90K when an AI coding agent costs less?”
+This isn’t just AI.
+Macro factors like rising interest rates and post-pandemic corrections
+hit around 2022, before AI tools became widespread. But AI has accelerated the trend. A single senior engineer with AI assistance can now produce what used to require a small team. Companies are quietly not hiring juniors more than they’re firing anyone.
+The flip scenario: AI unlocks massive demand for developers across every industry, not just tech. Healthcare, agriculture, manufacturing, and finance all start embedding software and automation. Rather than replacing developers, AI becomes a force multiplier that spreads development work into domains that never employed coders. We’d see more entry-level roles, just different ones: “AI-native” developers who quickly build automations and integrations for specific niches.
+The
+Bureau of Labor Statistics still projects ~15% growth
+in software jobs from 2024 to 2034. If businesses use AI to expand output rather than strictly cut headcount,
+they’ll need humans to seize the opportunities AI creates
+.
+The long-term risk of the pessimistic scenario is often overlooked: today’s juniors are tomorrow’s senior engineers and tech leaders. Cut off the talent pipeline entirely and you create a leadership vacuum in 5-10 years.
+Industry veterans call this the “slow decay”
+: an ecosystem that stops training its replacements.
+What to do about it:
+Junior developers:
+Make yourself AI-proficient and versatile. Demonstrate that one junior plus AI can match a small team’s output. Use AI coding agents (Cursor/Antigravity/Claude Code/Gemini CLI) to build bigger features, but understand and explain every line if not most. Focus on skills AI can’t easily replace: communication, problem decomposition, domain knowledge. Look at adjacent roles (QA, DevRel, data analytics) as entry points. Build a portfolio, especially projects integrating AI APIs. Consider apprenticeships, internships, contracting, or open source. Don’t be “just another new grad who needs training”; be an immediately useful engineer who learns quickly.
+Senior developers:
+Fewer juniors means more grunt work landing on your plate. Lean on automation for routine tasks, but don’t do everything yourself. Set up CI/CD, linters, and AI-assisted testing to catch basic issues. Mentor unofficially through open source or coaching colleagues in other departments.
+Be frank with management about the risks of all-senior teams
+. If junior demand rebounds, be ready to onboard effectively and delegate in ways that use AI. Your value is in multiplying the whole team’s output, not just your own code.
+2. The Skills question
+The bottom line: Core programming skills could atrophy as AI writes most code, or become more critical than ever as human developers focus on oversight. The coming years determine whether we trade understanding for speed.
+84% of developers now use AI assistance regularly
+. For many, the first instinct when facing a bug or new feature isn’t to write code from scratch, but to compose a prompt and stitch together AI-generated pieces. Entry-level coders are skipping the “hard way”: they might never build a binary search tree from scratch or debug a memory leak on their own.
+The skillset is shifting from implementing algorithms to knowing how to ask the AI the right questions and verify its output.
+The first rung of the ladder now demands prompting and validating AI
+rather than demonstrating raw coding ability. Some senior engineers worry this produces a generation who can’t code well independently, a kind of deskilling. AI-generated code introduces subtle bugs and security vulnerabilities that less-experienced developers might miss.
+The counter-scenario: as AI handles the routine 80%, humans focus on the hardest 20%. Architecture, tricky integrations, creative design, edge cases: the problems machines alone can’t solve. Rather than making deep knowledge obsolete, AI’s ubiquity makes human expertise more important than ever. This is the “high-leverage engineer” who uses AI as a force multiplier but must deeply understand the system to wield it effectively.
+If everyone has
+AI coding agent
+access, what distinguishes great developers is knowing when the AI is wrong or suboptimal.
+As one senior engineer put it
+: “The best software engineers won’t be the fastest coders, but those who know when to distrust AI.”
+Programming shifts: less typing boilerplate, more reviewing AI output for logical errors, security flaws, and mismatches with requirements. Critical skills become software architecture, system design, performance tuning, and security analysis.
+AI can produce a web app quickly, but an expert engineer ensures the AI followed security best practices
+and didn’t introduce race conditions.
+Developer discourse in 2025 was split. Some admitted they hardly ever write code “by hand” and think coding interviews should evolve. Others argued that skipping fundamentals leads to more firefighting when AI’s output breaks.
+The industry is starting to expect engineers to bring both
+: AI speed and foundational wisdom for quality.
+What to do about it:
+Junior developers:
+Use AI as a learning tool, not a crutch. When AI coding agents (Cursor/Antigravity/Claude Code/Gemini CLI) suggest code review why it works, identify weaknesses. Occasionally disable your AI helper and write key algorithms from scratch. Prioritize CS fundamentals: data structures, algorithms, complexity, memory management. Implement projects twice, once with AI, once without, and compare. Learn
+prompt engineering
+and tool mastery. Train yourself in rigorous testing: write unit tests, read stack traces without immediately asking AI, get comfortable with debuggers. Deepen complementary skills AI can’t replicate: system design, user experience intuition, concurrency reasoning. Show you can both crank out solutions with AI and tackle thorny issues when it fails.
+Senior developers:
+Position yourself as the guardian of quality and complexity. Sharpen your core expertise: architecture, security, scaling, domain knowledge. Practice modeling systems with AI components and think through failure modes. Stay current on vulnerabilities in AI-generated code. Embrace your role as mentor and reviewer: define where AI use is acceptable and where manual review is mandatory (payment or safety code). Lean into creative and strategic work; let the junior+AI combo handle routine API hookups while you decide which APIs to build. Invest in soft skills and cross-domain knowledge. Stay current on new tools and best practices. Double down on what makes a human developer indispensable: sound judgment, system-level thinking, and mentorship.
+3. The Role question
+The bottom line: The developer role could shrink into limited auditing (overseeing AI-generated code) or expand into a pivotal orchestrator position designing and governing AI-driven systems. Either way, adding value means more than just coding.
+The extremes here are stark. In one vision, developers see their creative responsibilities diminished. Rather than building software, they mostly audit and babysit AI outputs. AI systems (or “citizen developers” using no-code platforms) handle production; human developers review auto-generated code, check for errors, bias, or security issues, and approve deployments. Maker becomes checker. The joy of code creation replaced by the anxiety of risk management.
+There are reports of engineers spending more time evaluating AI-generated pull requests and managing automated pipelines, less time crafting code from scratch. Programming feels less like creative problem-solving and more like compliance. As one engineer lamented: “I don’t want to end up as a code janitor, cleaning up what the AI throws over the wall.”
+The alternative future is far more interesting: developers evolve into high-level orchestrators, combining technical, strategic, and ethical responsibilities. AI “workers” mean human developers take on an architect or general contractor role, designing the overall system, deciding which tasks go to which AI or software component, weaving solutions from many moving parts.
+A CEO of a low-code platform articulated this vision
+: in an “agentic” development environment, engineers become “composers,” orchestrating ensembles of AI agents and software services. They won’t write every note themselves, but they define the melody: architecture, interfaces, how agents interact. This role is interdisciplinary and creative: part software engineer, part system architect, part product strategist.
+The optimistic take: as AI handles rote work, developer roles shift toward higher-value activities by necessity. Jobs may become more interesting. Someone has to decide what the AI should build, verify the product makes sense, and continuously improve it.
+Which way it goes may depend on how organizations choose to integrate AI. Companies that see AI as labor replacement might trim dev teams and ask remaining engineers to keep automations running. Companies that see AI as a way to amplify their teams might keep headcounts similar but have each engineer deliver more ambitious projects.
+What to do about it:
+Junior developers:
+Seek opportunities beyond just writing code. Volunteer for test case writing, CI pipeline setup, or application monitoring: skills aligned with an auditor/custodian role. Keep your creative coding alive through personal projects so you don’t lose the joy of building. Develop a systems mindset: learn how components communicate, what makes APIs well-designed. Read engineering blogs and case studies of system designs. Familiarize yourself with AI and automation tools beyond code generation: orchestration frameworks, AI APIs. Improve communication skills, written and verbal. Write documentation as if explaining to someone else. Ask senior colleagues not just “Does my code work?” but “Did I consider the right things?” Prepare to be verifier, designer, and communicator, not just coder.
+Senior developers:
+Lean into leadership and architectural responsibilities. Shape the standards and frameworks that AI and junior team members follow. Define code quality checklists and ethical AI usage policies. Stay current on compliance and security topics for AI-produced software. Focus on system design and integration expertise; volunteer to map data flows across services and identify failure points. Get comfortable with orchestration platforms (Kubernetes, Airflow, serverless frameworks, agent orchestration tools). Double down on your role as technical mentor: more code reviews, design discussions, technical guidelines. Hone your ability to quickly assess someone else’s (or something’s) code and give high-level feedback. Develop product and business sense; understand why features get built and what customers care about. Shadow a product manager or join customer feedback sessions. Protect your creative passion through prototypes, hackathons, or emerging tech research. Evolve from coder to conductor.
+4. The Specialist vs. Generalist question
+The bottom line: Narrow specialists risk finding their niche automated or obsolete. The fast-changing, AI-infused landscape rewards T-shaped engineers: broad adaptability with one or two deep skills.
+Given how quickly models, tools and frameworks rise and fall, betting your career on a single technology stack is risky. A guru in a legacy framework might suddenly find themselves in less demand when a new AI tool handles that tech with minimal human intervention. Developers who specialize narrowly in “a single stack, framework or product area” might wake up to find that area declining or redundant.
+Think of COBOL developers, Flash developers, or mobile game engine specialists who didn’t pivot when the industry moved. What’s different now is the pace of change. AI automation can make certain programming tasks trivial, undercutting roles that revolved around those tasks. A specialist who only knows one thing (fine-tuning SQL queries, slicing Photoshop designs into HTML) could find AI handling 90% of that work.
+Hiring managers chase the newest niche. A few years ago everyone wanted cloud infrastructure specialists; now there’s a surge in AI/ML engineers. Those who specialized narrowly in yesterday’s technology feel stalled as that niche loses luster.
+The opposite outcome is specialization in a new form: the “versatile specialist” or
+T-shaped developer
+. Deep expertise in one or two areas (the vertical stroke), broad familiarity with many others (the horizontal stroke).
+These engineers become the “glue” in multidisciplinary teams
+; they communicate with specialists of other stripes and fill gaps when needed.
+Companies no longer want developers who are either too shallow or too narrowly focused
+; they want a strong core competency plus ability to work across the stack. Part of the reason is efficiency: a T-shaped engineer can often solve problems end-to-end without waiting on handoffs. Part is innovation: cross-pollination of knowledge leads to better solutions.
+AI tools actually augment generalists more, making it easier for one person to handle multiple components. A back-end engineer can rely on AI help to create a reasonable UI; a front-end specialist can have AI generate server boilerplate. An AI-rich environment lets people operate more broadly. Meanwhile, deep specialists might find their niche partly automated with no easy way to branch out.
+Nearly 45% of engineering roles now expect proficiency in multiple domains
+: programming plus cloud infrastructure knowledge, or front-end plus some ML familiarity.
+What to do about it:
+Junior developers:
+Establish a broad foundation early. Even if hired for a specific role, peek outside that silo. If you’re doing mobile, learn backend basics; if you’re doing front-end, try writing a simple server. Learn the deployment process and tools like Docker or GitHub Actions. Identify one or two areas that genuinely excite you and go deeper: this becomes your vertical expertise. Brand yourself as a hybrid: “full-stack developer with cloud security focus” or “frontend developer with UX expertise.” Use AI tools to learn new domains quickly; when you’re a novice in backend, have ChatGPT generate starter API code and study it. Build the habit of continuous re-skilling. Participate in hackathons or cross-functional projects to force yourself into generalist mode. Tell your manager you want exposure to different parts of the project. Adaptability is a superpower early in your career.
+Senior developers:
+Map your skill graph: what are you expert in, what related domains have you only touched superficially? Pick one or two adjacent domains and commit to becoming conversant. If you’re a back-end database specialist, get comfortable with a modern front-end framework or learn ML pipeline basics. Do a small project in your weak area with AI assistance. Integrate your deep expertise with new contexts; if you specialize in web app performance, explore how those skills apply to ML inference optimization. Advocate for or design your role to be more cross-functional. Volunteer to be the “integration champion” for projects touching multiple areas. Mentor others to spread skills around while picking up something from them in return. Update your resume to reflect versatility. Use your experience to identify patterns and transferable knowledge. Become the T-shaped role model: deep in your specialty (giving authority and confidence) but actively stretching horizontally.
+5. The Education question
+The bottom line: Will a CS degree remain the gold standard, or will faster learning paths (bootcamps, online platforms, employer training) overtake it? Universities may struggle to keep up with an industry that changes every few months.
+A four-year computer science degree has long been the primary ticket into software roles. But that tradition is being questioned.
+One future: universities remain important but struggle to stay relevant. Degrees stay the default credential, but programs lag behind rapidly evolving needs, hampered by slow curriculum update cycles and bureaucratic approval processes. Students and employers feel academia is disconnected from industry, teaching theory or outdated practice that doesn’t translate to job skills.
+Recent grads report never learning about cloud computing, modern DevOps, or AI tooling during their degree. If universities demand high time and financial investment while delivering low-relevance education, they risk being seen as expensive gatekeepers. But many companies still require a bachelor’s degree out of inertia, so the burden shifts to students to fill the gap with bootcamps, online courses, and self-taught projects.
+Student loan debt is enormous, and companies spend billions training new grads
+because those grads lack skills needed in the workplace. Universities might add an AI ethics class here, a cloud computing elective there, but by the time they implement something, industry tools have moved on.
+The disruptive scenario: traditional education gets increasingly replaced by new systems. Coding bootcamps, online certifications, self-taught portfolios, employer-created training academies. Many high-profile employers (Google, IBM) have dropped degree requirements for certain technical roles.
+In 2024, nearly 45% of companies planned to eliminate bachelor’s degree requirements
+for at least some positions.
+Bootcamps have matured. They produce grads who get hired at top companies alongside CS grads. These programs are shorter (12-week intensive) and focus on practical skills: current frameworks, cloud services, teamwork. The hiring currency is shifting toward live portfolios, micro-credentials, and verified skills. A strong GitHub portfolio or recognized certification can bypass degree requirements.
+Employer-driven education is emerging: companies creating their own training pipelines or partnering with bootcamps. Some big tech companies have started internal “universities” for non-traditional candidates. AI itself offers new ways to learn: AI tutors, interactive coding sandboxes, personalized instruction outside university settings.
+A modular ecosystem of learning is far more accessible than an expensive four-year degree. A kid in a country without strong CS universities can take the same Coursera courses and build the same portfolio as someone in Silicon Valley.
+What to do about it:
+Aspiring/junior developers:
+If in a traditional CS program, don’t rely on it exclusively. Augment coursework with real-world projects: build a web app, contribute to open source. Seek internships or co-ops. If your curriculum misses hot topics, learn them through online platforms. Earn industry-recognized certifications (GCP, AWS, Azure) to signal practical knowledge. If self-teaching or in a bootcamp, focus on a compelling portfolio: at least one substantial project with good documentation. Be active in the developer community: contribute to open source, write technical posts. Network through LinkedIn, meetups, dev events. Get an experienced developer to vouch for you. Keep learning continuously; the half-life of technical skills is short. Use AI as your personal tutor. Prove your skills in concrete ways: portfolio, certification, and ability to talk intelligently about your work will open doors.
+Senior developers and leaders:
+Your credential alone won’t carry you forever. Invest in continuous education: online courses, workshops, conferences, certifications. Validate your skills in new ways; be prepared for interviews that assess current competency through real problems. Maintain side projects with new tech. Reassess job requirements: do you really need a new hire to have a CS degree, or do you need certain skills and learning ability? Push for skills-first hiring to widen your talent pool. Support internal training programs or apprenticeship-style roles. Champion mentorship circles for junior devs without formal backgrounds. Engage with academia and alternatives: advisory boards, guest lectures, feedback on curriculum gaps. Reflect this in your own career growth: real-world achievements and continuous learning matter more than additional degrees.
+The Through-Line
+These scenarios aren’t mutually exclusive. Reality will draw elements from all of them. Some companies will reduce junior hiring while others expand it in new domains. AI will automate routine coding while raising standards for the code humans touch. Developers might spend mornings reviewing AI outputs and afternoons crafting high-level architecture.
+The consistent thread: change is the only constant. By keeping a finger on technology trends (and skepticism around them), you avoid being caught off-guard by hype or doom. By updating skills, diversifying abilities, and focusing on uniquely human aspects (creativity, critical thinking, collaboration) you remain in the loop.
+Whether the future brings a coding renaissance or a world where code writes itself, there will always be demand for engineers who think holistically, learn continuously, and drive technology toward solving real problems.
+The best way to predict the future is to actively engineer it.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC3; IC5</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Gartner for Software Engineering Leaders</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>careers.chevron.com</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>GL-412</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology at Chevron</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology at Chevron
+Skip to main content
+Alena's
+machine learning innovations will help deliver cleaner energy.
+that’s how we do IT
+As the global energy system evolves to meet the demands of a growing world, we are focused on delivering affordable, reliable and ever-cleaner energy. What’s our secret? A cutting-edge team of technology pros with the resources to make it happen. Every day, as part of this team, your software and cloud engineering, data science and cybersecurity expertise will help us lead the way in energy. You’ll learn, grow and build a career that can take you anywhere.
+IT career areas
+agile
+Servant leaders and coaches responsible for removing impediments and fostering an environment for high-performing team dynamics, continuous flow, and relentless improvement. Help educate Agile teams in Scrum and SAFe®.
+Scrum Master
+Release Train Engineer
+cloud engineering &amp; infrastructure
+Develop, implement, optimize and maintain cloud-based solutions. Responsible for deploying and debugging cloud stacks and ensuring the reliability and security of the cloud infrastructure.
+Cloud Engineer
+Network Engineer
+Reliability Engineer
+cybersecurity
+Responsible for consulting, designing, and deploying cybersecurity technologies and solutions for business partners and the entire enterprise.
+Cyber Engineer – Information Technology (IT)
+Cyber Engineer – Operational Technology (OT)
+data engineering
+Delivers data products to accelerate the delivery of analytics and workflow solutions.  Covers end-to-end data lifecycle activities—analyzing and mapping data sources, creating common information models, designing integration that enables data movement, and developing the pipelines.
+Data Engineer
+Data Architect
+Data Analyst
+data science &amp; analytics
+Identify business opportunities, analyze and process data, build models, and interpret results to create actionable insights for our business to improve decision making, business workflows and automation.
+Data Scientist
+Machine Learning Engineer
+Business Intelligence Analyst
+software engineering
+Delivers innovative solutions at scale, driving them through the complete life cycle to improve business processes and drive undeniable value.
+Software Engineering
+Application Engineering
+where we hire
+Chevron is the second-largest integrated energy company in the United States
+see jobs in United States
+Chevron has a major presence in the Philippines as one of the country’s biggest investors
+see jobs in Manila, PH
+Chevron has business and opportunities at various levels of expertise in Argentina
+see jobs in Buenos Aires, AR
+the technologies we deploy help us manage and develop our global assets efficiently and effectively.
+of
+Insights
+from a
+software
+engineer
+Insights from a software engineer
+Get a glimpse into the projects and positive impacts you can make as a software engineer at Chevron. Caitlin Rubia shares a bit on her experiences.
+watch video
+Chevron uses
+Microsoft HoloLens
+to Make Virtual
+Teleportation a
+Reality
+Chevron uses Microsoft HoloLens to Make Virtual Teleportation a Reality
+Chevron has partnered with Microsoft to fuel digital transformation. A technology called Microsoft HoloLens is showing us that the future is now, as it makes sci-fi virtual teleporting a business reality for safer operations and to address issues more quickly on the Chevron front lines.
+learn more
+chevron’s future
+of human energy
+chevron’s future of human energy
+Chevron has an exciting future as it continues to lead the way and empower human progress. With several big projects underway, Chevron is better positioned and knowledgeable and have access to new parts of the energy landscape.
+learn more
+Endless
+opportunities for
+a bright
+career
+Endless opportunities for a bright career
+Whether you’re just starting your career or looking for new ways to make an impact as an experienced professional, Chevron brings a broad range of opportunities. Todd MacGregor, cybersecurity chapter head, shares his insights.
+watch video
+Following Chevron’s
+Azure Migration
+Journey
+Following Chevron's Azure Migration Journey
+See how Chevron is using Microsoft Azure in its digital transformation. Through automation and the ability to manage data across multiple platforms, Azure offers ease of migration for large enterprise environments like Chevron's.
+watch video
+we’re proudly recognized as a preferred employer
+Newsweek America's Greatest Workplaces 2023
+Newsweek and data firm Plant-A Insights group named Chevron as one of America’s Greatest Workplaces in 2023.
+Forbes
+Forbes and Statista named Chevron to the 2024 list of America’s Best Employers for Diversity.
+search available jobs</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Information technology Review 1</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>society-rse.org</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GL-435</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Vacancies</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Vacancies - Society of Research Software Engineering
+Vacancies
+You can post a vacancy here for any role that involves a significant element of writing software for research, or supports the role of RSEs. Vacancies anywhere in the world are welcome. We have also collated
+resources to help improve EDIA for recruitment, as well as other job boards
+.
+It is not a requirement that your job title is listed as “Research Software Engineer” however you should consider the advantages of doing so.  I.e.:
+You will support the advocacy of the RSE role
+The job will have a clear intent that the position is about developing research software not necessarily undertaking novel research (more appropriate for a research associate).
+The job will be naturally signposted to our welcoming and growing RSE community
+If your job involves supporting RSEs in their role or is otherwise related to RSE without directly involving writing software for research, it will be published under ‘Related non-RSE’.
+You can
+submit a job advert using this form
+and it will go to a member of our web team for approval.
+Please also consider adding the role description to our
+RSE Career Ladder database
+.
+Other RSE organisations may have
+their own job boards
+so have a look at theirs too.
+RSE Job Vacancies
+Keywords
+Location
+Remote positions only
+Your browser does not support JavaScript, or it is disabled. JavaScript must be enabled in order to view listings.
+Load more listings
+Related non-RSE / RSE-like Vacancies
+These vacancies are not necessarily for RSE positions, but we believe they may still be of interest to our community.
+Keywords
+Location
+Remote positions only
+Your browser does not support JavaScript, or it is disabled. JavaScript must be enabled in order to view listings.
+Load more listings</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Reliability assessment of AI systems - ISO/IEC AWI TS 25570</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>www.wearedevelopers.com</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GL-439</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>What Jobs Can You Get with a Software Engineering ...</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>What Jobs Can You Get with a Software Engineering Degree?
+March 17, 2024
+5 min read
+What Jobs Can You Get with a Software Engineering Degree?
+By
+Luis Minvielle
+Link copied
+WeAreDevelopers Dev Digest
+Newsletter
+Your weekly digest of news, tools, and expert tips to elevate your developer career.
+Is the university path the only way to become a software engineer? No. There is no set-in-stone route for achieving a software engineer career. Indeed, becoming a software engineer
+without a degree
+, while is a more challenging path, is not impossible — for example, through self-teaching or coding bootcamps.
+However, generally speaking, a bachelor's degree in software engineering or any related area, such as Computer Science, is a key advantage when it comes to finding a job. According to a
+survey
+, 73.5% of software engineers have a bachelor's degree, which gives us an idea of the weight of this element in the current job market.
+Read our Software Engineer Career Path Guide →
+So, what jobs can you get with a Software Engineering degree?
+Good news — software engineers are required in almost every company, across all sectors. Any company that operates an online presence, such as a website or online service, almost certainly employs or has employed some kind of software engineer, or has cut a deal with a company with software engineers on its roster. And, in 2024, these are practically all companies. That’s why, at
+WeAreDevelopers
+, we help the top talent find new software engineer jobs in the best companies in Europe.
+We selected the most in-demand jobs so you can check them and find the one that best suits your intentions.
+1. Software Engineer
+Of course, a plausible job you can get with a software engineering degree is one as a software engineer.
+Job description:
+Software engineers build, test, maintain and improve software systems to meet particular requirements. Just remember before you apply — a software engineer is not the same as a software developer. Since they share similar functions and skills, it is not uncommon to mistake them and assume they are the same thing. But, while the latter focuses on creating application software or particular systems, the former is centred on the bigger picture, just like an architect drawing up building plans for a construction worker to implement. Now, realistically, these roles and duties are often mixed. The architect analogy could create some mix-ups with the actual role of a
+software architect
+, which requires a degree and plenty of years of experience, but we’re using it just as an example.
+💰
+Average salary
+: €56,787 per year in Germany
+Developer jobs in Europe 🇪🇺
+Over 1,300+ developer job opportunites from companies based in Western Europe. Onsite, hybrid, remote, and English-speaking roles available.
+Browse jobs
+‍
+2. Startup Founder
+Software engineers can also work in starting new businesses and become founders.
+Job description:
+Obviously, this isn't a predictable job. On the contrary, a startup is a highly volatile environment where business goals, tactics, concepts, and products constantly shift. As founders of new businesses, software engineers who have decided to be entrepreneurs will have multiple tasks, many of those very far off from software. These “errands” include building a bare-bones version of their MVP product and making financial and business decisions. And, of course, having to pitch their idea to investors, and then be held accountable by them. If you combine creative ideas and an entrepreneurial personality with your SE degree, this may be your path. Just remember that the execution and product-market fit could be even more valuable than your skills or your idea.
+Do startup founders have salaries, or just capitalize on profits?
+If you receive an investment, even if your company is not profitable yet, you can assign yourself a salary as part of the company’s payroll using the investment’s cash fund.
+💰
+Average salary:
+From €0 up to the moon 🚀
+3. AI Engineer
+Programmers say that to become an AI engineer, you need to be a software engineer first and learn AI and machine learning only afterwards. It’s a thorny path for everyone, but software engineering graduates have the advantage of being sharp with algebra, probability, and calculus. Don’t be surprised if the employers request some seniority and pretend you’ve worked as a software engineer first.
+💡Read our guide on
+how to become an AI engineer
+.
+💰
+Average salary
+: ~ $132,000 per year in the United States
+4. Web Developer
+A web developer is likely to be primarily concerned with software that runs in the browser. They may also be involved in web server-based software.
+Three main types of developers work with the web: frontend (design), backend (technical) and full-stack (both). You will choose one career path depending on personal skills, goals, and, of course, salaries.
+Check the difference between Fronted and Backend Development→
+5. Backend Developer
+Backend
+developers are essential to the development and upkeep of the internal workings of apps and websites, handling data processing, security, and server-side functions. Even though users may not see these components, they are essential since they result in making sure websites are carrying out their tasks. Some duties include building and managing databases that contain significant information, writing code, creating APIs, performing QA testing, and checking on web security.
+Have a look at the
+essential tools
+a backend developer must handle.
+💰
+Average salary:
+€60,000 per year in Germany
+6. Frontend Developer
+Frontend
+developers bring to life the visual aspects of websites or web apps using HTML, CSS, and JavaScript. In broad terms, they are responsible for the website or web app UI and UX, both fundamental aspects to captivate and retain people browsing through sites and app users. If you combine an acute sensibility for designing with programming capabilities, this may be a tempting option! You’ll notice that it pays a little less than its counterpart, the backend dev.
+💰
+Average salary:
+€55,000 per year in Germany
+7. Full Stack Developer
+Full stack
+developers can work on the front and back end of a website or web app. They have experience and knowledge in both roles. Some of their responsibilities entail designing and developing software, testing and debugging, writing quality code, ensuring code-platform compatibility, and maintaining a responsive app design. Full stack developers are usually in demand by startups and smaller businesses, since they can manage the complete development process independently and are typically self-sufficient.
+💰
+Average salary:
+€60,000 per year in Germany
+8. Mobile App Developer
+Software engineers who can’t stop looking at their phones can now earn a pay cheque from it.
+Job description:
+Mobile app developers
+specialise in designing, building, and maintaining applications for mobile devices and smartphones, and in adapting web or computer-based applications for mobile use. Their main tasks include designing apps, writing code, testing and debugging, updating and improving. There are two main types of mobile app developers.
+Native devs, specialise in building apps for a particular system, such as Android or iOS, with their corresponding compatible programming languages — Kotlin or Java for Android, Swift, or Objective-C for iOS.
+Cross-platform devs, who can build apps employing cross-platform technologies, like
+React Native
+,
+Xamarin
+or
+Flutter
+, that allow them to write the code once and apply it across various operating systems.
+💰
+Median salary:
+€58,000 per year in Germany for Xamarin
+9. DevOps Engineer
+This position is based on software engineers' coding skills and understanding of software development processes.
+Job description:
+DevOps engineers focus on simplifying the software delivery process and ensuring reliable app performance. As the name suggests, they are the bridge between development and operations. They automate software tasks, making collaboration easier between development and operation teams. They also design and manage infrastructure.
+💰
+Average salary:
+€65,800 per year in Germany
+10. Data Scientist and Machine Learning Engineer
+Although it may require some transitional steps, software engineers can definitely work as both data scientists and machine learning engineers.
+Job description:
+Data scientists study data and extract meaning from it, while machine learning engineers focus on understanding it and making predictions. A data scientist's job is to create a set of data, study it, make new things with the data they already have, tell people who need to know about what they found and understand what they caught up with. Machine learning engineers work on finding, making, and maintaining AI and machine learning algorithms.
+💸
+Average salary:
+Data Scientist: €70,000 per year in Germany
+Machine Learning: €60,000 per year in Germany
+11. Video Game Developer
+It takes grit and creativity to be a video game developer. A software engineering degree should give you both (and in the first semester).
+Job description:
+Game developers create and produce video games of any scope. The size of the company they work for determines their responsibilities. Game devs may concentrate on a specific area of programming, such as network, engine, graphics, toolchain, and artificial intelligence — if they work for a big gaming company. The lines between developer and designer roles are frequently blurred in smaller independent indie game producers, and your work may involve both.
+💰
+Average salary:
+$91,000
+per year in the United States. The figure is likely skewed toward senior developers.
+Looking for a job for your software engineering degree?
+For the most recent opportunities in software development, see our
+job boards
+. Wish you luck!
+By
+Luis Minvielle
+WeAreDevelopers Dev Digest
+Newsletter
+Your weekly digest of news, tools, and expert tips to elevate your developer career.
+Link copied</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>EC3</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Sampling in Software Engineering Research:A Critical Review ...</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>distantjob.com</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GL-49</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Computer Programming and Analysis (Software Engineering ...</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>37 Hybrid &amp; Onsite Software Engineering Jobs in Tallinn ...</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Information Technology Archives</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Information and Software Technology Journal</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Information Technology Course - Career Choices &amp; Jobs</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>A Preliminary Guide for Assertive Selection of Active ...</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Best Practices in 2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Best Practices in 2026 | DistantJob - Remote Recruitment Agency
+Hire Now
+Find a Job
+Resources
+Explore
+Blog
+The Podcast
+Remote Work Readiness Tool
+Interview Questions
+Salary Calculator
+Remote Hiring Course
+Compare DistantJob
+vs Local Recruitment Agencies
+vs Freelance Sites
+vs Outsourcing Firms
+How We Work
+Vetting Process Page
+Onboarding Protocol
+About Us
++1-888-886-7343
+Contact Us
+Tech Insights
+Software Engineering Best Practices in 2026
+Cesar Fazio
+Published on February 16, 2026
+-
+Updated on February 27, 2026
+-
+3 min. to read
+The problem with poor software is that it doesn’t just taint your image; you also lose revenue. Software engineering best practices have undergone many changes in recent years. Capers Jones said in 2009 that software engineering needed to discuss many technical issues “to become a legitimate term for an occupation that has been
+a craft or art
+form rather than a true engineering field”. Since then, software engineering has evolved to more iterative development processes, flexible and automated.
+The best practices in software engineering in 2026 focus on collaboration, continuous delivery, and adaptation to emerging technologies, especially artificial intelligence and machine learning.
+We have curated a list of best practices in software development in 2026, along with examples. Whether you’re leading a team of experienced engineers or newbies, these practices can help ensure your project’s success.
+Why are Software Engineering Best Practices so Important?
+Software engineering best practices are crucial for producing high-quality, reliable, and maintainable software.
+Agile
+Project Management is not enough to ensure that software is robust, secure, or can adapt to changing needs over time.
+In fact, many software engineers resent Agile.
+Robert Martin
+, also known as “Uncle Bob”, author of Clean Code and Clean Architecture, attacks what he and
+Martin Fowler
+(co-author of the Agile Manifesto) call “Flaccid Scrum”, which means “Scrum without Software Engineering Best Practices”. According to him, Flaccid Scrum leads to lower productivity overall.
+In contrast, these software engineering giants always recommend Extreme Programming, which was an Agile Framework before the Agile Manifesto was even written. Extreme Programming shares many elements with Scrum, while keeping software engineering best practices.
+In short, software engineering best practices are unavoidable if you want to develop and deploy the best software.
+Ten Essential Practices for Software Engineers to Implement
+There are many software development practices that we can’t possibly cover in this piece. But here are ten practical tips to guide your team in 2026.
+1. Requirements Gathering &amp; Analysis
+In software engineering, requirements gathering is the process of defining exactly what the software should do and how it should perform. It’s the most critical step in the
+SDLC
+.
+Fixing a misunderstanding during the design phase costs almost nothing. On the other hand, fixing the same misunderstanding after the code is written requires rewriting, re-testing, and re-deploying.
+It also avoids “scope creep”, the slow, uncontrolled growth of a project’s goals. Without a defined list of requirements, it is impossible to say “no” to new feature requests. Gathering requirements creates a baseline that keeps the project on schedule and within budget.
+Key Requirements Elicitation Techniques
+Gathering requirements isn’t just about asking, “What do you want?” It’s a systematic process of discovery, negotiation, and documentation.
+Interviews
+: One-on-one or group discussions with stakeholders to gain detailed, qualitative insights.
+Workshops
+: Collaborative, structured meetings involving users and stakeholders to define requirements, resolve conflicts, and foster agreement.
+Brainstorming
+: An informal, creative group session used to identify new, innovative, or undocumented ideas.
+Prototyping
+: Creating preliminary versions or wireframes of software to test functionality, reduce ambiguity, and gather feedback early.
+Observation (Job Shadowing)
+: Watching users perform their daily tasks to understand operational workflows, pain points, and implicit needs.
+Surveys
+: Efficient tools for gathering high-level, quantitative information from a large, dispersed group of stakeholders.
+Document Analysis
+: Reviewing existing system documentation, business plans, and competitors’ products to identify requirements.
+Scenarios
+: Modeling interactions to define how users will interact with the system to achieve specific goals.
+Focus Groups
+: Small, guided groups that provide feedback on specific aspects of the project, useful when individual stakeholders are unavailable.
+Key Techniques from the Product Discovery
+Product Discovery is an ongoing process of discovering what needs to be done without asking the customer what they want.
+User Journey Mapping
+: A visual timeline of a customer’s interactions with your brand. It tracks their actions, emotions, and pain points from initial discovery to final goal.
+Jobs To Be Done
+: It focuses on the “job” a customer hires a product to do. JBTD identifies the functional, emotional, and social progress a user seeks in a specific circumstance.
+Persona
+: A persona is a representation of a relevant group of a company’s ideal target audience. Personas are built based on research and real data about potential customers, considering aspects such as demographics, behaviors, and specific needs.
+2. Coding Standards
+Maintaining a consistent coding style throughout the project is a best practice for software engineering. It includes meaningful names for variables, functions, and other entities. It also includes proper indentation and dividing complex logic into manageable chunks.
+Don’t forget to keep your code clean. A clean code is a robust code that is easy to read and maintain. A robust code handles errors and unexpected situations gracefully. A readable code is a code with proper indentation, clear structure, meaningful names, and consistent formatting. Finally, maintainable code should prioritize ease of understanding for unfamiliar developers.
+3. Improve Code Quality
+To improve
+code quality
+, you must understand its three basic principles. DRY, KISS, and YAGNI. DRY means “Don’t Repeat Yourself”; avoid redundant code. Every piece of knowledge or logic within a system should have a single, unambiguous, authoritative representation. In other words, if your bank system already has a deposit function or class, don’t create other deposit functions or classes. It will make a mess.
+KISS means “Keep It Simple, Stupid”. Most systems work best if they are kept simple rather than made complex. Avoid unnecessary complexity in your code; only add complexity when really needed.
+YAGNI, “You Aren’t Gonna Need It”, advises against adding functionality until it is absolutely necessary. So, if you are planning to create an API that will connect your application to its many microservices while your software is still a modular monolith is not the best idea. Let your grandiose plans have a time to shine later.
+4. Version Control Management
+When submitting code for review, it is best to make smaller pull requests (PR) or change lists, not larger ones. One of the main reasons for this is that it makes the job of the code reviewer easier.
+Nothing is worse as a code reviewer than reviewing 1,000 or 2,000 lines of code. And because reviewing that many lines of code is difficult, it is easier for a bug to introduce itself in the pull request and eventually into the central repository.
+Ideally, make your pull request under 200-400 lines for thorough and faster reviews.
+Also, it makes it more challenging if the requester eventually has to fix the pull request because a bug made its way into the main code repository. The more code you have in a PR, the more likely you are to run into a merge conflict.
+This is especially useful if you work at a large company like Google or Facebook, where many engineers share the same
+code repository
+. So, try to err on the side of smaller pull requests.
+That might mean the requester has to put in more effort because they’ll have to break up their code into pieces that can be submitted as separate pull requests. But it will go a long way in improving the entire software development process.
+Git is the industry-standard distributed version control system, while platforms like GitHub, GitLab, and Bitbucket provide collaborative interfaces for code hosting and DevOps. Other top tools include SVN (centralized), Mercurial (distributed), and Perforce (high-performance for large files).
+5. Shifting-Left Testing
+Shift-Left Testing is the practice of moving testing and security checks earlier in the development lifecycle to reduce rework costs. From the beginning of a project, integrate various testing types such as integration testing (ensuring parts work together), end-to-end testing (simulating user scenarios), and Test-Driven Development (TDD) (writing tests before code).
+For example, writing unit tests is one of the easiest ways to improve code quality. Unit tests focus on small, modular pieces of code to test one functionality at a time. Consider different scenarios, including deliberately making test cases fail to observe behavior, and aim for 100% test coverage.
+Run all tests before requesting a review to catch bugs early, as fixing defects in early stages can be significantly cheaper than after release. Also, consider training the whole team in basic testing, even juniors. If the engineers can perform basic testing before sending their tasks to the test phase, the QAs can focus on deeper level testing. This is the essence of Shifting-Left Testing.
+Also, don’t forget to automate aspects of testing and review using linters, vulnerability scanners, and tools for checking best practices and coverage. AI tools can significantly streamline code reviews by detecting issues and providing suggestions.
+6. Effective Code Reviews
+Engage in code reviews where another software engineer examines your code or pull request to improve overall code quality, identify bugs, and reduce future optimization work.
+Stack related pull requests to separate logically distinct changes, enabling parallel work and more granular feedback. For example, while coding an API, you might feel inclined to split your pull requests into three parts: “Front-End”, “API endpoints and business logic”, and “database and schemas”. In that way, your reviewer might be able to review each snippet with clear intent.
+Google
+researchers found that limiting review sessions to under 60 minutes helps reviewers to maintain focus and accuracy.
+Use a
+code review checklist
+to standardize the process and ensure checks for functionality, readability, maintainability, security, performance, and coding standards. Maybe the company already has one. Use it.
+Document and explain code decisions, including the motivation, alternatives explored, and trade-offs, to provide context for reviewers and future maintenance.
+7. Design Patterns
+Instead of designing things from scratch, it’s an advisable best practice for software engineers to look for design patterns. A design pattern is a solution template used often to create software.
+Refactoring Guru
+compares them to “pre-made blueprints that you can customize to solve a recurring design problem in your code”.
+They are not code snippets; they are more like design choices for architectural decisions. While design patterns are more under the scope of software architects, in some companies, there is no architect, so a software engineer must decide for the project. Even if there is an architect, a software engineer must know how to build them.
+Design patterns come in three flavors: creational patterns, structural patterns, and behavioral patterns. Creational patterns create reusable objects, structural patterns connect different objects, and behavioral patterns assign objects with roles and responsibilities.
+8. Optimization and Performance Practices
+There are many best practices to optimize and add performance to your software. Among them, it’s worth noting:
+Asynchronous Jobs
+Cache-Aside Patterns
+Parallelism and Concurrence
+SQL Performance and Optimization
+Content Distribution Network (CDN)
+Asynchronous Jobs
+Asynchronous jobs
+are tasks that run independently and concurrently, without blocking other processes. They aim for more efficient use of system resources and a more responsive user experience. Instead of waiting for one operation to complete before starting another, asynchronous programming enables multiple tasks to proceed simultaneously.
+Cache-Aside Patterns
+Applications use a cache to deliver information and data held in databases. That being said, cached data won’t always match the real data stored in the database. A cache-aside pattern is a strategy to update the cache, to keep it relevant and reduce database overhead.
+Parallelism and Concurrence
+Concurrency is when multiple threads can be paused and resumed. In other words, it’s when a CPU pauses one task to prioritize another. Parallelism is when tasks are running on multiple cores (a quad-core CPU means four tasks running at the same time). In short, concurrency is about dealing with many things at once; parallelism is about doing many things at once. Pausing parts of the application while allowing the meaningful ones to run optimizes performance.
+SQL Performance and Optimization
+Optimizing SQL performance is key to guaranteeing SQL queries are as fast and smooth as possible, improving performance on any database that uses a relational database. This is especially concerning when dealing with Big Data, where many tables might have millions of rows.
+Content Distribution Network (CDN)
+A Content Distribution Network (CDN) is a server cluster distributed worldwide. They store cache content near the end user, making access to the services easier and faster. Important websites use this performance practice, such as Amazon, Facebook, Google, and Netflix.
+Don’t Overly Optimize or Modularize Upfront
+You complicate the code and risk improving runtime inconsequentially when you optimize early. Instead, get a clean, clear algorithm and prioritize it later. Similarly, trying to make the system modular and extensible should be done moderately. Wait until a need arises, or you risk making the wrong interfaces and wasting time and resources.
+9. AI-Assisted Development
+AI-Assisted Development consists of using LLMs for code generation and automated refactoring, and deploying AI tools for static analysis and vulnerability scanning.
+For code generation, have in mind that AIs don’t make architectural decisions alone, nor code considering your business needs, no matter how much context you give them in a prompt.
+According to a
+METR study
+published in July 2025, senior developers using AI tools were, on average, 19% slower at completing tasks compared to working without AI assistance. The reason for the slowness is both prompt and code refactoring. Despite decreased speed, these developers perceived themselves as being 20% faster when using AI. The phenomenon was described as a “productivity placebo”.
+To maintain high standards while leveraging these tools, divide the AI workflow into two categories: high-velocity delegation and high-stakes manual oversight.
+Leveraging AI
+Avoiding AI
+Boilerplate &amp; Scaffolding:
+Generating repetitive structures, standard API endpoints, and setup files.
+Architectural Decisions:
+Deciding how systems scale, how data flows, and how the overall design remains coherent.
+Unit Testing:
+Rapidly generating test cases for various edge scenarios.
+Ambiguous Requirements:
+Navigating the “gray areas” where business needs are poorly defined or contradictory.
+Documentation:
+Drafting initial versions of README files or inline comments based on existing logic.
+Root-Cause Debugging:
+Solving deep, systemic bugs that AI-generated “quick fixes” often overlook or exacerbate.
+Refactoring Logic:
+Using LLMs to suggest more idiomatic ways to write a specific, isolated function.
+Long-term Sustainability:
+Ensuring the code remains maintainable five years from now, not just “runnable” today.
+10. Automated And Secure CI/CD Pipelines
+Continuous Integration and Continuous Deployment
+(CI/CD) pipelines are the backbone of high-performing engineering teams. A robust pipeline ensures that every code change is automatically built, tested, and prepared for release, reducing human error and increasing deployment frequency.
+Continuous Integration (CI):
+Every time a developer pushes code, the system should automatically run unit tests and linters. This catches “breaking changes” immediately, preventing technical debt from accumulating.
+Continuous Deployment (CD):
+Once code passes all checks, it should be deployed to a staging or production environment automatically. This eliminates the “it works on my machine” syndrome and allows for faster feedback loops with users.
+Automation without
+security
+is a recipe for disaster. Integrating security into your pipeline (
+shifting left
+) is a critical best practice:
+Secrets Management:
+Never hardcode API keys or passwords. Use specialized tools (like HashiCorp Vault or AWS Secrets Manager) that your pipeline can call securely.
+SCA and SAST:
+Implement Software Composition Analysis (SCA) to check for vulnerabilities in third-party libraries (like Log4j) and Static Application Security Testing (SAST) to scan your own code for security flaws before it even hits production.
+Container Scanning:
+If you are using Docker or Kubernetes, ensure your pipeline scans images for vulnerabilities during the build process.
+Conclusion
+Software engineering best practices can help you build maintainable, scalable, and secure software products.
+We have shared ten software engineering practices that can enhance the outcome of your software projects. However, this is not an exhaustive list. The technology industry constantly evolves, so it can be tricky to keep up with the latest trends, especially when you’re looking for talent.
+That’s where we can help at DistantJob. We can help you find and vet potential hires to ensure they stay up-to-date with industry trends. Our culture-centric approach ensures that the candidates not only have the technical skills but also fit well into your company’s culture.
+In addition, we take care of all the
+HR processes
+, from finding suitable candidates to onboarding them. This enables you to focus on building your software products and growing your business. Ready to get started?
+Contact us!
+Cesar Fazio
+César is a digital marketing strategist and business growth consultant with experience in copywriting. Self-taught and passionate about continuous learning, César works at the intersection of technology, business, and strategic communication.
+In recent years, he has expanded his expertise to product management and Python, incorporating software development and Scrum best practices into his repertoire. This combination of business acumen and technical prowess allows structured scalable digital products aligned with real market needs.
+Currently, he collaborates with DistantJob, providing insights on marketing, branding, and digital transformation, always with a pragmatic, ethical, and results-oriented approach—far from vanity metrics and focused on measurable performance.
+Learn how to hire offshore people who outperform local hires
+What if you could approach companies similar to yours, interview their top performers, and hire them for 50% of a North American salary?
+Find Out How
+Subscribe to our newsletter and get exclusive content and bloopers
+or Share this post</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>EC3; EC5</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/data/processed/export/APOLLO_Screening_Results.xlsx
+++ b/data/processed/export/APOLLO_Screening_Results.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -706,7 +706,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -735,12 +735,12 @@
           <t>Data visualization; Visualization; API; Coding platform; Data; Digital resumes; Problem-solving; Project efficiency; Retrieval; Silicon valley; Software developer; Web scrapings; Websites</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -751,7 +751,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -796,7 +796,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -837,7 +837,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -866,12 +866,12 @@
           <t>collaborative and social computing; large language models; social simulation</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2; IC4</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -882,7 +882,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -919,7 +919,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -956,7 +956,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -993,7 +993,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1030,7 +1030,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -1075,7 +1075,7 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1112,7 +1112,7 @@
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1149,7 +1149,7 @@
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1186,7 +1186,7 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1223,7 +1223,7 @@
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1260,7 +1260,7 @@
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1297,7 +1297,7 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1334,7 +1334,7 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1371,7 +1371,7 @@
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1408,7 +1408,7 @@
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1445,7 +1445,7 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1482,7 +1482,7 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1519,7 +1519,7 @@
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1556,7 +1556,7 @@
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -1601,7 +1601,7 @@
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1638,7 +1638,7 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1675,7 +1675,7 @@
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1712,7 +1712,7 @@
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1749,7 +1749,7 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1786,7 +1786,7 @@
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1823,7 +1823,7 @@
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1860,7 +1860,7 @@
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1897,7 +1897,7 @@
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1934,7 +1934,7 @@
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -1971,7 +1971,7 @@
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2008,7 +2008,7 @@
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2045,7 +2045,7 @@
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2082,7 +2082,7 @@
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1">
+    <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2119,7 +2119,7 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2156,7 +2156,7 @@
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2193,7 +2193,7 @@
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2230,7 +2230,7 @@
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2267,7 +2267,7 @@
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2304,7 +2304,7 @@
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2349,7 +2349,7 @@
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2386,7 +2386,7 @@
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2407,12 +2407,12 @@
       </c>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC3; IC5</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
           <t>YES</t>
@@ -2423,7 +2423,7 @@
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2460,7 +2460,7 @@
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2497,7 +2497,7 @@
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Springer Nature</t>
@@ -2534,7 +2534,7 @@
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Web of Science</t>
@@ -2563,12 +2563,12 @@
           <t>Organizations; Project management; Recruitment; Software; Uncertainty; Stakeholders; Receivers; Agile project management (APM); Agile project manager (AgPM); competencies; job advertisements; signaling theory</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC3</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
           <t>YES</t>
@@ -2579,7 +2579,7 @@
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Web of Science</t>
@@ -2608,12 +2608,12 @@
           <t>Open Source Software; Mining Software Repositories; Developer Expertise; Visualization Tool</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC2; IC3</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>EC4</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2624,7 +2624,7 @@
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2669,7 +2669,7 @@
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2714,7 +2714,7 @@
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2759,7 +2759,7 @@
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2804,7 +2804,7 @@
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
     </row>
-    <row r="57" ht="20" customHeight="1">
+    <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2849,7 +2849,7 @@
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2894,7 +2894,7 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2939,7 +2939,7 @@
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -2984,7 +2984,7 @@
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3029,7 +3029,7 @@
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3074,7 +3074,7 @@
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3119,7 +3119,7 @@
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3160,7 +3160,7 @@
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
     </row>
-    <row r="65" ht="20" customHeight="1">
+    <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3205,7 +3205,7 @@
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1">
+    <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3250,7 +3250,7 @@
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3295,7 +3295,7 @@
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
     </row>
-    <row r="68" ht="20" customHeight="1">
+    <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3340,7 +3340,7 @@
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
     </row>
-    <row r="69" ht="20" customHeight="1">
+    <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3385,7 +3385,7 @@
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
     </row>
-    <row r="70" ht="20" customHeight="1">
+    <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3430,7 +3430,7 @@
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
+    <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3475,7 +3475,7 @@
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
     </row>
-    <row r="72" ht="20" customHeight="1">
+    <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>ACM Digital Library</t>
@@ -3520,7 +3520,7 @@
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
     </row>
-    <row r="73" ht="20" customHeight="1">
+    <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -3565,7 +3565,7 @@
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
     </row>
-    <row r="74" ht="20" customHeight="1">
+    <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -3606,7 +3606,7 @@
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
     </row>
-    <row r="75" ht="20" customHeight="1">
+    <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -3651,7 +3651,7 @@
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
     </row>
-    <row r="76" ht="20" customHeight="1">
+    <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Scopus</t>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Web Content</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>iiitsurat.ac.in</t>
@@ -3826,7 +3826,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>news.mit.edu</t>
@@ -3867,7 +3867,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>www.getharvest.com</t>
@@ -4000,7 +4000,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>www.ctm-it.com</t>
@@ -4065,12 +4065,12 @@
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>EC5</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>IC1; IC2; IC4</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>YES</t>
@@ -4081,7 +4081,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>www.hse.ru</t>
@@ -4169,7 +4169,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>www.thisdot.co</t>
@@ -4409,7 +4409,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>towardsdatascience.com</t>
@@ -4450,7 +4450,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>spb.hse.ru</t>
@@ -4603,7 +4603,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>www.securityclearedjobs.com</t>
@@ -4644,7 +4644,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>addyosmani.com</t>
@@ -4783,12 +4783,12 @@
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>IC1; IC3; IC5</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>EC5</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4799,7 +4799,7 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>careers.chevron.com</t>
@@ -4921,7 +4921,7 @@
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>society-rse.org</t>
@@ -4977,12 +4977,12 @@
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>EC3</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>IC1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>YES</t>
@@ -4993,7 +4993,7 @@
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>www.wearedevelopers.com</t>
@@ -5159,7 +5159,7 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>distantjob.com</t>
